--- a/analysis/derived_data/FT_STA_formatted-data.xlsx
+++ b/analysis/derived_data/FT_STA_formatted-data.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>276</v>
+        <v>600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>276</v>
+        <v>600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>276</v>
+        <v>600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>276</v>
+        <v>600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="C73">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="C78">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/analysis/derived_data/FT_STA_formatted-data.xlsx
+++ b/analysis/derived_data/FT_STA_formatted-data.xlsx
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>476</v>
+        <v>560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>476</v>
+        <v>560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>476</v>
+        <v>560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>476</v>
+        <v>560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/analysis/derived_data/FT_STA_formatted-data.xlsx
+++ b/analysis/derived_data/FT_STA_formatted-data.xlsx
@@ -598,7 +598,7 @@
         <v>510.3146761</v>
       </c>
       <c r="I2">
-        <v>0.2082995257</v>
+        <v>0.208299526</v>
       </c>
       <c r="J2">
         <v>3.611167169</v>
@@ -628,13 +628,13 @@
         <v>5.535717812</v>
       </c>
       <c r="S2">
-        <v>0.7571264937</v>
+        <v>0.757126494</v>
       </c>
       <c r="T2">
         <v>54.74853125</v>
       </c>
       <c r="U2">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V2">
         <v>0.59373265</v>
@@ -643,28 +643,28 @@
         <v>14.10821254</v>
       </c>
       <c r="X2">
-        <v>0.03220712242</v>
+        <v>0.032207122</v>
       </c>
       <c r="Y2">
-        <v>0.6632382845</v>
+        <v>0.663238285</v>
       </c>
       <c r="Z2">
-        <v>0.03220712242</v>
+        <v>0.032207122</v>
       </c>
       <c r="AA2">
-        <v>0.4298770045</v>
+        <v>0.429877005</v>
       </c>
       <c r="AB2">
-        <v>0.6058455505</v>
+        <v>0.605845551</v>
       </c>
       <c r="AC2">
-        <v>0.05739273397</v>
+        <v>0.057392734</v>
       </c>
       <c r="AD2">
         <v>44.99066565</v>
       </c>
       <c r="AE2">
-        <v>0.01081937014</v>
+        <v>0.01081937</v>
       </c>
       <c r="AF2">
         <v>90.00509230999999</v>
@@ -682,10 +682,10 @@
         <v>6492.158778</v>
       </c>
       <c r="AK2">
-        <v>0.0005855797274</v>
+        <v>0.00058558</v>
       </c>
       <c r="AL2">
-        <v>0.01748434864</v>
+        <v>0.017484349</v>
       </c>
       <c r="AM2">
         <v>49.92665862</v>
@@ -694,7 +694,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO2">
-        <v>0.1333228463</v>
+        <v>0.133322846</v>
       </c>
     </row>
     <row r="3">
@@ -763,37 +763,37 @@
         <v>6.570978128</v>
       </c>
       <c r="S3">
-        <v>0.6973377801</v>
+        <v>0.69733778</v>
       </c>
       <c r="T3">
         <v>74.74840725</v>
       </c>
       <c r="U3">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V3">
-        <v>0.3186908037</v>
+        <v>0.318690804</v>
       </c>
       <c r="W3">
         <v>4.665524789</v>
       </c>
       <c r="X3">
-        <v>0.04181877389</v>
+        <v>0.041818774</v>
       </c>
       <c r="Y3">
-        <v>0.7468693034</v>
+        <v>0.746869303</v>
       </c>
       <c r="Z3">
-        <v>0.04181877389</v>
+        <v>0.041818774</v>
       </c>
       <c r="AA3">
-        <v>0.4518376615</v>
+        <v>0.451837662</v>
       </c>
       <c r="AB3">
-        <v>0.6665194179</v>
+        <v>0.666519418</v>
       </c>
       <c r="AC3">
-        <v>0.08034988547999999</v>
+        <v>0.080349885</v>
       </c>
       <c r="AD3">
         <v>89.99558777999999</v>
@@ -817,10 +817,10 @@
         <v>6945.496465</v>
       </c>
       <c r="AK3">
-        <v>0.002807360738</v>
+        <v>0.002807361</v>
       </c>
       <c r="AL3">
-        <v>0.01681894117</v>
+        <v>0.016818941</v>
       </c>
       <c r="AM3">
         <v>13.83171789</v>
@@ -829,7 +829,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO3">
-        <v>0.4437028233</v>
+        <v>0.443702823</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
         <v>399.6521136</v>
       </c>
       <c r="O4">
-        <v>0.1384576616</v>
+        <v>0.138457662</v>
       </c>
       <c r="P4">
         <v>594.0356977</v>
@@ -898,13 +898,13 @@
         <v>5.662374686</v>
       </c>
       <c r="S4">
-        <v>0.6112437598</v>
+        <v>0.61124376</v>
       </c>
       <c r="T4">
         <v>85.50156405</v>
       </c>
       <c r="U4">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V4">
         <v>0.372205708</v>
@@ -913,22 +913,22 @@
         <v>5.960471374</v>
       </c>
       <c r="X4">
-        <v>0.04105984277</v>
+        <v>0.041059843</v>
       </c>
       <c r="Y4">
-        <v>0.6350725639</v>
+        <v>0.635072564</v>
       </c>
       <c r="Z4">
-        <v>0.04105984277</v>
+        <v>0.041059843</v>
       </c>
       <c r="AA4">
-        <v>0.3806122545</v>
+        <v>0.380612255</v>
       </c>
       <c r="AB4">
-        <v>0.5465986711</v>
+        <v>0.546598671</v>
       </c>
       <c r="AC4">
-        <v>0.08847389275</v>
+        <v>0.088473893</v>
       </c>
       <c r="AD4">
         <v>90.00049955</v>
@@ -952,10 +952,10 @@
         <v>7121.220991</v>
       </c>
       <c r="AK4">
-        <v>0.0017361474</v>
+        <v>0.001736147</v>
       </c>
       <c r="AL4">
-        <v>0.01787319695</v>
+        <v>0.017873197</v>
       </c>
       <c r="AM4">
         <v>19.82068691</v>
@@ -964,7 +964,7 @@
         <v>1.49503139</v>
       </c>
       <c r="AO4">
-        <v>0.9494296848</v>
+        <v>0.949429685</v>
       </c>
     </row>
     <row r="5">
@@ -1003,7 +1003,7 @@
         <v>535.8292596</v>
       </c>
       <c r="I5">
-        <v>0.3066294796</v>
+        <v>0.30662948</v>
       </c>
       <c r="J5">
         <v>3.504881576</v>
@@ -1033,13 +1033,13 @@
         <v>5.69363755</v>
       </c>
       <c r="S5">
-        <v>0.6484317613</v>
+        <v>0.648431761</v>
       </c>
       <c r="T5">
         <v>57.75130496</v>
       </c>
       <c r="U5">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V5">
         <v>0.324198925</v>
@@ -1048,22 +1048,22 @@
         <v>4.854969956</v>
       </c>
       <c r="X5">
-        <v>0.03305849431</v>
+        <v>0.033058494</v>
       </c>
       <c r="Y5">
-        <v>0.7030889261</v>
+        <v>0.7030889259999999</v>
       </c>
       <c r="Z5">
-        <v>0.03305849431</v>
+        <v>0.033058494</v>
       </c>
       <c r="AA5">
-        <v>0.4670876133</v>
+        <v>0.467087613</v>
       </c>
       <c r="AB5">
-        <v>0.6490425864</v>
+        <v>0.649042586</v>
       </c>
       <c r="AC5">
-        <v>0.05404633971</v>
+        <v>0.05404634</v>
       </c>
       <c r="AD5">
         <v>44.98490159</v>
@@ -1087,10 +1087,10 @@
         <v>6632.411999</v>
       </c>
       <c r="AK5">
-        <v>0.00238340124</v>
+        <v>0.002383401</v>
       </c>
       <c r="AL5">
-        <v>0.01666934487</v>
+        <v>0.016669345</v>
       </c>
       <c r="AM5">
         <v>13.0605013</v>
@@ -1099,7 +1099,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO5">
-        <v>0.3135671868</v>
+        <v>0.313567187</v>
       </c>
     </row>
     <row r="6">
@@ -1138,7 +1138,7 @@
         <v>461.3624847</v>
       </c>
       <c r="I6">
-        <v>0.3644241958</v>
+        <v>0.364424196</v>
       </c>
       <c r="J6">
         <v>3.438281754</v>
@@ -1168,37 +1168,37 @@
         <v>6.10753735</v>
       </c>
       <c r="S6">
-        <v>0.6810785363</v>
+        <v>0.681078536</v>
       </c>
       <c r="T6">
         <v>86.25057710999999</v>
       </c>
       <c r="U6">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V6">
-        <v>0.3179694623</v>
+        <v>0.317969462</v>
       </c>
       <c r="W6">
         <v>4.701684148</v>
       </c>
       <c r="X6">
-        <v>0.03014862059</v>
+        <v>0.030148621</v>
       </c>
       <c r="Y6">
-        <v>0.5983674765</v>
+        <v>0.598367477</v>
       </c>
       <c r="Z6">
-        <v>0.03014862059</v>
+        <v>0.030148621</v>
       </c>
       <c r="AA6">
-        <v>0.4005538481</v>
+        <v>0.400553848</v>
       </c>
       <c r="AB6">
-        <v>0.5514198143</v>
+        <v>0.551419814</v>
       </c>
       <c r="AC6">
-        <v>0.04694766218</v>
+        <v>0.046947662</v>
       </c>
       <c r="AD6">
         <v>89.99058392000001</v>
@@ -1222,19 +1222,19 @@
         <v>6748.033798</v>
       </c>
       <c r="AK6">
-        <v>0.002473628671</v>
+        <v>0.002473629</v>
       </c>
       <c r="AL6">
-        <v>0.01686902362</v>
+        <v>0.016869024</v>
       </c>
       <c r="AM6">
         <v>13.10260134</v>
       </c>
       <c r="AN6">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO6">
-        <v>0.1773680407</v>
+        <v>0.177368041</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
         <v>537.4528483</v>
       </c>
       <c r="I7">
-        <v>-0.3339857246</v>
+        <v>-0.333985725</v>
       </c>
       <c r="J7">
         <v>4.060290192</v>
@@ -1303,37 +1303,37 @@
         <v>5.961985451</v>
       </c>
       <c r="S7">
-        <v>0.6743631927</v>
+        <v>0.674363193</v>
       </c>
       <c r="T7">
         <v>86.99719416000001</v>
       </c>
       <c r="U7">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V7">
-        <v>0.4060170515</v>
+        <v>0.406017052</v>
       </c>
       <c r="W7">
         <v>7.404031275</v>
       </c>
       <c r="X7">
-        <v>0.02403996445</v>
+        <v>0.024039964</v>
       </c>
       <c r="Y7">
-        <v>0.6982754828</v>
+        <v>0.698275483</v>
       </c>
       <c r="Z7">
-        <v>0.02403996445</v>
+        <v>0.024039964</v>
       </c>
       <c r="AA7">
-        <v>0.4565222931</v>
+        <v>0.456522293</v>
       </c>
       <c r="AB7">
-        <v>0.6277425315</v>
+        <v>0.627742532</v>
       </c>
       <c r="AC7">
-        <v>0.07053295125</v>
+        <v>0.070532951</v>
       </c>
       <c r="AD7">
         <v>45.01407039</v>
@@ -1357,19 +1357,19 @@
         <v>7054.717255</v>
       </c>
       <c r="AK7">
-        <v>0.001293232514</v>
+        <v>0.001293233</v>
       </c>
       <c r="AL7">
-        <v>0.01710848802</v>
+        <v>0.017108488</v>
       </c>
       <c r="AM7">
         <v>26.90326537</v>
       </c>
       <c r="AN7">
-        <v>0.8893344066</v>
+        <v>0.889334407</v>
       </c>
       <c r="AO7">
-        <v>0.2908531468</v>
+        <v>0.290853147</v>
       </c>
     </row>
     <row r="8">
@@ -1408,7 +1408,7 @@
         <v>539.9840836</v>
       </c>
       <c r="I8">
-        <v>-0.3048245575</v>
+        <v>-0.304824558</v>
       </c>
       <c r="J8">
         <v>8.520845771999999</v>
@@ -1426,7 +1426,7 @@
         <v>372.9492162</v>
       </c>
       <c r="O8">
-        <v>0.1205739737</v>
+        <v>0.120573974</v>
       </c>
       <c r="P8">
         <v>572.0733026</v>
@@ -1438,43 +1438,43 @@
         <v>6.019787637</v>
       </c>
       <c r="S8">
-        <v>0.7277695592</v>
+        <v>0.727769559</v>
       </c>
       <c r="T8">
         <v>3.737033889</v>
       </c>
       <c r="U8">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V8">
-        <v>0.3262536467</v>
+        <v>0.326253647</v>
       </c>
       <c r="W8">
         <v>4.692863466</v>
       </c>
       <c r="X8">
-        <v>0.03517589837</v>
+        <v>0.035175898</v>
       </c>
       <c r="Y8">
-        <v>0.6072529225</v>
+        <v>0.607252923</v>
       </c>
       <c r="Z8">
-        <v>0.03517589837</v>
+        <v>0.035175898</v>
       </c>
       <c r="AA8">
-        <v>0.3695906382</v>
+        <v>0.369590638</v>
       </c>
       <c r="AB8">
-        <v>0.5320561324999999</v>
+        <v>0.532056133</v>
       </c>
       <c r="AC8">
-        <v>0.07519678993999999</v>
+        <v>0.07519679</v>
       </c>
       <c r="AD8">
         <v>89.99521581</v>
       </c>
       <c r="AE8">
-        <v>0.01655438439</v>
+        <v>0.016554384</v>
       </c>
       <c r="AF8">
         <v>45.0192746</v>
@@ -1492,10 +1492,10 @@
         <v>6799.609241</v>
       </c>
       <c r="AK8">
-        <v>0.00210622374</v>
+        <v>0.002106224</v>
       </c>
       <c r="AL8">
-        <v>0.01756054661</v>
+        <v>0.017560547</v>
       </c>
       <c r="AM8">
         <v>15.39682273</v>
@@ -1543,7 +1543,7 @@
         <v>588.5908686</v>
       </c>
       <c r="I9">
-        <v>0.3072441328</v>
+        <v>0.307244133</v>
       </c>
       <c r="J9">
         <v>3.674228689</v>
@@ -1573,37 +1573,37 @@
         <v>5.260780714</v>
       </c>
       <c r="S9">
-        <v>0.6515059861</v>
+        <v>0.651505986</v>
       </c>
       <c r="T9">
         <v>154.9948161</v>
       </c>
       <c r="U9">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V9">
-        <v>0.6756095828000001</v>
+        <v>0.675609583</v>
       </c>
       <c r="W9">
         <v>17.56141901</v>
       </c>
       <c r="X9">
-        <v>0.03707699527</v>
+        <v>0.037076995</v>
       </c>
       <c r="Y9">
-        <v>0.7713945615</v>
+        <v>0.771394562</v>
       </c>
       <c r="Z9">
-        <v>0.03707699527</v>
+        <v>0.037076995</v>
       </c>
       <c r="AA9">
-        <v>0.5044340074</v>
+        <v>0.504434007</v>
       </c>
       <c r="AB9">
-        <v>0.7104924061</v>
+        <v>0.710492406</v>
       </c>
       <c r="AC9">
-        <v>0.0609021554</v>
+        <v>0.060902155</v>
       </c>
       <c r="AD9">
         <v>44.96265715</v>
@@ -1627,10 +1627,10 @@
         <v>6332.729893</v>
       </c>
       <c r="AK9">
-        <v>0.001431175296</v>
+        <v>0.001431175</v>
       </c>
       <c r="AL9">
-        <v>0.01763059265</v>
+        <v>0.017630593</v>
       </c>
       <c r="AM9">
         <v>60.36009183</v>
@@ -1639,7 +1639,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO9">
-        <v>0.3175678915</v>
+        <v>0.317567892</v>
       </c>
     </row>
     <row r="10">
@@ -1678,7 +1678,7 @@
         <v>418.1911344</v>
       </c>
       <c r="I10">
-        <v>-0.2748245721</v>
+        <v>-0.274824572</v>
       </c>
       <c r="J10">
         <v>3.861412347</v>
@@ -1708,37 +1708,37 @@
         <v>5.350888373</v>
       </c>
       <c r="S10">
-        <v>0.7207036583999999</v>
+        <v>0.720703658</v>
       </c>
       <c r="T10">
         <v>73.24679519999999</v>
       </c>
       <c r="U10">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V10">
-        <v>0.3125742457</v>
+        <v>0.312574246</v>
       </c>
       <c r="W10">
         <v>4.595304171</v>
       </c>
       <c r="X10">
-        <v>0.01979167513</v>
+        <v>0.019791675</v>
       </c>
       <c r="Y10">
-        <v>0.5308658305</v>
+        <v>0.530865831</v>
       </c>
       <c r="Z10">
-        <v>0.01979167513</v>
+        <v>0.019791675</v>
       </c>
       <c r="AA10">
-        <v>0.3604080293</v>
+        <v>0.360408029</v>
       </c>
       <c r="AB10">
-        <v>0.4769462606</v>
+        <v>0.476946261</v>
       </c>
       <c r="AC10">
-        <v>0.05391956989</v>
+        <v>0.05391957</v>
       </c>
       <c r="AD10">
         <v>90.00599378</v>
@@ -1762,10 +1762,10 @@
         <v>7388.894195</v>
       </c>
       <c r="AK10">
-        <v>0.001747257457</v>
+        <v>0.001747257</v>
       </c>
       <c r="AL10">
-        <v>0.0169852232</v>
+        <v>0.016985223</v>
       </c>
       <c r="AM10">
         <v>13.21267267</v>
@@ -1813,7 +1813,7 @@
         <v>503.4285743</v>
       </c>
       <c r="I11">
-        <v>0.3235614654</v>
+        <v>0.323561465</v>
       </c>
       <c r="J11">
         <v>5.524179616</v>
@@ -1831,7 +1831,7 @@
         <v>368.7360754</v>
       </c>
       <c r="O11">
-        <v>0.4557563058</v>
+        <v>0.455756306</v>
       </c>
       <c r="P11">
         <v>572.6412771</v>
@@ -1843,37 +1843,37 @@
         <v>5.655654493</v>
       </c>
       <c r="S11">
-        <v>0.8276041391</v>
+        <v>0.827604139</v>
       </c>
       <c r="T11">
         <v>65.50174826999999</v>
       </c>
       <c r="U11">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V11">
-        <v>0.3703375321</v>
+        <v>0.370337532</v>
       </c>
       <c r="W11">
         <v>6.251337261</v>
       </c>
       <c r="X11">
-        <v>0.03554700628</v>
+        <v>0.035547006</v>
       </c>
       <c r="Y11">
         <v>0.6082180700000001</v>
       </c>
       <c r="Z11">
-        <v>0.03554700628</v>
+        <v>0.035547006</v>
       </c>
       <c r="AA11">
-        <v>0.3803869698</v>
+        <v>0.38038697</v>
       </c>
       <c r="AB11">
-        <v>0.5428319169</v>
+        <v>0.542831917</v>
       </c>
       <c r="AC11">
-        <v>0.0653861531</v>
+        <v>0.065386153</v>
       </c>
       <c r="AD11">
         <v>89.9983581</v>
@@ -1897,10 +1897,10 @@
         <v>8312.423063</v>
       </c>
       <c r="AK11">
-        <v>0.002688262227</v>
+        <v>0.002688262</v>
       </c>
       <c r="AL11">
-        <v>0.01721768627</v>
+        <v>0.017217686</v>
       </c>
       <c r="AM11">
         <v>20.59179929</v>
@@ -1909,7 +1909,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO11">
-        <v>0.4644043272</v>
+        <v>0.464404327</v>
       </c>
     </row>
     <row r="12">
@@ -1948,7 +1948,7 @@
         <v>510.7015034</v>
       </c>
       <c r="I12">
-        <v>-0.1017179979</v>
+        <v>-0.101717998</v>
       </c>
       <c r="J12">
         <v>4.289308911</v>
@@ -1978,43 +1978,43 @@
         <v>5.036067516</v>
       </c>
       <c r="S12">
-        <v>0.5964002514</v>
+        <v>0.596400251</v>
       </c>
       <c r="T12">
         <v>67.24925881</v>
       </c>
       <c r="U12">
-        <v>0.4246372572</v>
+        <v>0.424637257</v>
       </c>
       <c r="V12">
-        <v>0.3248305286</v>
+        <v>0.324830529</v>
       </c>
       <c r="W12">
         <v>4.878476929</v>
       </c>
       <c r="X12">
-        <v>0.03065693051</v>
+        <v>0.030656931</v>
       </c>
       <c r="Y12">
-        <v>0.6317136548</v>
+        <v>0.631713655</v>
       </c>
       <c r="Z12">
-        <v>0.03065693051</v>
+        <v>0.030656931</v>
       </c>
       <c r="AA12">
-        <v>0.4059322184</v>
+        <v>0.405932218</v>
       </c>
       <c r="AB12">
-        <v>0.5619703065</v>
+        <v>0.5619703069999999</v>
       </c>
       <c r="AC12">
-        <v>0.06974334824</v>
+        <v>0.069743348</v>
       </c>
       <c r="AD12">
         <v>90.00229208</v>
       </c>
       <c r="AE12">
-        <v>0.001037537941</v>
+        <v>0.001037538</v>
       </c>
       <c r="AF12">
         <v>44.99882789</v>
@@ -2032,10 +2032,10 @@
         <v>7508.532352</v>
       </c>
       <c r="AK12">
-        <v>0.0006787347894</v>
+        <v>0.000678735</v>
       </c>
       <c r="AL12">
-        <v>0.01750135799</v>
+        <v>0.017501358</v>
       </c>
       <c r="AM12">
         <v>14.13784574</v>
@@ -2044,7 +2044,7 @@
         <v>1.07962932</v>
       </c>
       <c r="AO12">
-        <v>0.3309803241</v>
+        <v>0.330980324</v>
       </c>
     </row>
     <row r="13">
@@ -2083,7 +2083,7 @@
         <v>484.9841795</v>
       </c>
       <c r="I13">
-        <v>0.01735928726</v>
+        <v>0.017359287</v>
       </c>
       <c r="J13">
         <v>3.09126278</v>
@@ -2119,31 +2119,31 @@
         <v>69.25657594</v>
       </c>
       <c r="U13">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V13">
-        <v>0.3093763631</v>
+        <v>0.309376363</v>
       </c>
       <c r="W13">
         <v>4.488861045</v>
       </c>
       <c r="X13">
-        <v>0.02343528147</v>
+        <v>0.023435281</v>
       </c>
       <c r="Y13">
-        <v>0.6423321598</v>
+        <v>0.64233216</v>
       </c>
       <c r="Z13">
-        <v>0.02343528147</v>
+        <v>0.023435281</v>
       </c>
       <c r="AA13">
-        <v>0.4252767668</v>
+        <v>0.425276767</v>
       </c>
       <c r="AB13">
-        <v>0.5867447531</v>
+        <v>0.586744753</v>
       </c>
       <c r="AC13">
-        <v>0.05558740676</v>
+        <v>0.055587407</v>
       </c>
       <c r="AD13">
         <v>90.00294669</v>
@@ -2167,10 +2167,10 @@
         <v>7731.862037</v>
       </c>
       <c r="AK13">
-        <v>0.00213097714</v>
+        <v>0.002130977</v>
       </c>
       <c r="AL13">
-        <v>0.01717676117</v>
+        <v>0.017176761</v>
       </c>
       <c r="AM13">
         <v>11.53373567</v>
@@ -2179,7 +2179,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO13">
-        <v>0.2004400441</v>
+        <v>0.200440044</v>
       </c>
     </row>
     <row r="14">
@@ -2218,7 +2218,7 @@
         <v>387.299794</v>
       </c>
       <c r="I14">
-        <v>0.07979476923000001</v>
+        <v>0.079794769</v>
       </c>
       <c r="J14">
         <v>3.500776241</v>
@@ -2254,31 +2254,31 @@
         <v>87.74501932</v>
       </c>
       <c r="U14">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V14">
-        <v>0.3187273061</v>
+        <v>0.318727306</v>
       </c>
       <c r="W14">
         <v>4.777423368</v>
       </c>
       <c r="X14">
-        <v>0.02218227862</v>
+        <v>0.022182279</v>
       </c>
       <c r="Y14">
-        <v>0.5041637596</v>
+        <v>0.50416376</v>
       </c>
       <c r="Z14">
-        <v>0.02218227862</v>
+        <v>0.022182279</v>
       </c>
       <c r="AA14">
-        <v>0.3282154699</v>
+        <v>0.32821547</v>
       </c>
       <c r="AB14">
-        <v>0.4594924808</v>
+        <v>0.459492481</v>
       </c>
       <c r="AC14">
-        <v>0.04467127885</v>
+        <v>0.044671279</v>
       </c>
       <c r="AD14">
         <v>89.98919463999999</v>
@@ -2302,19 +2302,19 @@
         <v>6638.707642</v>
       </c>
       <c r="AK14">
-        <v>0.002563995152</v>
+        <v>0.002563995</v>
       </c>
       <c r="AL14">
-        <v>0.01681041264</v>
+        <v>0.016810413</v>
       </c>
       <c r="AM14">
         <v>13.38708385</v>
       </c>
       <c r="AN14">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO14">
-        <v>0.1359610398</v>
+        <v>0.13596104</v>
       </c>
     </row>
     <row r="15">
@@ -2353,7 +2353,7 @@
         <v>521.4110425</v>
       </c>
       <c r="I15">
-        <v>0.3784196771</v>
+        <v>0.378419677</v>
       </c>
       <c r="J15">
         <v>5.334335944</v>
@@ -2371,7 +2371,7 @@
         <v>382.9884276</v>
       </c>
       <c r="O15">
-        <v>0.5592288168</v>
+        <v>0.559228817</v>
       </c>
       <c r="P15">
         <v>596.4435599</v>
@@ -2383,37 +2383,37 @@
         <v>5.804250165</v>
       </c>
       <c r="S15">
-        <v>0.8260109616</v>
+        <v>0.826010962</v>
       </c>
       <c r="T15">
         <v>64.99888462</v>
       </c>
       <c r="U15">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V15">
-        <v>0.3640128028</v>
+        <v>0.364012803</v>
       </c>
       <c r="W15">
         <v>6.023867001</v>
       </c>
       <c r="X15">
-        <v>0.03726276208</v>
+        <v>0.037262762</v>
       </c>
       <c r="Y15">
-        <v>0.6337051803</v>
+        <v>0.63370518</v>
       </c>
       <c r="Z15">
-        <v>0.03726276208</v>
+        <v>0.037262762</v>
       </c>
       <c r="AA15">
-        <v>0.3969249607</v>
+        <v>0.396924961</v>
       </c>
       <c r="AB15">
-        <v>0.5665934141</v>
+        <v>0.566593414</v>
       </c>
       <c r="AC15">
-        <v>0.06711176620000001</v>
+        <v>0.067111766</v>
       </c>
       <c r="AD15">
         <v>90.01348286</v>
@@ -2422,7 +2422,7 @@
         <v>63.5669445</v>
       </c>
       <c r="AF15">
-        <v>0.0148335673</v>
+        <v>0.014833567</v>
       </c>
       <c r="AG15">
         <v>84.32437627</v>
@@ -2437,10 +2437,10 @@
         <v>7635.045151</v>
       </c>
       <c r="AK15">
-        <v>0.002549388052</v>
+        <v>0.002549388</v>
       </c>
       <c r="AL15">
-        <v>0.01716253874</v>
+        <v>0.017162539</v>
       </c>
       <c r="AM15">
         <v>17.57738677</v>
@@ -2449,7 +2449,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO15">
-        <v>0.3766890808</v>
+        <v>0.376689081</v>
       </c>
     </row>
     <row r="16">
@@ -2518,40 +2518,40 @@
         <v>5.552590159</v>
       </c>
       <c r="S16">
-        <v>0.8802058318</v>
+        <v>0.880205832</v>
       </c>
       <c r="T16">
         <v>42.24951719</v>
       </c>
       <c r="U16">
-        <v>0.4246372572</v>
+        <v>0.424637257</v>
       </c>
       <c r="V16">
-        <v>0.3861588316</v>
+        <v>0.386158832</v>
       </c>
       <c r="W16">
         <v>6.784148269</v>
       </c>
       <c r="X16">
-        <v>0.02908580468</v>
+        <v>0.029085805</v>
       </c>
       <c r="Y16">
-        <v>0.6163789111</v>
+        <v>0.616378911</v>
       </c>
       <c r="Z16">
-        <v>0.02908580468</v>
+        <v>0.029085805</v>
       </c>
       <c r="AA16">
-        <v>0.4105293434</v>
+        <v>0.410529343</v>
       </c>
       <c r="AB16">
-        <v>0.5657108883</v>
+        <v>0.565710888</v>
       </c>
       <c r="AC16">
-        <v>0.05066802277</v>
+        <v>0.050668023</v>
       </c>
       <c r="AD16">
-        <v>0.0204526717</v>
+        <v>0.020452672</v>
       </c>
       <c r="AE16">
         <v>89.99623647</v>
@@ -2572,19 +2572,19 @@
         <v>7704.171062</v>
       </c>
       <c r="AK16">
-        <v>0.001504958411</v>
+        <v>0.001504958</v>
       </c>
       <c r="AL16">
-        <v>0.01702651601</v>
+        <v>0.017026516</v>
       </c>
       <c r="AM16">
         <v>20.52295659</v>
       </c>
       <c r="AN16">
-        <v>0.9481772307</v>
+        <v>0.948177231</v>
       </c>
       <c r="AO16">
-        <v>0.1694933578</v>
+        <v>0.169493358</v>
       </c>
     </row>
     <row r="17">
@@ -2623,7 +2623,7 @@
         <v>471.8481138</v>
       </c>
       <c r="I17">
-        <v>-0.03028751984</v>
+        <v>-0.03028752</v>
       </c>
       <c r="J17">
         <v>3.110815759</v>
@@ -2653,37 +2653,37 @@
         <v>5.336796261</v>
       </c>
       <c r="S17">
-        <v>0.6677286332</v>
+        <v>0.667728633</v>
       </c>
       <c r="T17">
         <v>50.99396777</v>
       </c>
       <c r="U17">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V17">
-        <v>0.3255764283</v>
+        <v>0.325576428</v>
       </c>
       <c r="W17">
         <v>4.955007873</v>
       </c>
       <c r="X17">
-        <v>0.02241051508</v>
+        <v>0.022410515</v>
       </c>
       <c r="Y17">
-        <v>0.6276818111</v>
+        <v>0.627681811</v>
       </c>
       <c r="Z17">
-        <v>0.02241051508</v>
+        <v>0.022410515</v>
       </c>
       <c r="AA17">
-        <v>0.4102652263</v>
+        <v>0.410265226</v>
       </c>
       <c r="AB17">
-        <v>0.5715046582</v>
+        <v>0.5715046580000001</v>
       </c>
       <c r="AC17">
-        <v>0.05617715287</v>
+        <v>0.056177153</v>
       </c>
       <c r="AD17">
         <v>63.53787504</v>
@@ -2707,10 +2707,10 @@
         <v>7696.915631</v>
       </c>
       <c r="AK17">
-        <v>0.002408372343</v>
+        <v>0.002408372</v>
       </c>
       <c r="AL17">
-        <v>0.01720808354</v>
+        <v>0.017208084</v>
       </c>
       <c r="AM17">
         <v>13.65012657</v>
@@ -2719,7 +2719,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO17">
-        <v>0.1478858446</v>
+        <v>0.147885845</v>
       </c>
     </row>
     <row r="18">
@@ -2758,7 +2758,7 @@
         <v>548.0495092</v>
       </c>
       <c r="I18">
-        <v>-0.1874626698</v>
+        <v>-0.18746267</v>
       </c>
       <c r="J18">
         <v>3.186759226</v>
@@ -2788,13 +2788,13 @@
         <v>6.49623193</v>
       </c>
       <c r="S18">
-        <v>0.8600703289</v>
+        <v>0.860070329</v>
       </c>
       <c r="T18">
         <v>132.2503093</v>
       </c>
       <c r="U18">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V18">
         <v>0.333193916</v>
@@ -2803,22 +2803,22 @@
         <v>5.162452275</v>
       </c>
       <c r="X18">
-        <v>0.02562058476</v>
+        <v>0.025620585</v>
       </c>
       <c r="Y18">
-        <v>0.6870499348</v>
+        <v>0.687049935</v>
       </c>
       <c r="Z18">
-        <v>0.02562058476</v>
+        <v>0.025620585</v>
       </c>
       <c r="AA18">
-        <v>0.4908631662</v>
+        <v>0.490863166</v>
       </c>
       <c r="AB18">
-        <v>0.6196552071</v>
+        <v>0.619655207</v>
       </c>
       <c r="AC18">
-        <v>0.06739472769</v>
+        <v>0.067394728</v>
       </c>
       <c r="AD18">
         <v>90.00216137</v>
@@ -2842,10 +2842,10 @@
         <v>7668.045181</v>
       </c>
       <c r="AK18">
-        <v>0.001883012182</v>
+        <v>0.001883012</v>
       </c>
       <c r="AL18">
-        <v>0.01696157831</v>
+        <v>0.016961578</v>
       </c>
       <c r="AM18">
         <v>15.23046992</v>
@@ -2893,7 +2893,7 @@
         <v>661.5677942</v>
       </c>
       <c r="I19">
-        <v>0.2383651136</v>
+        <v>0.238365114</v>
       </c>
       <c r="J19">
         <v>3.493185053</v>
@@ -2929,31 +2929,31 @@
         <v>71.25125500999999</v>
       </c>
       <c r="U19">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V19">
-        <v>0.3388553304</v>
+        <v>0.33885533</v>
       </c>
       <c r="W19">
         <v>5.244692208</v>
       </c>
       <c r="X19">
-        <v>0.04105877466</v>
+        <v>0.041058775</v>
       </c>
       <c r="Y19">
-        <v>0.8881626566</v>
+        <v>0.888162657</v>
       </c>
       <c r="Z19">
-        <v>0.04105877466</v>
+        <v>0.041058775</v>
       </c>
       <c r="AA19">
-        <v>0.5489007326999999</v>
+        <v>0.548900733</v>
       </c>
       <c r="AB19">
-        <v>0.8152185101</v>
+        <v>0.81521851</v>
       </c>
       <c r="AC19">
-        <v>0.07294414649</v>
+        <v>0.072944146</v>
       </c>
       <c r="AD19">
         <v>44.98925474</v>
@@ -2977,10 +2977,10 @@
         <v>8068.601261</v>
       </c>
       <c r="AK19">
-        <v>0.0007416757947000001</v>
+        <v>0.000741676</v>
       </c>
       <c r="AL19">
-        <v>0.01775605854</v>
+        <v>0.017756059</v>
       </c>
       <c r="AM19">
         <v>15.74455287</v>
@@ -2989,7 +2989,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO19">
-        <v>0.5674207524</v>
+        <v>0.567420752</v>
       </c>
     </row>
     <row r="20">
@@ -3028,7 +3028,7 @@
         <v>519.2917982</v>
       </c>
       <c r="I20">
-        <v>0.008388549015</v>
+        <v>0.008388549</v>
       </c>
       <c r="J20">
         <v>3.362976194</v>
@@ -3058,13 +3058,13 @@
         <v>5.47080351</v>
       </c>
       <c r="S20">
-        <v>0.6306597567</v>
+        <v>0.630659757</v>
       </c>
       <c r="T20">
         <v>92.51457499</v>
       </c>
       <c r="U20">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V20">
         <v>0.301225401</v>
@@ -3073,22 +3073,22 @@
         <v>4.262667829</v>
       </c>
       <c r="X20">
-        <v>0.02839968715</v>
+        <v>0.028399687</v>
       </c>
       <c r="Y20">
-        <v>0.6682566522</v>
+        <v>0.668256652</v>
       </c>
       <c r="Z20">
-        <v>0.02839968715</v>
+        <v>0.028399687</v>
       </c>
       <c r="AA20">
-        <v>0.4498010684</v>
+        <v>0.449801068</v>
       </c>
       <c r="AB20">
-        <v>0.6052956213</v>
+        <v>0.605295621</v>
       </c>
       <c r="AC20">
-        <v>0.06296103097</v>
+        <v>0.062961031</v>
       </c>
       <c r="AD20">
         <v>90.00556184</v>
@@ -3112,10 +3112,10 @@
         <v>8249.824144</v>
       </c>
       <c r="AK20">
-        <v>0.002493304332</v>
+        <v>0.002493304</v>
       </c>
       <c r="AL20">
-        <v>0.01662275187</v>
+        <v>0.016622752</v>
       </c>
       <c r="AM20">
         <v>11.39144626</v>
@@ -3124,7 +3124,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO20">
-        <v>0.2659656469</v>
+        <v>0.265965647</v>
       </c>
     </row>
     <row r="21">
@@ -3163,7 +3163,7 @@
         <v>564.0463701</v>
       </c>
       <c r="I21">
-        <v>-0.06787330208</v>
+        <v>-0.067873302</v>
       </c>
       <c r="J21">
         <v>3.301562239</v>
@@ -3193,43 +3193,43 @@
         <v>4.859419226</v>
       </c>
       <c r="S21">
-        <v>0.7911815992</v>
+        <v>0.791181599</v>
       </c>
       <c r="T21">
         <v>51.24495329</v>
       </c>
       <c r="U21">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V21">
-        <v>0.3737852595</v>
+        <v>0.37378526</v>
       </c>
       <c r="W21">
         <v>6.256990387</v>
       </c>
       <c r="X21">
-        <v>0.02790315737</v>
+        <v>0.027903157</v>
       </c>
       <c r="Y21">
-        <v>0.7101621866</v>
+        <v>0.710162187</v>
       </c>
       <c r="Z21">
-        <v>0.02790315737</v>
+        <v>0.027903157</v>
       </c>
       <c r="AA21">
-        <v>0.5008117147</v>
+        <v>0.500811715</v>
       </c>
       <c r="AB21">
-        <v>0.6410925072</v>
+        <v>0.641092507</v>
       </c>
       <c r="AC21">
-        <v>0.06906967941</v>
+        <v>0.06906967899999999</v>
       </c>
       <c r="AD21">
         <v>44.97297542</v>
       </c>
       <c r="AE21">
-        <v>0.007793994133</v>
+        <v>0.007793994</v>
       </c>
       <c r="AF21">
         <v>90.00897873</v>
@@ -3247,10 +3247,10 @@
         <v>7039.042073</v>
       </c>
       <c r="AK21">
-        <v>0.0005732247993</v>
+        <v>0.000573225</v>
       </c>
       <c r="AL21">
-        <v>0.01743382023</v>
+        <v>0.01743382</v>
       </c>
       <c r="AM21">
         <v>19.6791778</v>
@@ -3259,7 +3259,7 @@
         <v>1.49503139</v>
       </c>
       <c r="AO21">
-        <v>0.4474173785</v>
+        <v>0.447417379</v>
       </c>
     </row>
     <row r="22">
@@ -3298,7 +3298,7 @@
         <v>620.4114056</v>
       </c>
       <c r="I22">
-        <v>-0.1594525648</v>
+        <v>-0.159452565</v>
       </c>
       <c r="J22">
         <v>3.102289955</v>
@@ -3328,13 +3328,13 @@
         <v>5.935100543</v>
       </c>
       <c r="S22">
-        <v>0.8120827881</v>
+        <v>0.812082788</v>
       </c>
       <c r="T22">
         <v>50.74145054</v>
       </c>
       <c r="U22">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V22">
         <v>0.714250804</v>
@@ -3343,28 +3343,28 @@
         <v>19.96640139</v>
       </c>
       <c r="X22">
-        <v>0.02905754353</v>
+        <v>0.029057544</v>
       </c>
       <c r="Y22">
-        <v>0.7896252634000001</v>
+        <v>0.789625263</v>
       </c>
       <c r="Z22">
-        <v>0.02905754353</v>
+        <v>0.029057544</v>
       </c>
       <c r="AA22">
-        <v>0.5584170063</v>
+        <v>0.558417006</v>
       </c>
       <c r="AB22">
         <v>0.715195777</v>
       </c>
       <c r="AC22">
-        <v>0.07442948639999999</v>
+        <v>0.074429486</v>
       </c>
       <c r="AD22">
         <v>89.97403188</v>
       </c>
       <c r="AE22">
-        <v>0.001899650606</v>
+        <v>0.001899651</v>
       </c>
       <c r="AF22">
         <v>26.46854869</v>
@@ -3382,19 +3382,19 @@
         <v>6659.713418</v>
       </c>
       <c r="AK22">
-        <v>0.00152117973</v>
+        <v>0.00152118</v>
       </c>
       <c r="AL22">
-        <v>0.01743769648</v>
+        <v>0.017437696</v>
       </c>
       <c r="AM22">
         <v>64.81045314000001</v>
       </c>
       <c r="AN22">
-        <v>0.8893344066</v>
+        <v>0.889334407</v>
       </c>
       <c r="AO22">
-        <v>0.2436451422</v>
+        <v>0.243645142</v>
       </c>
     </row>
     <row r="23">
@@ -3433,7 +3433,7 @@
         <v>694.0895814</v>
       </c>
       <c r="I23">
-        <v>0.3039321889</v>
+        <v>0.303932189</v>
       </c>
       <c r="J23">
         <v>3.609368521</v>
@@ -3463,37 +3463,37 @@
         <v>6.040427342</v>
       </c>
       <c r="S23">
-        <v>0.7279763794</v>
+        <v>0.727976379</v>
       </c>
       <c r="T23">
         <v>148.7538807</v>
       </c>
       <c r="U23">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V23">
-        <v>0.5363073806999999</v>
+        <v>0.536307381</v>
       </c>
       <c r="W23">
         <v>11.78032782</v>
       </c>
       <c r="X23">
-        <v>0.04320473483</v>
+        <v>0.043204735</v>
       </c>
       <c r="Y23">
-        <v>0.9383660592</v>
+        <v>0.938366059</v>
       </c>
       <c r="Z23">
-        <v>0.04320473483</v>
+        <v>0.043204735</v>
       </c>
       <c r="AA23">
-        <v>0.5722132674</v>
+        <v>0.572213267</v>
       </c>
       <c r="AB23">
-        <v>0.8627112862</v>
+        <v>0.862711286</v>
       </c>
       <c r="AC23">
-        <v>0.07565477298000001</v>
+        <v>0.07565477299999999</v>
       </c>
       <c r="AD23">
         <v>135.017562</v>
@@ -3502,7 +3502,7 @@
         <v>90.01076676</v>
       </c>
       <c r="AF23">
-        <v>0.03067224704</v>
+        <v>0.030672247</v>
       </c>
       <c r="AG23">
         <v>75.06602556999999</v>
@@ -3517,16 +3517,16 @@
         <v>6694.243065</v>
       </c>
       <c r="AK23">
-        <v>0.0007551278542</v>
+        <v>0.000755128</v>
       </c>
       <c r="AL23">
-        <v>0.01792389637</v>
+        <v>0.017923896</v>
       </c>
       <c r="AM23">
         <v>41.61284652</v>
       </c>
       <c r="AN23">
-        <v>0.8893344066</v>
+        <v>0.889334407</v>
       </c>
       <c r="AO23">
         <v>0.5149618</v>
@@ -3568,7 +3568,7 @@
         <v>501.9184038</v>
       </c>
       <c r="I24">
-        <v>0.01162607298</v>
+        <v>0.011626073</v>
       </c>
       <c r="J24">
         <v>3.25887195</v>
@@ -3598,37 +3598,37 @@
         <v>5.405077641</v>
       </c>
       <c r="S24">
-        <v>0.6387970371</v>
+        <v>0.638797037</v>
       </c>
       <c r="T24">
         <v>93.24863053999999</v>
       </c>
       <c r="U24">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V24">
-        <v>0.3149514373</v>
+        <v>0.314951437</v>
       </c>
       <c r="W24">
         <v>4.635522315</v>
       </c>
       <c r="X24">
-        <v>0.02650430829</v>
+        <v>0.026504308</v>
       </c>
       <c r="Y24">
         <v>0.655713474</v>
       </c>
       <c r="Z24">
-        <v>0.02650430829</v>
+        <v>0.026504308</v>
       </c>
       <c r="AA24">
-        <v>0.4371981864</v>
+        <v>0.437198186</v>
       </c>
       <c r="AB24">
-        <v>0.5960041167</v>
+        <v>0.596004117</v>
       </c>
       <c r="AC24">
-        <v>0.05970935723</v>
+        <v>0.059709357</v>
       </c>
       <c r="AD24">
         <v>90.00597908</v>
@@ -3652,10 +3652,10 @@
         <v>6897.993574</v>
       </c>
       <c r="AK24">
-        <v>0.002630952126</v>
+        <v>0.002630952</v>
       </c>
       <c r="AL24">
-        <v>0.01663611613</v>
+        <v>0.016636116</v>
       </c>
       <c r="AM24">
         <v>12.71700486</v>
@@ -3664,7 +3664,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO24">
-        <v>0.2132350694</v>
+        <v>0.213235069</v>
       </c>
     </row>
     <row r="25">
@@ -3703,7 +3703,7 @@
         <v>509.961186</v>
       </c>
       <c r="I25">
-        <v>-0.1418313935</v>
+        <v>-0.141831394</v>
       </c>
       <c r="J25">
         <v>3.522457213</v>
@@ -3733,37 +3733,37 @@
         <v>4.716368922</v>
       </c>
       <c r="S25">
-        <v>0.7823987672</v>
+        <v>0.782398767</v>
       </c>
       <c r="T25">
         <v>86.50627641</v>
       </c>
       <c r="U25">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V25">
-        <v>0.3636285932</v>
+        <v>0.363628593</v>
       </c>
       <c r="W25">
         <v>6.083900295</v>
       </c>
       <c r="X25">
-        <v>0.02455762446</v>
+        <v>0.024557624</v>
       </c>
       <c r="Y25">
-        <v>0.6515959314000001</v>
+        <v>0.651595931</v>
       </c>
       <c r="Z25">
-        <v>0.02455762446</v>
+        <v>0.024557624</v>
       </c>
       <c r="AA25">
-        <v>0.4456409942</v>
+        <v>0.445640994</v>
       </c>
       <c r="AB25">
-        <v>0.5873385035000001</v>
+        <v>0.587338504</v>
       </c>
       <c r="AC25">
-        <v>0.06425742792</v>
+        <v>0.06425742800000001</v>
       </c>
       <c r="AD25">
         <v>44.99817506</v>
@@ -3772,7 +3772,7 @@
         <v>26.48703346</v>
       </c>
       <c r="AF25">
-        <v>0.007795418284</v>
+        <v>0.007795418</v>
       </c>
       <c r="AG25">
         <v>83.65164932</v>
@@ -3787,10 +3787,10 @@
         <v>7943.285787</v>
       </c>
       <c r="AK25">
-        <v>0.001574084128</v>
+        <v>0.001574084</v>
       </c>
       <c r="AL25">
-        <v>0.01703484812</v>
+        <v>0.017034848</v>
       </c>
       <c r="AM25">
         <v>17.7961098</v>
@@ -3838,7 +3838,7 @@
         <v>440.8546733</v>
       </c>
       <c r="I26">
-        <v>0.3155870863</v>
+        <v>0.315587086</v>
       </c>
       <c r="J26">
         <v>4.64621104</v>
@@ -3856,7 +3856,7 @@
         <v>337.3759436</v>
       </c>
       <c r="O26">
-        <v>0.4828109236</v>
+        <v>0.482810924</v>
       </c>
       <c r="P26">
         <v>515.5724259</v>
@@ -3868,37 +3868,37 @@
         <v>5.23457575</v>
       </c>
       <c r="S26">
-        <v>0.8178366825</v>
+        <v>0.817836683</v>
       </c>
       <c r="T26">
         <v>93.74015838</v>
       </c>
       <c r="U26">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V26">
-        <v>0.3427007782</v>
+        <v>0.342700778</v>
       </c>
       <c r="W26">
         <v>5.447045667</v>
       </c>
       <c r="X26">
-        <v>0.0281407183</v>
+        <v>0.028140718</v>
       </c>
       <c r="Y26">
-        <v>0.5437026824</v>
+        <v>0.543702682</v>
       </c>
       <c r="Z26">
-        <v>0.0281407183</v>
+        <v>0.028140718</v>
       </c>
       <c r="AA26">
-        <v>0.3714173394</v>
+        <v>0.371417339</v>
       </c>
       <c r="AB26">
-        <v>0.4926520807</v>
+        <v>0.492652081</v>
       </c>
       <c r="AC26">
-        <v>0.05105060176</v>
+        <v>0.051050602</v>
       </c>
       <c r="AD26">
         <v>90.00585438</v>
@@ -3922,10 +3922,10 @@
         <v>7483.865782</v>
       </c>
       <c r="AK26">
-        <v>0.001852017408</v>
+        <v>0.001852017</v>
       </c>
       <c r="AL26">
-        <v>0.0168855103</v>
+        <v>0.01688551</v>
       </c>
       <c r="AM26">
         <v>16.78921936</v>
@@ -3934,7 +3934,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO26">
-        <v>0.2277336719</v>
+        <v>0.227733672</v>
       </c>
     </row>
     <row r="27">
@@ -3973,7 +3973,7 @@
         <v>700.4567584</v>
       </c>
       <c r="I27">
-        <v>0.1497377386</v>
+        <v>0.149737739</v>
       </c>
       <c r="J27">
         <v>3.988445829</v>
@@ -3991,7 +3991,7 @@
         <v>532.7177045</v>
       </c>
       <c r="O27">
-        <v>0.5352789687</v>
+        <v>0.535278969</v>
       </c>
       <c r="P27">
         <v>844.8970715</v>
@@ -4003,37 +4003,37 @@
         <v>5.373104493</v>
       </c>
       <c r="S27">
-        <v>0.5981096239</v>
+        <v>0.598109624</v>
       </c>
       <c r="T27">
         <v>73.49694091000001</v>
       </c>
       <c r="U27">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V27">
-        <v>0.3992679307</v>
+        <v>0.399267931</v>
       </c>
       <c r="W27">
         <v>7.075261445</v>
       </c>
       <c r="X27">
-        <v>0.04399245058</v>
+        <v>0.043992451</v>
       </c>
       <c r="Y27">
-        <v>0.8889419513</v>
+        <v>0.888941951</v>
       </c>
       <c r="Z27">
-        <v>0.04399245058</v>
+        <v>0.043992451</v>
       </c>
       <c r="AA27">
-        <v>0.5816847745</v>
+        <v>0.581684775</v>
       </c>
       <c r="AB27">
-        <v>0.8034067993</v>
+        <v>0.803406799</v>
       </c>
       <c r="AC27">
-        <v>0.08553515199</v>
+        <v>0.085535152</v>
       </c>
       <c r="AD27">
         <v>90.00765536</v>
@@ -4042,7 +4042,7 @@
         <v>116.4418765</v>
       </c>
       <c r="AF27">
-        <v>0.002838020157</v>
+        <v>0.00283802</v>
       </c>
       <c r="AG27">
         <v>70.34549975</v>
@@ -4057,10 +4057,10 @@
         <v>8735.340389000001</v>
       </c>
       <c r="AK27">
-        <v>0.003375705353</v>
+        <v>0.003375705</v>
       </c>
       <c r="AL27">
-        <v>0.01697801963</v>
+        <v>0.01697802</v>
       </c>
       <c r="AM27">
         <v>24.52109864</v>
@@ -4069,7 +4069,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO27">
-        <v>0.3104949791</v>
+        <v>0.310494979</v>
       </c>
     </row>
     <row r="28">
@@ -4108,7 +4108,7 @@
         <v>742.1566598000001</v>
       </c>
       <c r="I28">
-        <v>-0.02353699093</v>
+        <v>-0.023536991</v>
       </c>
       <c r="J28">
         <v>4.573964834</v>
@@ -4138,37 +4138,37 @@
         <v>5.828312604</v>
       </c>
       <c r="S28">
-        <v>0.9317736326</v>
+        <v>0.931773633</v>
       </c>
       <c r="T28">
         <v>86.7459691</v>
       </c>
       <c r="U28">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V28">
-        <v>0.5944934879</v>
+        <v>0.594493488</v>
       </c>
       <c r="W28">
         <v>14.64351978</v>
       </c>
       <c r="X28">
-        <v>0.04897817346</v>
+        <v>0.048978173</v>
       </c>
       <c r="Y28">
-        <v>0.9184615287</v>
+        <v>0.918461529</v>
       </c>
       <c r="Z28">
-        <v>0.04897817346</v>
+        <v>0.048978173</v>
       </c>
       <c r="AA28">
-        <v>0.5800373808</v>
+        <v>0.580037381</v>
       </c>
       <c r="AB28">
-        <v>0.8218457139000001</v>
+        <v>0.8218457139999999</v>
       </c>
       <c r="AC28">
-        <v>0.09661581482000001</v>
+        <v>0.09661581499999999</v>
       </c>
       <c r="AD28">
         <v>90.00639803999999</v>
@@ -4192,10 +4192,10 @@
         <v>8428.875056999999</v>
       </c>
       <c r="AK28">
-        <v>0.0007247786166</v>
+        <v>0.000724779</v>
       </c>
       <c r="AL28">
-        <v>0.0174068415</v>
+        <v>0.017406842</v>
       </c>
       <c r="AM28">
         <v>48.38877145</v>
@@ -4204,7 +4204,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO28">
-        <v>0.3629778147</v>
+        <v>0.362977815</v>
       </c>
     </row>
     <row r="29">
@@ -4243,7 +4243,7 @@
         <v>515.6712267</v>
       </c>
       <c r="I29">
-        <v>-0.3448691316</v>
+        <v>-0.344869132</v>
       </c>
       <c r="J29">
         <v>5.153260937</v>
@@ -4273,37 +4273,37 @@
         <v>5.140027519</v>
       </c>
       <c r="S29">
-        <v>0.7049336234</v>
+        <v>0.704933623</v>
       </c>
       <c r="T29">
         <v>129.003893</v>
       </c>
       <c r="U29">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V29">
-        <v>0.3455097737</v>
+        <v>0.345509774</v>
       </c>
       <c r="W29">
         <v>5.469556126</v>
       </c>
       <c r="X29">
-        <v>0.03143092061</v>
+        <v>0.031430921</v>
       </c>
       <c r="Y29">
-        <v>0.6310421943</v>
+        <v>0.6310421939999999</v>
       </c>
       <c r="Z29">
-        <v>0.03143092061</v>
+        <v>0.031430921</v>
       </c>
       <c r="AA29">
-        <v>0.3997216557</v>
+        <v>0.399721656</v>
       </c>
       <c r="AB29">
-        <v>0.5619095286</v>
+        <v>0.561909529</v>
       </c>
       <c r="AC29">
-        <v>0.06913266563000001</v>
+        <v>0.069132666</v>
       </c>
       <c r="AD29">
         <v>90.03107985</v>
@@ -4327,10 +4327,10 @@
         <v>8313.804614999999</v>
       </c>
       <c r="AK29">
-        <v>0.001176662404</v>
+        <v>0.001176662</v>
       </c>
       <c r="AL29">
-        <v>0.01752365669</v>
+        <v>0.017523657</v>
       </c>
       <c r="AM29">
         <v>16.91495435</v>
@@ -4339,7 +4339,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO29">
-        <v>0.3512691556</v>
+        <v>0.351269156</v>
       </c>
     </row>
     <row r="30">
@@ -4396,7 +4396,7 @@
         <v>329.3369465</v>
       </c>
       <c r="O30">
-        <v>0.06969595141</v>
+        <v>0.06969595100000001</v>
       </c>
       <c r="P30">
         <v>503.5606015</v>
@@ -4408,37 +4408,37 @@
         <v>4.971890066</v>
       </c>
       <c r="S30">
-        <v>0.7720100087</v>
+        <v>0.7720100090000001</v>
       </c>
       <c r="T30">
         <v>93.75175869</v>
       </c>
       <c r="U30">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V30">
-        <v>0.3512310021</v>
+        <v>0.351231002</v>
       </c>
       <c r="W30">
         <v>5.674495731</v>
       </c>
       <c r="X30">
-        <v>0.02897027389</v>
+        <v>0.028970274</v>
       </c>
       <c r="Y30">
-        <v>0.5325616726</v>
+        <v>0.532561673</v>
       </c>
       <c r="Z30">
-        <v>0.02897027389</v>
+        <v>0.028970274</v>
       </c>
       <c r="AA30">
-        <v>0.3579514914</v>
+        <v>0.357951491</v>
       </c>
       <c r="AB30">
-        <v>0.4815342887</v>
+        <v>0.481534289</v>
       </c>
       <c r="AC30">
-        <v>0.05102738393</v>
+        <v>0.051027384</v>
       </c>
       <c r="AD30">
         <v>89.99550463</v>
@@ -4462,10 +4462,10 @@
         <v>7270.008905</v>
       </c>
       <c r="AK30">
-        <v>0.001619891832</v>
+        <v>0.001619892</v>
       </c>
       <c r="AL30">
-        <v>0.01700721273</v>
+        <v>0.017007213</v>
       </c>
       <c r="AM30">
         <v>17.75026635</v>
@@ -4474,7 +4474,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO30">
-        <v>0.2292642696</v>
+        <v>0.22926427</v>
       </c>
     </row>
     <row r="31">
@@ -4513,7 +4513,7 @@
         <v>615.7832499</v>
       </c>
       <c r="I31">
-        <v>0.1433740748</v>
+        <v>0.143374075</v>
       </c>
       <c r="J31">
         <v>3.698901556</v>
@@ -4549,31 +4549,31 @@
         <v>119.7517713</v>
       </c>
       <c r="U31">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V31">
-        <v>0.3743342781</v>
+        <v>0.374334278</v>
       </c>
       <c r="W31">
         <v>6.288912683</v>
       </c>
       <c r="X31">
-        <v>0.03493160126</v>
+        <v>0.034931601</v>
       </c>
       <c r="Y31">
-        <v>0.8107492462</v>
+        <v>0.810749246</v>
       </c>
       <c r="Z31">
-        <v>0.03493160126</v>
+        <v>0.034931601</v>
       </c>
       <c r="AA31">
-        <v>0.5161942621</v>
+        <v>0.516194262</v>
       </c>
       <c r="AB31">
-        <v>0.7392907096</v>
+        <v>0.73929071</v>
       </c>
       <c r="AC31">
-        <v>0.07145853659</v>
+        <v>0.071458537</v>
       </c>
       <c r="AD31">
         <v>134.9816176</v>
@@ -4597,10 +4597,10 @@
         <v>8260.064982</v>
       </c>
       <c r="AK31">
-        <v>0.002286015131</v>
+        <v>0.002286015</v>
       </c>
       <c r="AL31">
-        <v>0.01679945722</v>
+        <v>0.016799457</v>
       </c>
       <c r="AM31">
         <v>20.96166202</v>
@@ -4609,7 +4609,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO31">
-        <v>0.2793546341</v>
+        <v>0.279354634</v>
       </c>
     </row>
     <row r="32">
@@ -4648,7 +4648,7 @@
         <v>728.8004426</v>
       </c>
       <c r="I32">
-        <v>-0.1779885563</v>
+        <v>-0.177988556</v>
       </c>
       <c r="J32">
         <v>4.866987085</v>
@@ -4678,43 +4678,43 @@
         <v>5.81351224</v>
       </c>
       <c r="S32">
-        <v>0.8410800042</v>
+        <v>0.841080004</v>
       </c>
       <c r="T32">
         <v>86.49498733</v>
       </c>
       <c r="U32">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V32">
-        <v>0.4168597353</v>
+        <v>0.416859735</v>
       </c>
       <c r="W32">
         <v>7.594139273</v>
       </c>
       <c r="X32">
-        <v>0.05116827374</v>
+        <v>0.051168274</v>
       </c>
       <c r="Y32">
-        <v>0.8651508479</v>
+        <v>0.865150848</v>
       </c>
       <c r="Z32">
-        <v>0.05116827374</v>
+        <v>0.051168274</v>
       </c>
       <c r="AA32">
-        <v>0.5360602087</v>
+        <v>0.536060209</v>
       </c>
       <c r="AB32">
-        <v>0.7600813745</v>
+        <v>0.7600813749999999</v>
       </c>
       <c r="AC32">
-        <v>0.1050694733</v>
+        <v>0.105069473</v>
       </c>
       <c r="AD32">
         <v>89.99984895999999</v>
       </c>
       <c r="AE32">
-        <v>0.008306653793</v>
+        <v>0.008306654</v>
       </c>
       <c r="AF32">
         <v>134.9948709</v>
@@ -4732,10 +4732,10 @@
         <v>8104.97664</v>
       </c>
       <c r="AK32">
-        <v>0.001028466988</v>
+        <v>0.001028467</v>
       </c>
       <c r="AL32">
-        <v>0.01724745342</v>
+        <v>0.017247453</v>
       </c>
       <c r="AM32">
         <v>26.55289353</v>
@@ -4744,7 +4744,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO32">
-        <v>0.3971246619</v>
+        <v>0.397124662</v>
       </c>
     </row>
     <row r="33">
@@ -4783,7 +4783,7 @@
         <v>523.2467327000001</v>
       </c>
       <c r="I33">
-        <v>-0.2493768572</v>
+        <v>-0.249376857</v>
       </c>
       <c r="J33">
         <v>4.434631953</v>
@@ -4813,37 +4813,37 @@
         <v>5.374707515</v>
       </c>
       <c r="S33">
-        <v>0.5931511648</v>
+        <v>0.593151165</v>
       </c>
       <c r="T33">
         <v>86.74687109</v>
       </c>
       <c r="U33">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V33">
-        <v>0.3728543142</v>
+        <v>0.372854314</v>
       </c>
       <c r="W33">
         <v>6.323570483</v>
       </c>
       <c r="X33">
-        <v>0.0309126899</v>
+        <v>0.03091269</v>
       </c>
       <c r="Y33">
-        <v>0.6469359223</v>
+        <v>0.6469359220000001</v>
       </c>
       <c r="Z33">
-        <v>0.0309126899</v>
+        <v>0.03091269</v>
       </c>
       <c r="AA33">
-        <v>0.4137117508</v>
+        <v>0.413711751</v>
       </c>
       <c r="AB33">
-        <v>0.5759558842</v>
+        <v>0.575955884</v>
       </c>
       <c r="AC33">
-        <v>0.07098003808</v>
+        <v>0.070980038</v>
       </c>
       <c r="AD33">
         <v>89.99320978999999</v>
@@ -4867,10 +4867,10 @@
         <v>7121.622208</v>
       </c>
       <c r="AK33">
-        <v>0.002216719769</v>
+        <v>0.00221672</v>
       </c>
       <c r="AL33">
-        <v>0.01723768321</v>
+        <v>0.017237683</v>
       </c>
       <c r="AM33">
         <v>19.87722505</v>
@@ -4879,7 +4879,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO33">
-        <v>0.3198283716</v>
+        <v>0.319828372</v>
       </c>
     </row>
     <row r="34">
@@ -4918,7 +4918,7 @@
         <v>473.7795641</v>
       </c>
       <c r="I34">
-        <v>-0.2979859558</v>
+        <v>-0.297985956</v>
       </c>
       <c r="J34">
         <v>4.282493802</v>
@@ -4948,37 +4948,37 @@
         <v>4.868315564</v>
       </c>
       <c r="S34">
-        <v>0.6515923173</v>
+        <v>0.651592317</v>
       </c>
       <c r="T34">
         <v>86.74915917</v>
       </c>
       <c r="U34">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V34">
-        <v>0.3409079106</v>
+        <v>0.340907911</v>
       </c>
       <c r="W34">
         <v>5.366702015</v>
       </c>
       <c r="X34">
-        <v>0.02494600301</v>
+        <v>0.024946003</v>
       </c>
       <c r="Y34">
-        <v>0.5897647824</v>
+        <v>0.589764782</v>
       </c>
       <c r="Z34">
-        <v>0.02494600301</v>
+        <v>0.024946003</v>
       </c>
       <c r="AA34">
-        <v>0.3919227229</v>
+        <v>0.391922723</v>
       </c>
       <c r="AB34">
-        <v>0.5257117575</v>
+        <v>0.525711758</v>
       </c>
       <c r="AC34">
-        <v>0.06405302488</v>
+        <v>0.064053025</v>
       </c>
       <c r="AD34">
         <v>89.99149339</v>
@@ -5002,10 +5002,10 @@
         <v>8292.710837000001</v>
       </c>
       <c r="AK34">
-        <v>0.002227322249</v>
+        <v>0.002227322</v>
       </c>
       <c r="AL34">
-        <v>0.0169068511</v>
+        <v>0.016906851</v>
       </c>
       <c r="AM34">
         <v>16.90755897</v>
@@ -5053,7 +5053,7 @@
         <v>488.9681076</v>
       </c>
       <c r="I35">
-        <v>-0.08535257407999999</v>
+        <v>-0.085352574</v>
       </c>
       <c r="J35">
         <v>3.360738022</v>
@@ -5083,37 +5083,37 @@
         <v>4.824586328</v>
       </c>
       <c r="S35">
-        <v>0.6595370939</v>
+        <v>0.659537094</v>
       </c>
       <c r="T35">
         <v>93.74600368</v>
       </c>
       <c r="U35">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V35">
-        <v>0.3668328875</v>
+        <v>0.366832888</v>
       </c>
       <c r="W35">
         <v>6.169645666</v>
       </c>
       <c r="X35">
-        <v>0.02374231703</v>
+        <v>0.023742317</v>
       </c>
       <c r="Y35">
-        <v>0.6401023852</v>
+        <v>0.6401023850000001</v>
       </c>
       <c r="Z35">
-        <v>0.02374231703</v>
+        <v>0.023742317</v>
       </c>
       <c r="AA35">
-        <v>0.4207073027</v>
+        <v>0.420707303</v>
       </c>
       <c r="AB35">
-        <v>0.5781193135</v>
+        <v>0.5781193140000001</v>
       </c>
       <c r="AC35">
-        <v>0.06198307171</v>
+        <v>0.061983072</v>
       </c>
       <c r="AD35">
         <v>134.9997648</v>
@@ -5137,10 +5137,10 @@
         <v>8549.450559000001</v>
       </c>
       <c r="AK35">
-        <v>0.002655500418</v>
+        <v>0.0026555</v>
       </c>
       <c r="AL35">
-        <v>0.0168811383</v>
+        <v>0.016881138</v>
       </c>
       <c r="AM35">
         <v>19.96053253</v>
@@ -5149,7 +5149,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO35">
-        <v>0.1903924826</v>
+        <v>0.190392483</v>
       </c>
     </row>
     <row r="36">
@@ -5188,7 +5188,7 @@
         <v>532.9491592000001</v>
       </c>
       <c r="I36">
-        <v>0.08322342079</v>
+        <v>0.08322342100000001</v>
       </c>
       <c r="J36">
         <v>3.399470241</v>
@@ -5224,31 +5224,31 @@
         <v>81.75323211</v>
       </c>
       <c r="U36">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V36">
-        <v>0.3575162477</v>
+        <v>0.357516248</v>
       </c>
       <c r="W36">
         <v>5.82554151</v>
       </c>
       <c r="X36">
-        <v>0.02976094447</v>
+        <v>0.029760944</v>
       </c>
       <c r="Y36">
-        <v>0.6948247384</v>
+        <v>0.694824738</v>
       </c>
       <c r="Z36">
-        <v>0.02976094447</v>
+        <v>0.029760944</v>
       </c>
       <c r="AA36">
-        <v>0.4724639668</v>
+        <v>0.472463967</v>
       </c>
       <c r="AB36">
-        <v>0.6354918211</v>
+        <v>0.635491821</v>
       </c>
       <c r="AC36">
-        <v>0.05933291729</v>
+        <v>0.059332917</v>
       </c>
       <c r="AD36">
         <v>89.99727976</v>
@@ -5272,10 +5272,10 @@
         <v>7880.072409</v>
       </c>
       <c r="AK36">
-        <v>0.001567656591</v>
+        <v>0.001567657</v>
       </c>
       <c r="AL36">
-        <v>0.0170352735</v>
+        <v>0.017035274</v>
       </c>
       <c r="AM36">
         <v>19.4607995</v>
@@ -5284,7 +5284,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO36">
-        <v>0.3056000886</v>
+        <v>0.305600089</v>
       </c>
     </row>
     <row r="37">
@@ -5323,7 +5323,7 @@
         <v>638.3373587</v>
       </c>
       <c r="I37">
-        <v>0.2188257208</v>
+        <v>0.218825721</v>
       </c>
       <c r="J37">
         <v>3.067112333</v>
@@ -5353,37 +5353,37 @@
         <v>5.69470673</v>
       </c>
       <c r="S37">
-        <v>0.8022487577</v>
+        <v>0.802248758</v>
       </c>
       <c r="T37">
         <v>98.26071595000001</v>
       </c>
       <c r="U37">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V37">
-        <v>0.3888184957</v>
+        <v>0.388818496</v>
       </c>
       <c r="W37">
         <v>6.879844179</v>
       </c>
       <c r="X37">
-        <v>0.03581227078</v>
+        <v>0.035812271</v>
       </c>
       <c r="Y37">
-        <v>0.8673011336000001</v>
+        <v>0.867301134</v>
       </c>
       <c r="Z37">
-        <v>0.03581227078</v>
+        <v>0.035812271</v>
       </c>
       <c r="AA37">
-        <v>0.5667961619</v>
+        <v>0.566796162</v>
       </c>
       <c r="AB37">
-        <v>0.8011138964</v>
+        <v>0.801113896</v>
       </c>
       <c r="AC37">
-        <v>0.06618723723</v>
+        <v>0.066187237</v>
       </c>
       <c r="AD37">
         <v>89.99985174</v>
@@ -5407,10 +5407,10 @@
         <v>7741.515482</v>
       </c>
       <c r="AK37">
-        <v>0.001640228437</v>
+        <v>0.001640228</v>
       </c>
       <c r="AL37">
-        <v>0.01710387232</v>
+        <v>0.017103872</v>
       </c>
       <c r="AM37">
         <v>20.83204398</v>
@@ -5419,7 +5419,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO37">
-        <v>0.1916166835</v>
+        <v>0.191616684</v>
       </c>
     </row>
     <row r="38">
@@ -5458,7 +5458,7 @@
         <v>524.1161681</v>
       </c>
       <c r="I38">
-        <v>0.1537915592</v>
+        <v>0.153791559</v>
       </c>
       <c r="J38">
         <v>3.384159379</v>
@@ -5488,37 +5488,37 @@
         <v>5.15389965</v>
       </c>
       <c r="S38">
-        <v>0.7779167388</v>
+        <v>0.777916739</v>
       </c>
       <c r="T38">
         <v>35.99358031</v>
       </c>
       <c r="U38">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V38">
-        <v>0.4043116086</v>
+        <v>0.404311609</v>
       </c>
       <c r="W38">
         <v>7.394706621</v>
       </c>
       <c r="X38">
-        <v>0.02938038872</v>
+        <v>0.029380389</v>
       </c>
       <c r="Y38">
-        <v>0.6844853279000001</v>
+        <v>0.6844853279999999</v>
       </c>
       <c r="Z38">
-        <v>0.02938038872</v>
+        <v>0.029380389</v>
       </c>
       <c r="AA38">
-        <v>0.4634569317</v>
+        <v>0.463456932</v>
       </c>
       <c r="AB38">
-        <v>0.6274269386</v>
+        <v>0.627426939</v>
       </c>
       <c r="AC38">
-        <v>0.05705838924</v>
+        <v>0.057058389</v>
       </c>
       <c r="AD38">
         <v>179.9882456</v>
@@ -5542,10 +5542,10 @@
         <v>8580.190863</v>
       </c>
       <c r="AK38">
-        <v>0.001057781381</v>
+        <v>0.001057781</v>
       </c>
       <c r="AL38">
-        <v>0.01765157793</v>
+        <v>0.017651578</v>
       </c>
       <c r="AM38">
         <v>25.95923489</v>
@@ -5554,7 +5554,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO38">
-        <v>0.2469117038</v>
+        <v>0.246911704</v>
       </c>
     </row>
     <row r="39">
@@ -5593,7 +5593,7 @@
         <v>524.5376113</v>
       </c>
       <c r="I39">
-        <v>0.5696771959</v>
+        <v>0.569677196</v>
       </c>
       <c r="J39">
         <v>4.807428613</v>
@@ -5623,37 +5623,37 @@
         <v>5.75673384</v>
       </c>
       <c r="S39">
-        <v>0.9129652908</v>
+        <v>0.912965291</v>
       </c>
       <c r="T39">
         <v>28.50829381</v>
       </c>
       <c r="U39">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V39">
-        <v>0.3505137962</v>
+        <v>0.350513796</v>
       </c>
       <c r="W39">
         <v>5.601959522</v>
       </c>
       <c r="X39">
-        <v>0.03960906451</v>
+        <v>0.039609065</v>
       </c>
       <c r="Y39">
-        <v>0.6372708199</v>
+        <v>0.63727082</v>
       </c>
       <c r="Z39">
-        <v>0.03960906451</v>
+        <v>0.039609065</v>
       </c>
       <c r="AA39">
-        <v>0.4263834951</v>
+        <v>0.426383495</v>
       </c>
       <c r="AB39">
-        <v>0.5812592188</v>
+        <v>0.581259219</v>
       </c>
       <c r="AC39">
-        <v>0.0560116011</v>
+        <v>0.056011601</v>
       </c>
       <c r="AD39">
         <v>44.99537972</v>
@@ -5662,7 +5662,7 @@
         <v>89.99052301</v>
       </c>
       <c r="AF39">
-        <v>0.005992967951</v>
+        <v>0.005992968</v>
       </c>
       <c r="AG39">
         <v>88.48560938</v>
@@ -5677,10 +5677,10 @@
         <v>8142.471146</v>
       </c>
       <c r="AK39">
-        <v>0.001375051449</v>
+        <v>0.001375051</v>
       </c>
       <c r="AL39">
-        <v>0.0178410465</v>
+        <v>0.017841047</v>
       </c>
       <c r="AM39">
         <v>18.47639836</v>
@@ -5689,7 +5689,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO39">
-        <v>0.5159941061</v>
+        <v>0.515994106</v>
       </c>
     </row>
     <row r="40">
@@ -5758,37 +5758,37 @@
         <v>5.553216105</v>
       </c>
       <c r="S40">
-        <v>0.8281898434</v>
+        <v>0.828189843</v>
       </c>
       <c r="T40">
         <v>151.7487401</v>
       </c>
       <c r="U40">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V40">
-        <v>0.3671344635</v>
+        <v>0.367134464</v>
       </c>
       <c r="W40">
         <v>6.145770503</v>
       </c>
       <c r="X40">
-        <v>0.03052807986</v>
+        <v>0.03052808</v>
       </c>
       <c r="Y40">
-        <v>0.7135822596</v>
+        <v>0.71358226</v>
       </c>
       <c r="Z40">
-        <v>0.03052807986</v>
+        <v>0.03052808</v>
       </c>
       <c r="AA40">
-        <v>0.4657319329</v>
+        <v>0.465731933</v>
       </c>
       <c r="AB40">
-        <v>0.6537585074</v>
+        <v>0.653758507</v>
       </c>
       <c r="AC40">
-        <v>0.05982375224</v>
+        <v>0.059823752</v>
       </c>
       <c r="AD40">
         <v>44.9843084</v>
@@ -5812,10 +5812,10 @@
         <v>8211.845914</v>
       </c>
       <c r="AK40">
-        <v>0.0001784002546</v>
+        <v>0.0001784</v>
       </c>
       <c r="AL40">
-        <v>0.01771201069</v>
+        <v>0.017712011</v>
       </c>
       <c r="AM40">
         <v>19.43860115</v>
@@ -5824,7 +5824,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO40">
-        <v>0.2369683093</v>
+        <v>0.236968309</v>
       </c>
     </row>
     <row r="41">
@@ -5863,7 +5863,7 @@
         <v>684.2428391</v>
       </c>
       <c r="I41">
-        <v>0.1506982072</v>
+        <v>0.150698207</v>
       </c>
       <c r="J41">
         <v>2.990583612</v>
@@ -5893,37 +5893,37 @@
         <v>5.829542482</v>
       </c>
       <c r="S41">
-        <v>0.8431730388000001</v>
+        <v>0.843173039</v>
       </c>
       <c r="T41">
         <v>93.26049132999999</v>
       </c>
       <c r="U41">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V41">
-        <v>0.4197233536</v>
+        <v>0.419723354</v>
       </c>
       <c r="W41">
         <v>7.924443727</v>
       </c>
       <c r="X41">
-        <v>0.03658621536</v>
+        <v>0.036586215</v>
       </c>
       <c r="Y41">
-        <v>0.9209007885</v>
+        <v>0.9209007890000001</v>
       </c>
       <c r="Z41">
-        <v>0.03658621536</v>
+        <v>0.036586215</v>
       </c>
       <c r="AA41">
-        <v>0.6096890835</v>
+        <v>0.609689084</v>
       </c>
       <c r="AB41">
-        <v>0.8468600226</v>
+        <v>0.846860023</v>
       </c>
       <c r="AC41">
-        <v>0.07404076582000001</v>
+        <v>0.07404076599999999</v>
       </c>
       <c r="AD41">
         <v>135.0113827</v>
@@ -5947,10 +5947,10 @@
         <v>9044.194199</v>
       </c>
       <c r="AK41">
-        <v>0.00131835554</v>
+        <v>0.001318356</v>
       </c>
       <c r="AL41">
-        <v>0.01723214849</v>
+        <v>0.017232148</v>
       </c>
       <c r="AM41">
         <v>22.63907348</v>
@@ -5959,7 +5959,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO41">
-        <v>0.1257311141</v>
+        <v>0.125731114</v>
       </c>
     </row>
     <row r="42">
@@ -5998,7 +5998,7 @@
         <v>588.4516861</v>
       </c>
       <c r="I42">
-        <v>0.3121030499</v>
+        <v>0.31210305</v>
       </c>
       <c r="J42">
         <v>3.30542193</v>
@@ -6028,37 +6028,37 @@
         <v>5.46888513</v>
       </c>
       <c r="S42">
-        <v>0.8114546213</v>
+        <v>0.811454621</v>
       </c>
       <c r="T42">
         <v>12.75117744</v>
       </c>
       <c r="U42">
-        <v>0.4187143393</v>
+        <v>0.418714339</v>
       </c>
       <c r="V42">
-        <v>0.3581520446</v>
+        <v>0.358152045</v>
       </c>
       <c r="W42">
         <v>5.845710443</v>
       </c>
       <c r="X42">
-        <v>0.03541937557</v>
+        <v>0.035419376</v>
       </c>
       <c r="Y42">
-        <v>0.7906447351</v>
+        <v>0.790644735</v>
       </c>
       <c r="Z42">
-        <v>0.03541937557</v>
+        <v>0.035419376</v>
       </c>
       <c r="AA42">
         <v>0.50457176</v>
       </c>
       <c r="AB42">
-        <v>0.7277112229</v>
+        <v>0.727711223</v>
       </c>
       <c r="AC42">
-        <v>0.06293351219</v>
+        <v>0.062933512</v>
       </c>
       <c r="AD42">
         <v>27.25845449</v>
@@ -6067,7 +6067,7 @@
         <v>45.69686284</v>
       </c>
       <c r="AF42">
-        <v>0.00531276875</v>
+        <v>0.005312769</v>
       </c>
       <c r="AG42">
         <v>81.39797646</v>
@@ -6082,10 +6082,10 @@
         <v>9711.901282999999</v>
       </c>
       <c r="AK42">
-        <v>0.0002990006263</v>
+        <v>0.000299001</v>
       </c>
       <c r="AL42">
-        <v>0.01752425386</v>
+        <v>0.017524254</v>
       </c>
       <c r="AM42">
         <v>18.74536075</v>
@@ -6094,7 +6094,7 @@
         <v>1.129141677</v>
       </c>
       <c r="AO42">
-        <v>0.2146397734</v>
+        <v>0.214639773</v>
       </c>
     </row>
     <row r="43">
@@ -6133,7 +6133,7 @@
         <v>551.3157571</v>
       </c>
       <c r="I43">
-        <v>-0.1157537166</v>
+        <v>-0.115753717</v>
       </c>
       <c r="J43">
         <v>3.130713154</v>
@@ -6163,37 +6163,37 @@
         <v>5.308047039</v>
       </c>
       <c r="S43">
-        <v>0.5558046223000001</v>
+        <v>0.555804622</v>
       </c>
       <c r="T43">
         <v>50.98882622</v>
       </c>
       <c r="U43">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V43">
-        <v>0.3562756325</v>
+        <v>0.356275633</v>
       </c>
       <c r="W43">
         <v>5.889797839</v>
       </c>
       <c r="X43">
-        <v>0.02625724378</v>
+        <v>0.026257244</v>
       </c>
       <c r="Y43">
-        <v>0.7250933888</v>
+        <v>0.725093389</v>
       </c>
       <c r="Z43">
-        <v>0.02625724378</v>
+        <v>0.026257244</v>
       </c>
       <c r="AA43">
-        <v>0.4835653102</v>
+        <v>0.48356531</v>
       </c>
       <c r="AB43">
         <v>0.655066844</v>
       </c>
       <c r="AC43">
-        <v>0.07002654474</v>
+        <v>0.070026545</v>
       </c>
       <c r="AD43">
         <v>45.00965739</v>
@@ -6202,7 +6202,7 @@
         <v>89.99979691999999</v>
       </c>
       <c r="AF43">
-        <v>0.00884178111</v>
+        <v>0.008841781</v>
       </c>
       <c r="AG43">
         <v>64.09347944</v>
@@ -6217,10 +6217,10 @@
         <v>8139.808622</v>
       </c>
       <c r="AK43">
-        <v>0.002404656823</v>
+        <v>0.002404657</v>
       </c>
       <c r="AL43">
-        <v>0.01732209526</v>
+        <v>0.017322095</v>
       </c>
       <c r="AM43">
         <v>16.72983538</v>
@@ -6229,7 +6229,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO43">
-        <v>0.1826235645</v>
+        <v>0.182623565</v>
       </c>
     </row>
     <row r="44">
@@ -6268,7 +6268,7 @@
         <v>585.5325658</v>
       </c>
       <c r="I44">
-        <v>0.3480703235</v>
+        <v>0.348070324</v>
       </c>
       <c r="J44">
         <v>3.802934238</v>
@@ -6298,43 +6298,43 @@
         <v>5.095130561</v>
       </c>
       <c r="S44">
-        <v>0.5447976481</v>
+        <v>0.544797648</v>
       </c>
       <c r="T44">
         <v>36.2486234</v>
       </c>
       <c r="U44">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V44">
-        <v>0.3685085482</v>
+        <v>0.368508548</v>
       </c>
       <c r="W44">
         <v>6.158966556</v>
       </c>
       <c r="X44">
-        <v>0.04009628135</v>
+        <v>0.040096281</v>
       </c>
       <c r="Y44">
-        <v>0.7818762913</v>
+        <v>0.781876291</v>
       </c>
       <c r="Z44">
-        <v>0.04009628135</v>
+        <v>0.040096281</v>
       </c>
       <c r="AA44">
-        <v>0.4839401497</v>
+        <v>0.48394015</v>
       </c>
       <c r="AB44">
-        <v>0.7191937639</v>
+        <v>0.719193764</v>
       </c>
       <c r="AC44">
-        <v>0.06268252735</v>
+        <v>0.062682527</v>
       </c>
       <c r="AD44">
         <v>134.9898477</v>
       </c>
       <c r="AE44">
-        <v>0.009506207628</v>
+        <v>0.009506208</v>
       </c>
       <c r="AF44">
         <v>26.47225109</v>
@@ -6352,10 +6352,10 @@
         <v>8319.43773</v>
       </c>
       <c r="AK44">
-        <v>0.003144669483</v>
+        <v>0.003144669</v>
       </c>
       <c r="AL44">
-        <v>0.01834850337</v>
+        <v>0.018348503</v>
       </c>
       <c r="AM44">
         <v>20.25456374</v>
@@ -6403,7 +6403,7 @@
         <v>462.9315333</v>
       </c>
       <c r="I45">
-        <v>0.03748129312</v>
+        <v>0.037481293</v>
       </c>
       <c r="J45">
         <v>3.350299542</v>
@@ -6439,37 +6439,37 @@
         <v>8.512598153000001</v>
       </c>
       <c r="U45">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V45">
-        <v>0.3322304884</v>
+        <v>0.332230488</v>
       </c>
       <c r="W45">
         <v>5.163046513</v>
       </c>
       <c r="X45">
-        <v>0.02478939859</v>
+        <v>0.024789399</v>
       </c>
       <c r="Y45">
-        <v>0.6172552079</v>
+        <v>0.617255208</v>
       </c>
       <c r="Z45">
-        <v>0.02478939859</v>
+        <v>0.024789399</v>
       </c>
       <c r="AA45">
-        <v>0.3960208026</v>
+        <v>0.396020803</v>
       </c>
       <c r="AB45">
-        <v>0.5644050551999999</v>
+        <v>0.564405055</v>
       </c>
       <c r="AC45">
-        <v>0.05285015266</v>
+        <v>0.052850153</v>
       </c>
       <c r="AD45">
         <v>135.0475337</v>
       </c>
       <c r="AE45">
-        <v>0.008561733261</v>
+        <v>0.008561733</v>
       </c>
       <c r="AF45">
         <v>56.22895163</v>
@@ -6487,10 +6487,10 @@
         <v>6827.805954</v>
       </c>
       <c r="AK45">
-        <v>0.0009626586932</v>
+        <v>0.000962659</v>
       </c>
       <c r="AL45">
-        <v>0.01780371462</v>
+        <v>0.017803715</v>
       </c>
       <c r="AM45">
         <v>14.63001114</v>
@@ -6499,7 +6499,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO45">
-        <v>0.1489784002</v>
+        <v>0.1489784</v>
       </c>
     </row>
     <row r="46">
@@ -6538,7 +6538,7 @@
         <v>591.962143</v>
       </c>
       <c r="I46">
-        <v>0.1911905825</v>
+        <v>0.191190583</v>
       </c>
       <c r="J46">
         <v>3.958394892</v>
@@ -6574,31 +6574,31 @@
         <v>148.7513097</v>
       </c>
       <c r="U46">
-        <v>0.4187143393</v>
+        <v>0.418714339</v>
       </c>
       <c r="V46">
-        <v>0.3546843476</v>
+        <v>0.354684348</v>
       </c>
       <c r="W46">
         <v>5.741260877</v>
       </c>
       <c r="X46">
-        <v>0.03805280405</v>
+        <v>0.038052804</v>
       </c>
       <c r="Y46">
-        <v>0.7682531523</v>
+        <v>0.768253152</v>
       </c>
       <c r="Z46">
-        <v>0.03805280405</v>
+        <v>0.038052804</v>
       </c>
       <c r="AA46">
-        <v>0.4815035301</v>
+        <v>0.48150353</v>
       </c>
       <c r="AB46">
-        <v>0.6994110132</v>
+        <v>0.699411013</v>
       </c>
       <c r="AC46">
-        <v>0.06884213916</v>
+        <v>0.068842139</v>
       </c>
       <c r="AD46">
         <v>152.7190893</v>
@@ -6622,10 +6622,10 @@
         <v>8809.064363</v>
       </c>
       <c r="AK46">
-        <v>0.001225667241</v>
+        <v>0.001225667</v>
       </c>
       <c r="AL46">
-        <v>0.01730003264</v>
+        <v>0.017300033</v>
       </c>
       <c r="AM46">
         <v>18.51823915</v>
@@ -6634,7 +6634,7 @@
         <v>1.204526773</v>
       </c>
       <c r="AO46">
-        <v>0.2439010544</v>
+        <v>0.243901054</v>
       </c>
     </row>
     <row r="47">
@@ -6691,7 +6691,7 @@
         <v>502.2451101</v>
       </c>
       <c r="O47">
-        <v>0.6328987361</v>
+        <v>0.632898736</v>
       </c>
       <c r="P47">
         <v>771.7290972</v>
@@ -6703,37 +6703,37 @@
         <v>6.401168813</v>
       </c>
       <c r="S47">
-        <v>0.7742813181</v>
+        <v>0.774281318</v>
       </c>
       <c r="T47">
         <v>50.75030135</v>
       </c>
       <c r="U47">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V47">
-        <v>0.4163004534</v>
+        <v>0.416300453</v>
       </c>
       <c r="W47">
         <v>7.68186065</v>
       </c>
       <c r="X47">
-        <v>0.04148572031</v>
+        <v>0.04148572</v>
       </c>
       <c r="Y47">
-        <v>0.8131742913</v>
+        <v>0.813174291</v>
       </c>
       <c r="Z47">
-        <v>0.04148572031</v>
+        <v>0.04148572</v>
       </c>
       <c r="AA47">
-        <v>0.5490450554</v>
+        <v>0.549045055</v>
       </c>
       <c r="AB47">
-        <v>0.7387360238</v>
+        <v>0.738736024</v>
       </c>
       <c r="AC47">
-        <v>0.07443826745</v>
+        <v>0.074438267</v>
       </c>
       <c r="AD47">
         <v>44.96467987</v>
@@ -6757,10 +6757,10 @@
         <v>8391.570460000001</v>
       </c>
       <c r="AK47">
-        <v>0.000774373068</v>
+        <v>0.000774373</v>
       </c>
       <c r="AL47">
-        <v>0.01742623706</v>
+        <v>0.017426237</v>
       </c>
       <c r="AM47">
         <v>25.45691301</v>
@@ -6769,7 +6769,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO47">
-        <v>0.2639051363</v>
+        <v>0.263905136</v>
       </c>
     </row>
     <row r="48">
@@ -6808,7 +6808,7 @@
         <v>525.4680747</v>
       </c>
       <c r="I48">
-        <v>0.3928235512</v>
+        <v>0.392823551</v>
       </c>
       <c r="J48">
         <v>3.524110682</v>
@@ -6838,37 +6838,37 @@
         <v>5.525380873</v>
       </c>
       <c r="S48">
-        <v>0.7744444056000001</v>
+        <v>0.774444406</v>
       </c>
       <c r="T48">
         <v>114.7474355</v>
       </c>
       <c r="U48">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V48">
-        <v>0.3734981758</v>
+        <v>0.373498176</v>
       </c>
       <c r="W48">
         <v>6.34685705</v>
       </c>
       <c r="X48">
-        <v>0.03448307574</v>
+        <v>0.034483076</v>
       </c>
       <c r="Y48">
-        <v>0.6798962254000001</v>
+        <v>0.679896225</v>
       </c>
       <c r="Z48">
-        <v>0.03448307574</v>
+        <v>0.034483076</v>
       </c>
       <c r="AA48">
-        <v>0.4643473387</v>
+        <v>0.464347339</v>
       </c>
       <c r="AB48">
-        <v>0.6301364926</v>
+        <v>0.630136493</v>
       </c>
       <c r="AC48">
-        <v>0.04975973284</v>
+        <v>0.049759733</v>
       </c>
       <c r="AD48">
         <v>89.99617205</v>
@@ -6892,10 +6892,10 @@
         <v>8732.169253</v>
       </c>
       <c r="AK48">
-        <v>0.0009258252545</v>
+        <v>0.000925825</v>
       </c>
       <c r="AL48">
-        <v>0.01794171014</v>
+        <v>0.01794171</v>
       </c>
       <c r="AM48">
         <v>21.26196646</v>
@@ -6904,7 +6904,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO48">
-        <v>0.1810745606</v>
+        <v>0.181074561</v>
       </c>
     </row>
     <row r="49">
@@ -6973,37 +6973,37 @@
         <v>5.13705294</v>
       </c>
       <c r="S49">
-        <v>0.7248085389</v>
+        <v>0.724808539</v>
       </c>
       <c r="T49">
         <v>73.00049077</v>
       </c>
       <c r="U49">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V49">
-        <v>0.3414073529</v>
+        <v>0.341407353</v>
       </c>
       <c r="W49">
         <v>5.423704219</v>
       </c>
       <c r="X49">
-        <v>0.02609590705</v>
+        <v>0.026095907</v>
       </c>
       <c r="Y49">
-        <v>0.6374204609</v>
+        <v>0.637420461</v>
       </c>
       <c r="Z49">
-        <v>0.02609590705</v>
+        <v>0.026095907</v>
       </c>
       <c r="AA49">
-        <v>0.3965615409</v>
+        <v>0.396561541</v>
       </c>
       <c r="AB49">
         <v>0.586618177</v>
       </c>
       <c r="AC49">
-        <v>0.05080228392</v>
+        <v>0.050802284</v>
       </c>
       <c r="AD49">
         <v>135.0414044</v>
@@ -7027,10 +7027,10 @@
         <v>6952.37334</v>
       </c>
       <c r="AK49">
-        <v>0.0009072663414</v>
+        <v>0.000907266</v>
       </c>
       <c r="AL49">
-        <v>0.01756143425</v>
+        <v>0.017561434</v>
       </c>
       <c r="AM49">
         <v>15.41287664</v>
@@ -7039,7 +7039,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO49">
-        <v>0.1000581488</v>
+        <v>0.100058149</v>
       </c>
     </row>
     <row r="50">
@@ -7078,7 +7078,7 @@
         <v>373.4984129</v>
       </c>
       <c r="I50">
-        <v>0.1964575612</v>
+        <v>0.196457561</v>
       </c>
       <c r="J50">
         <v>3.563664101</v>
@@ -7108,37 +7108,37 @@
         <v>5.420697749</v>
       </c>
       <c r="S50">
-        <v>0.5803974472</v>
+        <v>0.580397447</v>
       </c>
       <c r="T50">
         <v>64.9942559</v>
       </c>
       <c r="U50">
-        <v>0.4243661838</v>
+        <v>0.424366184</v>
       </c>
       <c r="V50">
-        <v>0.2761510142</v>
+        <v>0.276151014</v>
       </c>
       <c r="W50">
         <v>3.606743844</v>
       </c>
       <c r="X50">
-        <v>0.02191535293</v>
+        <v>0.021915353</v>
       </c>
       <c r="Y50">
-        <v>0.4876103046</v>
+        <v>0.487610305</v>
       </c>
       <c r="Z50">
-        <v>0.02191535293</v>
+        <v>0.021915353</v>
       </c>
       <c r="AA50">
-        <v>0.3175603173</v>
+        <v>0.317560317</v>
       </c>
       <c r="AB50">
-        <v>0.4454197036</v>
+        <v>0.445419704</v>
       </c>
       <c r="AC50">
-        <v>0.0421906011</v>
+        <v>0.042190601</v>
       </c>
       <c r="AD50">
         <v>90.01550007</v>
@@ -7162,10 +7162,10 @@
         <v>6342.800022</v>
       </c>
       <c r="AK50">
-        <v>0.002656972344</v>
+        <v>0.002656972</v>
       </c>
       <c r="AL50">
-        <v>0.01751352188</v>
+        <v>0.017513522</v>
       </c>
       <c r="AM50">
         <v>10.19115438</v>
@@ -7174,7 +7174,7 @@
         <v>1.078671731</v>
       </c>
       <c r="AO50">
-        <v>0.1871649203</v>
+        <v>0.18716492</v>
       </c>
     </row>
     <row r="51">
@@ -7243,37 +7243,37 @@
         <v>5.589738786</v>
       </c>
       <c r="S51">
-        <v>0.6768365983</v>
+        <v>0.676836598</v>
       </c>
       <c r="T51">
         <v>93.00196585</v>
       </c>
       <c r="U51">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V51">
-        <v>0.3447145688</v>
+        <v>0.344714569</v>
       </c>
       <c r="W51">
         <v>5.094008493</v>
       </c>
       <c r="X51">
-        <v>0.03084662972</v>
+        <v>0.03084663</v>
       </c>
       <c r="Y51">
-        <v>0.6640076059</v>
+        <v>0.664007606</v>
       </c>
       <c r="Z51">
-        <v>0.03084662972</v>
+        <v>0.03084663</v>
       </c>
       <c r="AA51">
-        <v>0.4034238486</v>
+        <v>0.403423849</v>
       </c>
       <c r="AB51">
-        <v>0.5975917393</v>
+        <v>0.597591739</v>
       </c>
       <c r="AC51">
-        <v>0.06641586662</v>
+        <v>0.066415867</v>
       </c>
       <c r="AD51">
         <v>90.00745773</v>
@@ -7297,7 +7297,7 @@
         <v>8646.19326</v>
       </c>
       <c r="AK51">
-        <v>0.002230366568</v>
+        <v>0.002230367</v>
       </c>
       <c r="AL51">
         <v>0.016631524</v>
@@ -7309,7 +7309,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO51">
-        <v>0.5030336354</v>
+        <v>0.503033635</v>
       </c>
     </row>
     <row r="52">
@@ -7348,7 +7348,7 @@
         <v>480.2972762</v>
       </c>
       <c r="I52">
-        <v>-0.1019608982</v>
+        <v>-0.101960898</v>
       </c>
       <c r="J52">
         <v>4.566993706</v>
@@ -7378,40 +7378,40 @@
         <v>5.832833733</v>
       </c>
       <c r="S52">
-        <v>0.9104298436</v>
+        <v>0.910429844</v>
       </c>
       <c r="T52">
         <v>175.7451914</v>
       </c>
       <c r="U52">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V52">
-        <v>0.3057566165</v>
+        <v>0.305756617</v>
       </c>
       <c r="W52">
         <v>4.348405432</v>
       </c>
       <c r="X52">
-        <v>0.02920086239</v>
+        <v>0.029200862</v>
       </c>
       <c r="Y52">
-        <v>0.6104440747</v>
+        <v>0.610444075</v>
       </c>
       <c r="Z52">
-        <v>0.02920086239</v>
+        <v>0.029200862</v>
       </c>
       <c r="AA52">
-        <v>0.3833868363</v>
+        <v>0.383386836</v>
       </c>
       <c r="AB52">
-        <v>0.5499182497</v>
+        <v>0.5499182500000001</v>
       </c>
       <c r="AC52">
-        <v>0.06052582496</v>
+        <v>0.060525825</v>
       </c>
       <c r="AD52">
-        <v>0.006755462179</v>
+        <v>0.006755462</v>
       </c>
       <c r="AE52">
         <v>90.00600211</v>
@@ -7432,10 +7432,10 @@
         <v>6876.646911</v>
       </c>
       <c r="AK52">
-        <v>0.002075245871</v>
+        <v>0.002075246</v>
       </c>
       <c r="AL52">
-        <v>0.01687923584</v>
+        <v>0.016879236</v>
       </c>
       <c r="AM52">
         <v>13.25188741</v>
@@ -7444,7 +7444,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO52">
-        <v>0.2860348266</v>
+        <v>0.286034827</v>
       </c>
     </row>
     <row r="53">
@@ -7483,7 +7483,7 @@
         <v>442.7706082</v>
       </c>
       <c r="I53">
-        <v>-0.06232073995</v>
+        <v>-0.06232074</v>
       </c>
       <c r="J53">
         <v>3.005025126</v>
@@ -7513,37 +7513,37 @@
         <v>5.453197929</v>
       </c>
       <c r="S53">
-        <v>0.8591135294</v>
+        <v>0.859113529</v>
       </c>
       <c r="T53">
         <v>33.74369209</v>
       </c>
       <c r="U53">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V53">
-        <v>0.3246843175</v>
+        <v>0.324684318</v>
       </c>
       <c r="W53">
         <v>4.923591601</v>
       </c>
       <c r="X53">
-        <v>0.02080265478</v>
+        <v>0.020802655</v>
       </c>
       <c r="Y53">
-        <v>0.5822905904</v>
+        <v>0.5822905900000001</v>
       </c>
       <c r="Z53">
-        <v>0.02080265478</v>
+        <v>0.020802655</v>
       </c>
       <c r="AA53">
-        <v>0.3995599396</v>
+        <v>0.39955994</v>
       </c>
       <c r="AB53">
-        <v>0.5304558834999999</v>
+        <v>0.530455884</v>
       </c>
       <c r="AC53">
-        <v>0.05183470689</v>
+        <v>0.051834707</v>
       </c>
       <c r="AD53">
         <v>45.0062722</v>
@@ -7567,10 +7567,10 @@
         <v>7310.472342</v>
       </c>
       <c r="AK53">
-        <v>0.0007337238601</v>
+        <v>0.0007337240000000001</v>
       </c>
       <c r="AL53">
-        <v>0.01780436042</v>
+        <v>0.01780436</v>
       </c>
       <c r="AM53">
         <v>14.18348266</v>
@@ -7579,7 +7579,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO53">
-        <v>0.1695671514</v>
+        <v>0.169567151</v>
       </c>
     </row>
     <row r="54">
@@ -7618,7 +7618,7 @@
         <v>400.4771777</v>
       </c>
       <c r="I54">
-        <v>0.1701220677</v>
+        <v>0.170122068</v>
       </c>
       <c r="J54">
         <v>3.494574401</v>
@@ -7648,37 +7648,37 @@
         <v>5.490501519</v>
       </c>
       <c r="S54">
-        <v>0.6582689056</v>
+        <v>0.658268906</v>
       </c>
       <c r="T54">
         <v>54.00076207</v>
       </c>
       <c r="U54">
-        <v>0.4243661838</v>
+        <v>0.424366184</v>
       </c>
       <c r="V54">
-        <v>0.3108501293</v>
+        <v>0.310850129</v>
       </c>
       <c r="W54">
         <v>4.50705213</v>
       </c>
       <c r="X54">
-        <v>0.02301079003</v>
+        <v>0.02301079</v>
       </c>
       <c r="Y54">
-        <v>0.5202322901</v>
+        <v>0.52023229</v>
       </c>
       <c r="Z54">
-        <v>0.02301079003</v>
+        <v>0.02301079</v>
       </c>
       <c r="AA54">
-        <v>0.3479217217</v>
+        <v>0.347921722</v>
       </c>
       <c r="AB54">
-        <v>0.4749438809</v>
+        <v>0.474943881</v>
       </c>
       <c r="AC54">
-        <v>0.04528840924</v>
+        <v>0.045288409</v>
       </c>
       <c r="AD54">
         <v>63.47766885</v>
@@ -7687,7 +7687,7 @@
         <v>44.94073482</v>
       </c>
       <c r="AF54">
-        <v>0.01189361617</v>
+        <v>0.011893616</v>
       </c>
       <c r="AG54">
         <v>67.10080227</v>
@@ -7702,10 +7702,10 @@
         <v>7251.998623</v>
       </c>
       <c r="AK54">
-        <v>0.002544959671</v>
+        <v>0.00254496</v>
       </c>
       <c r="AL54">
-        <v>0.01784463694</v>
+        <v>0.017844637</v>
       </c>
       <c r="AM54">
         <v>13.87228779</v>
@@ -7714,7 +7714,7 @@
         <v>1.078671731</v>
       </c>
       <c r="AO54">
-        <v>0.1531690396</v>
+        <v>0.15316904</v>
       </c>
     </row>
     <row r="55">
@@ -7753,7 +7753,7 @@
         <v>413.3544307</v>
       </c>
       <c r="I55">
-        <v>-0.1315222219</v>
+        <v>-0.131522222</v>
       </c>
       <c r="J55">
         <v>3.792988664</v>
@@ -7783,43 +7783,43 @@
         <v>5.378359602</v>
       </c>
       <c r="S55">
-        <v>0.6207433812000001</v>
+        <v>0.620743381</v>
       </c>
       <c r="T55">
         <v>68.99938056000001</v>
       </c>
       <c r="U55">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V55">
-        <v>0.3125383543</v>
+        <v>0.312538354</v>
       </c>
       <c r="W55">
         <v>4.555356693</v>
       </c>
       <c r="X55">
-        <v>0.0217790291</v>
+        <v>0.021779029</v>
       </c>
       <c r="Y55">
         <v>0.533039154</v>
       </c>
       <c r="Z55">
-        <v>0.0217790291</v>
+        <v>0.021779029</v>
       </c>
       <c r="AA55">
-        <v>0.3468878271</v>
+        <v>0.346887827</v>
       </c>
       <c r="AB55">
-        <v>0.4814550038</v>
+        <v>0.481455004</v>
       </c>
       <c r="AC55">
-        <v>0.05158415023</v>
+        <v>0.05158415</v>
       </c>
       <c r="AD55">
         <v>90.01015080000001</v>
       </c>
       <c r="AE55">
-        <v>0.01210454786</v>
+        <v>0.012104548</v>
       </c>
       <c r="AF55">
         <v>45.02164771</v>
@@ -7837,7 +7837,7 @@
         <v>8420.657267000001</v>
       </c>
       <c r="AK55">
-        <v>0.0007697196835</v>
+        <v>0.00076972</v>
       </c>
       <c r="AL55">
         <v>0.017348198</v>
@@ -7849,7 +7849,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO55">
-        <v>0.1508194389</v>
+        <v>0.150819439</v>
       </c>
     </row>
     <row r="56">
@@ -7888,7 +7888,7 @@
         <v>498.9645318</v>
       </c>
       <c r="I56">
-        <v>-0.04034416909</v>
+        <v>-0.040344169</v>
       </c>
       <c r="J56">
         <v>4.066183278</v>
@@ -7918,37 +7918,37 @@
         <v>5.815101184</v>
       </c>
       <c r="S56">
-        <v>0.9219122105999999</v>
+        <v>0.921912211</v>
       </c>
       <c r="T56">
         <v>50.99301474</v>
       </c>
       <c r="U56">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V56">
-        <v>0.3250896562</v>
+        <v>0.325089656</v>
       </c>
       <c r="W56">
         <v>4.873550451</v>
       </c>
       <c r="X56">
-        <v>0.03015659758</v>
+        <v>0.030156598</v>
       </c>
       <c r="Y56">
-        <v>0.6377006938000001</v>
+        <v>0.637700694</v>
       </c>
       <c r="Z56">
-        <v>0.03015659758</v>
+        <v>0.030156598</v>
       </c>
       <c r="AA56">
-        <v>0.4038496361</v>
+        <v>0.403849636</v>
       </c>
       <c r="AB56">
-        <v>0.5748487918</v>
+        <v>0.5748487920000001</v>
       </c>
       <c r="AC56">
-        <v>0.06285190206000001</v>
+        <v>0.062851902</v>
       </c>
       <c r="AD56">
         <v>89.99556767999999</v>
@@ -7972,10 +7972,10 @@
         <v>8498.933789999999</v>
       </c>
       <c r="AK56">
-        <v>0.001481266991</v>
+        <v>0.001481267</v>
       </c>
       <c r="AL56">
-        <v>0.01702515162</v>
+        <v>0.017025152</v>
       </c>
       <c r="AM56">
         <v>15.453352</v>
@@ -7984,7 +7984,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO56">
-        <v>0.1959371928</v>
+        <v>0.195937193</v>
       </c>
     </row>
     <row r="57">
@@ -8023,7 +8023,7 @@
         <v>419.9978511</v>
       </c>
       <c r="I57">
-        <v>-0.02971464853</v>
+        <v>-0.029714649</v>
       </c>
       <c r="J57">
         <v>3.366626208</v>
@@ -8053,37 +8053,37 @@
         <v>5.767203536</v>
       </c>
       <c r="S57">
-        <v>0.8846393807</v>
+        <v>0.8846393809999999</v>
       </c>
       <c r="T57">
         <v>3.513223453</v>
       </c>
       <c r="U57">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V57">
-        <v>0.2866332013</v>
+        <v>0.286633201</v>
       </c>
       <c r="W57">
         <v>3.870426511</v>
       </c>
       <c r="X57">
-        <v>0.0226624117</v>
+        <v>0.022662412</v>
       </c>
       <c r="Y57">
-        <v>0.5355667149</v>
+        <v>0.535566715</v>
       </c>
       <c r="Z57">
-        <v>0.0226624117</v>
+        <v>0.022662412</v>
       </c>
       <c r="AA57">
-        <v>0.3641653625</v>
+        <v>0.364165363</v>
       </c>
       <c r="AB57">
-        <v>0.4833396646</v>
+        <v>0.483339665</v>
       </c>
       <c r="AC57">
-        <v>0.05222705031</v>
+        <v>0.05222705</v>
       </c>
       <c r="AD57">
         <v>44.99962733</v>
@@ -8107,19 +8107,19 @@
         <v>7206.022353</v>
       </c>
       <c r="AK57">
-        <v>0.0001576070395</v>
+        <v>0.000157607</v>
       </c>
       <c r="AL57">
-        <v>0.01767751563</v>
+        <v>0.017677516</v>
       </c>
       <c r="AM57">
         <v>11.1871122</v>
       </c>
       <c r="AN57">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO57">
-        <v>0.1637002381</v>
+        <v>0.163700238</v>
       </c>
     </row>
     <row r="58">
@@ -8158,7 +8158,7 @@
         <v>307.2428073</v>
       </c>
       <c r="I58">
-        <v>0.1872790611</v>
+        <v>0.187279061</v>
       </c>
       <c r="J58">
         <v>3.039965615</v>
@@ -8188,37 +8188,37 @@
         <v>5.085529985</v>
       </c>
       <c r="S58">
-        <v>0.8061037176</v>
+        <v>0.806103718</v>
       </c>
       <c r="T58">
         <v>129.2513768</v>
       </c>
       <c r="U58">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V58">
-        <v>0.2401633664</v>
+        <v>0.240163366</v>
       </c>
       <c r="W58">
         <v>2.779315264</v>
       </c>
       <c r="X58">
-        <v>0.01650107964</v>
+        <v>0.01650108</v>
       </c>
       <c r="Y58">
-        <v>0.4119775259</v>
+        <v>0.411977526</v>
       </c>
       <c r="Z58">
-        <v>0.01650107964</v>
+        <v>0.01650108</v>
       </c>
       <c r="AA58">
-        <v>0.2718920666</v>
+        <v>0.271892067</v>
       </c>
       <c r="AB58">
-        <v>0.3798208078</v>
+        <v>0.379820808</v>
       </c>
       <c r="AC58">
-        <v>0.03215671815</v>
+        <v>0.032156718</v>
       </c>
       <c r="AD58">
         <v>90.00202926</v>
@@ -8227,7 +8227,7 @@
         <v>135.0317109</v>
       </c>
       <c r="AF58">
-        <v>0.004792651759</v>
+        <v>0.004792652</v>
       </c>
       <c r="AG58">
         <v>77.12299346</v>
@@ -8242,10 +8242,10 @@
         <v>5523.281326</v>
       </c>
       <c r="AK58">
-        <v>0.001973014116</v>
+        <v>0.001973014</v>
       </c>
       <c r="AL58">
-        <v>0.01714991321</v>
+        <v>0.017149913</v>
       </c>
       <c r="AM58">
         <v>6.676743458</v>
@@ -8254,7 +8254,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO58">
-        <v>0.1092128975</v>
+        <v>0.109212898</v>
       </c>
     </row>
     <row r="59">
@@ -8293,7 +8293,7 @@
         <v>315.0246399</v>
       </c>
       <c r="I59">
-        <v>-0.03365080047</v>
+        <v>-0.0336508</v>
       </c>
       <c r="J59">
         <v>3.738613091</v>
@@ -8323,37 +8323,37 @@
         <v>5.22050176</v>
       </c>
       <c r="S59">
-        <v>0.5469210791</v>
+        <v>0.546921079</v>
       </c>
       <c r="T59">
         <v>39.25185162</v>
       </c>
       <c r="U59">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V59">
-        <v>0.2641394813</v>
+        <v>0.264139481</v>
       </c>
       <c r="W59">
         <v>3.331965924</v>
       </c>
       <c r="X59">
-        <v>0.01871902711</v>
+        <v>0.018719027</v>
       </c>
       <c r="Y59">
-        <v>0.3908139322</v>
+        <v>0.390813932</v>
       </c>
       <c r="Z59">
-        <v>0.01871902711</v>
+        <v>0.018719027</v>
       </c>
       <c r="AA59">
-        <v>0.2655033152</v>
+        <v>0.265503315</v>
       </c>
       <c r="AB59">
-        <v>0.3513810189</v>
+        <v>0.351381019</v>
       </c>
       <c r="AC59">
-        <v>0.03943291331</v>
+        <v>0.039432913</v>
       </c>
       <c r="AD59">
         <v>90.01557022</v>
@@ -8377,16 +8377,16 @@
         <v>6048.524942</v>
       </c>
       <c r="AK59">
-        <v>0.001249512889</v>
+        <v>0.001249513</v>
       </c>
       <c r="AL59">
-        <v>0.01711355623</v>
+        <v>0.017113556</v>
       </c>
       <c r="AM59">
         <v>8.958262952</v>
       </c>
       <c r="AN59">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO59">
         <v>0.13560597</v>
@@ -8428,7 +8428,7 @@
         <v>426.3785753</v>
       </c>
       <c r="I60">
-        <v>0.3294835149</v>
+        <v>0.329483515</v>
       </c>
       <c r="J60">
         <v>4.004909746</v>
@@ -8458,13 +8458,13 @@
         <v>6.113245892</v>
       </c>
       <c r="S60">
-        <v>0.7368888252</v>
+        <v>0.736888825</v>
       </c>
       <c r="T60">
         <v>140.7451735</v>
       </c>
       <c r="U60">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V60">
         <v>0.284717505</v>
@@ -8473,22 +8473,22 @@
         <v>3.801138657</v>
       </c>
       <c r="X60">
-        <v>0.02894863998</v>
+        <v>0.02894864</v>
       </c>
       <c r="Y60">
-        <v>0.5509098203</v>
+        <v>0.55090982</v>
       </c>
       <c r="Z60">
-        <v>0.02894863998</v>
+        <v>0.02894864</v>
       </c>
       <c r="AA60">
-        <v>0.3487442045</v>
+        <v>0.348744205</v>
       </c>
       <c r="AB60">
-        <v>0.5043129125</v>
+        <v>0.504312913</v>
       </c>
       <c r="AC60">
-        <v>0.04659690778</v>
+        <v>0.046596908</v>
       </c>
       <c r="AD60">
         <v>134.9801679</v>
@@ -8512,10 +8512,10 @@
         <v>7208.95622</v>
       </c>
       <c r="AK60">
-        <v>0.002542021269</v>
+        <v>0.002542021</v>
       </c>
       <c r="AL60">
-        <v>0.01756862823</v>
+        <v>0.017568628</v>
       </c>
       <c r="AM60">
         <v>11.37591746</v>
@@ -8524,7 +8524,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO60">
-        <v>0.4986756843</v>
+        <v>0.498675684</v>
       </c>
     </row>
     <row r="61">
@@ -8563,7 +8563,7 @@
         <v>381.3990292</v>
       </c>
       <c r="I61">
-        <v>0.05864173432</v>
+        <v>0.058641734</v>
       </c>
       <c r="J61">
         <v>3.21691317</v>
@@ -8593,43 +8593,43 @@
         <v>5.7438799</v>
       </c>
       <c r="S61">
-        <v>0.8395270144</v>
+        <v>0.839527014</v>
       </c>
       <c r="T61">
         <v>132.2587946</v>
       </c>
       <c r="U61">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V61">
-        <v>0.2753550496</v>
+        <v>0.27535505</v>
       </c>
       <c r="W61">
         <v>3.606230651</v>
       </c>
       <c r="X61">
-        <v>0.02102322261</v>
+        <v>0.021023223</v>
       </c>
       <c r="Y61">
-        <v>0.4983542869</v>
+        <v>0.498354287</v>
       </c>
       <c r="Z61">
-        <v>0.02102322261</v>
+        <v>0.021023223</v>
       </c>
       <c r="AA61">
-        <v>0.3318879779</v>
+        <v>0.331887978</v>
       </c>
       <c r="AB61">
-        <v>0.4538254009</v>
+        <v>0.453825401</v>
       </c>
       <c r="AC61">
-        <v>0.04452888602</v>
+        <v>0.044528886</v>
       </c>
       <c r="AD61">
         <v>134.9978621</v>
       </c>
       <c r="AE61">
-        <v>0.0009779071909000001</v>
+        <v>0.0009779070000000001</v>
       </c>
       <c r="AF61">
         <v>89.98747093999999</v>
@@ -8647,10 +8647,10 @@
         <v>6734.339328</v>
       </c>
       <c r="AK61">
-        <v>0.002292210192</v>
+        <v>0.00229221</v>
       </c>
       <c r="AL61">
-        <v>0.01684510327</v>
+        <v>0.016845103</v>
       </c>
       <c r="AM61">
         <v>9.479947277999999</v>
@@ -8659,7 +8659,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO61">
-        <v>0.1518984782</v>
+        <v>0.151898478</v>
       </c>
     </row>
     <row r="62">
@@ -8728,37 +8728,37 @@
         <v>4.987168241</v>
       </c>
       <c r="S62">
-        <v>0.8361955003</v>
+        <v>0.8361955</v>
       </c>
       <c r="T62">
         <v>93.75100836999999</v>
       </c>
       <c r="U62">
-        <v>0.5665446722</v>
+        <v>0.566544672</v>
       </c>
       <c r="V62">
-        <v>0.2922084617</v>
+        <v>0.292208462</v>
       </c>
       <c r="W62">
         <v>4.05195178</v>
       </c>
       <c r="X62">
-        <v>0.01744267275</v>
+        <v>0.017442673</v>
       </c>
       <c r="Y62">
-        <v>0.4399893978</v>
+        <v>0.439989398</v>
       </c>
       <c r="Z62">
-        <v>0.01744267275</v>
+        <v>0.017442673</v>
       </c>
       <c r="AA62">
-        <v>0.2878108799</v>
+        <v>0.28781088</v>
       </c>
       <c r="AB62">
-        <v>0.4063837905</v>
+        <v>0.406383791</v>
       </c>
       <c r="AC62">
-        <v>0.03360560735</v>
+        <v>0.033605607</v>
       </c>
       <c r="AD62">
         <v>90.00602234999999</v>
@@ -8782,19 +8782,19 @@
         <v>6059.662655</v>
       </c>
       <c r="AK62">
-        <v>0.001330907819</v>
+        <v>0.001330908</v>
       </c>
       <c r="AL62">
-        <v>0.01716745663</v>
+        <v>0.017167457</v>
       </c>
       <c r="AM62">
         <v>11.47167012</v>
       </c>
       <c r="AN62">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO62">
-        <v>0.1555497971</v>
+        <v>0.155549797</v>
       </c>
     </row>
     <row r="63">
@@ -8833,7 +8833,7 @@
         <v>304.5316773</v>
       </c>
       <c r="I63">
-        <v>-0.0983086953</v>
+        <v>-0.098308695</v>
       </c>
       <c r="J63">
         <v>3.747891506</v>
@@ -8863,37 +8863,37 @@
         <v>5.027709405</v>
       </c>
       <c r="S63">
-        <v>0.5363065228</v>
+        <v>0.536306523</v>
       </c>
       <c r="T63">
         <v>111.0058114</v>
       </c>
       <c r="U63">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V63">
-        <v>0.2766544226</v>
+        <v>0.276654423</v>
       </c>
       <c r="W63">
         <v>3.649494698</v>
       </c>
       <c r="X63">
-        <v>0.01713469591</v>
+        <v>0.017134696</v>
       </c>
       <c r="Y63">
-        <v>0.3817836094</v>
+        <v>0.381783609</v>
       </c>
       <c r="Z63">
-        <v>0.01713469591</v>
+        <v>0.017134696</v>
       </c>
       <c r="AA63">
         <v>0.25828685</v>
       </c>
       <c r="AB63">
-        <v>0.3439576338</v>
+        <v>0.343957634</v>
       </c>
       <c r="AC63">
-        <v>0.03782597558</v>
+        <v>0.037825976</v>
       </c>
       <c r="AD63">
         <v>89.99824252000001</v>
@@ -8917,19 +8917,19 @@
         <v>6714.935503</v>
       </c>
       <c r="AK63">
-        <v>0.001397247844</v>
+        <v>0.001397248</v>
       </c>
       <c r="AL63">
-        <v>0.01706241779</v>
+        <v>0.017062418</v>
       </c>
       <c r="AM63">
         <v>10.4519849</v>
       </c>
       <c r="AN63">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO63">
-        <v>0.1301284424</v>
+        <v>0.130128442</v>
       </c>
     </row>
     <row r="64">
@@ -8968,7 +8968,7 @@
         <v>417.8681758</v>
       </c>
       <c r="I64">
-        <v>0.2637384546</v>
+        <v>0.263738455</v>
       </c>
       <c r="J64">
         <v>3.778695783</v>
@@ -8998,37 +8998,37 @@
         <v>5.844354549</v>
       </c>
       <c r="S64">
-        <v>0.2887483731</v>
+        <v>0.288748373</v>
       </c>
       <c r="T64">
         <v>107.0041413</v>
       </c>
       <c r="U64">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V64">
-        <v>0.3010617469</v>
+        <v>0.301061747</v>
       </c>
       <c r="W64">
         <v>4.219203725</v>
       </c>
       <c r="X64">
-        <v>0.02750705781</v>
+        <v>0.027507058</v>
       </c>
       <c r="Y64">
-        <v>0.5437310883000001</v>
+        <v>0.543731088</v>
       </c>
       <c r="Z64">
-        <v>0.02750705781</v>
+        <v>0.027507058</v>
       </c>
       <c r="AA64">
         <v>0.347352828</v>
       </c>
       <c r="AB64">
-        <v>0.4985567348</v>
+        <v>0.498556735</v>
       </c>
       <c r="AC64">
-        <v>0.04517435347</v>
+        <v>0.045174353</v>
       </c>
       <c r="AD64">
         <v>44.97238686</v>
@@ -9052,10 +9052,10 @@
         <v>7949.457502</v>
       </c>
       <c r="AK64">
-        <v>0.001464636231</v>
+        <v>0.001464636</v>
       </c>
       <c r="AL64">
-        <v>0.0173385776</v>
+        <v>0.017338578</v>
       </c>
       <c r="AM64">
         <v>13.0066057</v>
@@ -9103,7 +9103,7 @@
         <v>386.9930395</v>
       </c>
       <c r="I65">
-        <v>0.04795133276</v>
+        <v>0.047951333</v>
       </c>
       <c r="J65">
         <v>3.317682391</v>
@@ -9133,37 +9133,37 @@
         <v>5.736736394</v>
       </c>
       <c r="S65">
-        <v>0.7984314766</v>
+        <v>0.7984314769999999</v>
       </c>
       <c r="T65">
         <v>137.7437965</v>
       </c>
       <c r="U65">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V65">
-        <v>0.2866934299</v>
+        <v>0.28669343</v>
       </c>
       <c r="W65">
         <v>3.890825893</v>
       </c>
       <c r="X65">
-        <v>0.0217150876</v>
+        <v>0.021715088</v>
       </c>
       <c r="Y65">
-        <v>0.5032212966</v>
+        <v>0.503221297</v>
       </c>
       <c r="Z65">
-        <v>0.0217150876</v>
+        <v>0.021715088</v>
       </c>
       <c r="AA65">
-        <v>0.3357115017</v>
+        <v>0.335711502</v>
       </c>
       <c r="AB65">
-        <v>0.4583252681</v>
+        <v>0.458325268</v>
       </c>
       <c r="AC65">
-        <v>0.04489602851</v>
+        <v>0.044896029</v>
       </c>
       <c r="AD65">
         <v>135.0084059</v>
@@ -9187,19 +9187,19 @@
         <v>6952.282145</v>
       </c>
       <c r="AK65">
-        <v>0.002419675128</v>
+        <v>0.002419675</v>
       </c>
       <c r="AL65">
-        <v>0.01687142286</v>
+        <v>0.016871423</v>
       </c>
       <c r="AM65">
         <v>10.35075437</v>
       </c>
       <c r="AN65">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO65">
-        <v>0.1816624751</v>
+        <v>0.181662475</v>
       </c>
     </row>
     <row r="66">
@@ -9238,7 +9238,7 @@
         <v>517.7693349</v>
       </c>
       <c r="I66">
-        <v>-0.3205215945</v>
+        <v>-0.320521595</v>
       </c>
       <c r="J66">
         <v>3.720009261</v>
@@ -9268,37 +9268,37 @@
         <v>6.400142744</v>
       </c>
       <c r="S66">
-        <v>0.7534311691</v>
+        <v>0.753431169</v>
       </c>
       <c r="T66">
         <v>47.75212056</v>
       </c>
       <c r="U66">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V66">
-        <v>0.3229561879</v>
+        <v>0.322956188</v>
       </c>
       <c r="W66">
         <v>4.834977551</v>
       </c>
       <c r="X66">
-        <v>0.02448225177</v>
+        <v>0.024482252</v>
       </c>
       <c r="Y66">
-        <v>0.6595049041</v>
+        <v>0.6595049039999999</v>
       </c>
       <c r="Z66">
-        <v>0.02448225177</v>
+        <v>0.024482252</v>
       </c>
       <c r="AA66">
-        <v>0.4261916144</v>
+        <v>0.426191614</v>
       </c>
       <c r="AB66">
-        <v>0.5885495707</v>
+        <v>0.588549571</v>
       </c>
       <c r="AC66">
-        <v>0.07095533337</v>
+        <v>0.070955333</v>
       </c>
       <c r="AD66">
         <v>44.98191128</v>
@@ -9307,7 +9307,7 @@
         <v>90.01480506999999</v>
       </c>
       <c r="AF66">
-        <v>0.005046928729</v>
+        <v>0.005046929</v>
       </c>
       <c r="AG66">
         <v>81.51971949</v>
@@ -9322,10 +9322,10 @@
         <v>8313.740258</v>
       </c>
       <c r="AK66">
-        <v>0.0004876679945</v>
+        <v>0.000487668</v>
       </c>
       <c r="AL66">
-        <v>0.01750121606</v>
+        <v>0.017501216</v>
       </c>
       <c r="AM66">
         <v>14.46620128</v>
@@ -9334,7 +9334,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO66">
-        <v>0.3919526666</v>
+        <v>0.391952667</v>
       </c>
     </row>
     <row r="67">
@@ -9373,7 +9373,7 @@
         <v>563.9910596</v>
       </c>
       <c r="I67">
-        <v>0.004988791514</v>
+        <v>0.004988792</v>
       </c>
       <c r="J67">
         <v>2.75808754</v>
@@ -9403,37 +9403,37 @@
         <v>6.014871235</v>
       </c>
       <c r="S67">
-        <v>0.7088922416</v>
+        <v>0.708892242</v>
       </c>
       <c r="T67">
         <v>93.25517787</v>
       </c>
       <c r="U67">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V67">
-        <v>0.3440988616</v>
+        <v>0.344098862</v>
       </c>
       <c r="W67">
         <v>5.519905521</v>
       </c>
       <c r="X67">
-        <v>0.02656060679</v>
+        <v>0.026560607</v>
       </c>
       <c r="Y67">
-        <v>0.7435240722999999</v>
+        <v>0.743524072</v>
       </c>
       <c r="Z67">
-        <v>0.02656060679</v>
+        <v>0.026560607</v>
       </c>
       <c r="AA67">
-        <v>0.5257881499</v>
+        <v>0.52578815</v>
       </c>
       <c r="AB67">
-        <v>0.6811642778</v>
+        <v>0.681164278</v>
       </c>
       <c r="AC67">
-        <v>0.06235979441</v>
+        <v>0.062359794</v>
       </c>
       <c r="AD67">
         <v>90.00133503000001</v>
@@ -9457,10 +9457,10 @@
         <v>8683.278</v>
       </c>
       <c r="AK67">
-        <v>0.001903947719</v>
+        <v>0.001903948</v>
       </c>
       <c r="AL67">
-        <v>0.01716187567</v>
+        <v>0.017161876</v>
       </c>
       <c r="AM67">
         <v>16.33687704</v>
@@ -9469,7 +9469,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO67">
-        <v>0.1728958752</v>
+        <v>0.172895875</v>
       </c>
     </row>
     <row r="68">
@@ -9508,7 +9508,7 @@
         <v>401.0010849</v>
       </c>
       <c r="I68">
-        <v>-0.2416325778</v>
+        <v>-0.241632578</v>
       </c>
       <c r="J68">
         <v>3.459914961</v>
@@ -9538,37 +9538,37 @@
         <v>5.435497932</v>
       </c>
       <c r="S68">
-        <v>0.7941327928</v>
+        <v>0.7941327929999999</v>
       </c>
       <c r="T68">
         <v>132.9842939</v>
       </c>
       <c r="U68">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V68">
-        <v>0.3240123559</v>
+        <v>0.324012356</v>
       </c>
       <c r="W68">
         <v>4.930065365</v>
       </c>
       <c r="X68">
-        <v>0.01816319969</v>
+        <v>0.0181632</v>
       </c>
       <c r="Y68">
-        <v>0.5149593973</v>
+        <v>0.514959397</v>
       </c>
       <c r="Z68">
-        <v>0.01816319969</v>
+        <v>0.0181632</v>
       </c>
       <c r="AA68">
-        <v>0.3591200533</v>
+        <v>0.359120053</v>
       </c>
       <c r="AB68">
-        <v>0.4648627109</v>
+        <v>0.464862711</v>
       </c>
       <c r="AC68">
-        <v>0.05009668632</v>
+        <v>0.050096686</v>
       </c>
       <c r="AD68">
         <v>134.989853</v>
@@ -9592,10 +9592,10 @@
         <v>6732.352212</v>
       </c>
       <c r="AK68">
-        <v>0.001445821406</v>
+        <v>0.001445821</v>
       </c>
       <c r="AL68">
-        <v>0.01719826133</v>
+        <v>0.017198261</v>
       </c>
       <c r="AM68">
         <v>14.6815462</v>
@@ -9604,7 +9604,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO68">
-        <v>0.1397309554</v>
+        <v>0.139730955</v>
       </c>
     </row>
     <row r="69">
@@ -9643,7 +9643,7 @@
         <v>535.8477432</v>
       </c>
       <c r="I69">
-        <v>0.3727384278</v>
+        <v>0.372738428</v>
       </c>
       <c r="J69">
         <v>3.505507152</v>
@@ -9673,37 +9673,37 @@
         <v>5.150563723</v>
       </c>
       <c r="S69">
-        <v>0.8244829275</v>
+        <v>0.824482928</v>
       </c>
       <c r="T69">
         <v>64.99647315999999</v>
       </c>
       <c r="U69">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V69">
-        <v>0.3691974903</v>
+        <v>0.36919749</v>
       </c>
       <c r="W69">
         <v>6.264271959</v>
       </c>
       <c r="X69">
-        <v>0.03384876706</v>
+        <v>0.033848767</v>
       </c>
       <c r="Y69">
-        <v>0.7110588792</v>
+        <v>0.711058879</v>
       </c>
       <c r="Z69">
-        <v>0.03384876706</v>
+        <v>0.033848767</v>
       </c>
       <c r="AA69">
-        <v>0.4621403896</v>
+        <v>0.46214039</v>
       </c>
       <c r="AB69">
-        <v>0.6564908508</v>
+        <v>0.656490851</v>
       </c>
       <c r="AC69">
-        <v>0.05456802843</v>
+        <v>0.054568028</v>
       </c>
       <c r="AD69">
         <v>179.9843774</v>
@@ -9727,10 +9727,10 @@
         <v>7775.392235</v>
       </c>
       <c r="AK69">
-        <v>0.002053967474</v>
+        <v>0.002053967</v>
       </c>
       <c r="AL69">
-        <v>0.01770157273</v>
+        <v>0.017701573</v>
       </c>
       <c r="AM69">
         <v>19.05408826</v>
@@ -9739,7 +9739,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO69">
-        <v>0.1011746451</v>
+        <v>0.101174645</v>
       </c>
     </row>
     <row r="70">
@@ -9808,37 +9808,37 @@
         <v>6.501686547</v>
       </c>
       <c r="S70">
-        <v>0.7821944823</v>
+        <v>0.782194482</v>
       </c>
       <c r="T70">
         <v>47.75220638</v>
       </c>
       <c r="U70">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V70">
-        <v>0.3723513932</v>
+        <v>0.372351393</v>
       </c>
       <c r="W70">
         <v>6.287440268</v>
       </c>
       <c r="X70">
-        <v>0.02767340313</v>
+        <v>0.027673403</v>
       </c>
       <c r="Y70">
-        <v>0.6669086383</v>
+        <v>0.666908638</v>
       </c>
       <c r="Z70">
-        <v>0.02767340313</v>
+        <v>0.027673403</v>
       </c>
       <c r="AA70">
         <v>0.437863012</v>
       </c>
       <c r="AB70">
-        <v>0.5926067116</v>
+        <v>0.592606712</v>
       </c>
       <c r="AC70">
-        <v>0.07430192665</v>
+        <v>0.074301927</v>
       </c>
       <c r="AD70">
         <v>44.97328878</v>
@@ -9862,10 +9862,10 @@
         <v>7932.573905</v>
       </c>
       <c r="AK70">
-        <v>0.001145964589</v>
+        <v>0.001145965</v>
       </c>
       <c r="AL70">
-        <v>0.01750345133</v>
+        <v>0.017503451</v>
       </c>
       <c r="AM70">
         <v>21.04311967</v>
@@ -9874,7 +9874,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO70">
-        <v>0.3080227281</v>
+        <v>0.308022728</v>
       </c>
     </row>
     <row r="71">
@@ -9913,7 +9913,7 @@
         <v>544.0909351</v>
       </c>
       <c r="I71">
-        <v>0.04861886228</v>
+        <v>0.048618862</v>
       </c>
       <c r="J71">
         <v>2.775194011</v>
@@ -9943,37 +9943,37 @@
         <v>6.049986434</v>
       </c>
       <c r="S71">
-        <v>0.7076632128</v>
+        <v>0.707663213</v>
       </c>
       <c r="T71">
         <v>93.25609701</v>
       </c>
       <c r="U71">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V71">
-        <v>0.3595331978</v>
+        <v>0.359533198</v>
       </c>
       <c r="W71">
         <v>5.974886589</v>
       </c>
       <c r="X71">
-        <v>0.02528972088</v>
+        <v>0.025289721</v>
       </c>
       <c r="Y71">
-        <v>0.7309649954</v>
+        <v>0.730964995</v>
       </c>
       <c r="Z71">
-        <v>0.02528972088</v>
+        <v>0.025289721</v>
       </c>
       <c r="AA71">
-        <v>0.5046081684</v>
+        <v>0.504608168</v>
       </c>
       <c r="AB71">
-        <v>0.6722493265</v>
+        <v>0.672249327</v>
       </c>
       <c r="AC71">
-        <v>0.05871566896</v>
+        <v>0.058715669</v>
       </c>
       <c r="AD71">
         <v>90.00874064</v>
@@ -9997,10 +9997,10 @@
         <v>6976.508125</v>
       </c>
       <c r="AK71">
-        <v>0.002052059834</v>
+        <v>0.00205206</v>
       </c>
       <c r="AL71">
-        <v>0.01682298951</v>
+        <v>0.01682299</v>
       </c>
       <c r="AM71">
         <v>17.37933814</v>
@@ -10048,7 +10048,7 @@
         <v>399.3463231</v>
       </c>
       <c r="I72">
-        <v>-0.2561506425</v>
+        <v>-0.256150643</v>
       </c>
       <c r="J72">
         <v>3.389816905</v>
@@ -10078,37 +10078,37 @@
         <v>5.46182266</v>
       </c>
       <c r="S72">
-        <v>0.8259039011</v>
+        <v>0.825903901</v>
       </c>
       <c r="T72">
         <v>137.2590893</v>
       </c>
       <c r="U72">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V72">
-        <v>0.3416676377</v>
+        <v>0.341667638</v>
       </c>
       <c r="W72">
         <v>5.455179044</v>
       </c>
       <c r="X72">
-        <v>0.01803915446</v>
+        <v>0.018039154</v>
       </c>
       <c r="Y72">
-        <v>0.5089618486</v>
+        <v>0.508961849</v>
       </c>
       <c r="Z72">
-        <v>0.01803915446</v>
+        <v>0.018039154</v>
       </c>
       <c r="AA72">
-        <v>0.3597795747</v>
+        <v>0.359779575</v>
       </c>
       <c r="AB72">
-        <v>0.4592098855</v>
+        <v>0.459209886</v>
       </c>
       <c r="AC72">
-        <v>0.04975196313</v>
+        <v>0.049751963</v>
       </c>
       <c r="AD72">
         <v>134.9911242</v>
@@ -10132,19 +10132,19 @@
         <v>6849.59987</v>
       </c>
       <c r="AK72">
-        <v>0.001913704039</v>
+        <v>0.001913704</v>
       </c>
       <c r="AL72">
-        <v>0.01709213667</v>
+        <v>0.017092137</v>
       </c>
       <c r="AM72">
         <v>16.02241157</v>
       </c>
       <c r="AN72">
-        <v>0.9489935195</v>
+        <v>0.94899352</v>
       </c>
       <c r="AO72">
-        <v>0.09944248416</v>
+        <v>0.099442484</v>
       </c>
     </row>
     <row r="73">
@@ -10183,7 +10183,7 @@
         <v>513.9530512</v>
       </c>
       <c r="I73">
-        <v>0.3734214574</v>
+        <v>0.373421457</v>
       </c>
       <c r="J73">
         <v>3.508212674</v>
@@ -10213,40 +10213,40 @@
         <v>5.323396336</v>
       </c>
       <c r="S73">
-        <v>0.8398337833</v>
+        <v>0.839833783</v>
       </c>
       <c r="T73">
         <v>65.01273119</v>
       </c>
       <c r="U73">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V73">
-        <v>0.3555287588</v>
+        <v>0.355528759</v>
       </c>
       <c r="W73">
         <v>5.829993467</v>
       </c>
       <c r="X73">
-        <v>0.03187385923</v>
+        <v>0.031873859</v>
       </c>
       <c r="Y73">
-        <v>0.6837504451999999</v>
+        <v>0.683750445</v>
       </c>
       <c r="Z73">
-        <v>0.03187385923</v>
+        <v>0.031873859</v>
       </c>
       <c r="AA73">
-        <v>0.4468036417</v>
+        <v>0.446803642</v>
       </c>
       <c r="AB73">
         <v>0.632118559</v>
       </c>
       <c r="AC73">
-        <v>0.05163188626</v>
+        <v>0.051631886</v>
       </c>
       <c r="AD73">
-        <v>0.003520189146</v>
+        <v>0.003520189</v>
       </c>
       <c r="AE73">
         <v>26.48705589</v>
@@ -10267,10 +10267,10 @@
         <v>7850.562888</v>
       </c>
       <c r="AK73">
-        <v>0.001656846775</v>
+        <v>0.001656847</v>
       </c>
       <c r="AL73">
-        <v>0.01781997912</v>
+        <v>0.017819979</v>
       </c>
       <c r="AM73">
         <v>17.02024272</v>
@@ -10279,7 +10279,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO73">
-        <v>0.1235634134</v>
+        <v>0.123563413</v>
       </c>
     </row>
     <row r="74">
@@ -10318,7 +10318,7 @@
         <v>634.8586626</v>
       </c>
       <c r="I74">
-        <v>0.1850226333</v>
+        <v>0.185022633</v>
       </c>
       <c r="J74">
         <v>3.488796906</v>
@@ -10348,37 +10348,37 @@
         <v>6.505632121</v>
       </c>
       <c r="S74">
-        <v>0.9563442993</v>
+        <v>0.956344299</v>
       </c>
       <c r="T74">
         <v>140.998305</v>
       </c>
       <c r="U74">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V74">
-        <v>0.3800538536</v>
+        <v>0.380053854</v>
       </c>
       <c r="W74">
         <v>6.612526978</v>
       </c>
       <c r="X74">
-        <v>0.03818967575</v>
+        <v>0.038189676</v>
       </c>
       <c r="Y74">
-        <v>0.8331597925000001</v>
+        <v>0.833159793</v>
       </c>
       <c r="Z74">
-        <v>0.03818967575</v>
+        <v>0.038189676</v>
       </c>
       <c r="AA74">
-        <v>0.5494078814</v>
+        <v>0.549407881</v>
       </c>
       <c r="AB74">
-        <v>0.7661243637</v>
+        <v>0.7661243639999999</v>
       </c>
       <c r="AC74">
-        <v>0.0670354288</v>
+        <v>0.06703542899999999</v>
       </c>
       <c r="AD74">
         <v>135.0010265</v>
@@ -10402,10 +10402,10 @@
         <v>11355.58808</v>
       </c>
       <c r="AK74">
-        <v>0.001054771963</v>
+        <v>0.001054772</v>
       </c>
       <c r="AL74">
-        <v>0.01736284784</v>
+        <v>0.017362848</v>
       </c>
       <c r="AM74">
         <v>18.63439743</v>
@@ -10414,7 +10414,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO74">
-        <v>0.3068598835</v>
+        <v>0.306859884</v>
       </c>
     </row>
     <row r="75">
@@ -10453,7 +10453,7 @@
         <v>461.5079497</v>
       </c>
       <c r="I75">
-        <v>-0.1684940691</v>
+        <v>-0.168494069</v>
       </c>
       <c r="J75">
         <v>4.453926188</v>
@@ -10483,37 +10483,37 @@
         <v>6.448611093</v>
       </c>
       <c r="S75">
-        <v>0.8202372233</v>
+        <v>0.820237223</v>
       </c>
       <c r="T75">
         <v>78.74003784999999</v>
       </c>
       <c r="U75">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V75">
-        <v>0.3240448875</v>
+        <v>0.324044888</v>
       </c>
       <c r="W75">
         <v>4.911084687</v>
       </c>
       <c r="X75">
-        <v>0.02711556844</v>
+        <v>0.027115568</v>
       </c>
       <c r="Y75">
-        <v>0.5735053714</v>
+        <v>0.573505371</v>
       </c>
       <c r="Z75">
-        <v>0.02711556844</v>
+        <v>0.027115568</v>
       </c>
       <c r="AA75">
-        <v>0.3653741091</v>
+        <v>0.365374109</v>
       </c>
       <c r="AB75">
-        <v>0.5125574751</v>
+        <v>0.512557475</v>
       </c>
       <c r="AC75">
-        <v>0.0609478963</v>
+        <v>0.060947896</v>
       </c>
       <c r="AD75">
         <v>90.00384127</v>
@@ -10537,10 +10537,10 @@
         <v>7122.95579</v>
       </c>
       <c r="AK75">
-        <v>0.001141416965</v>
+        <v>0.001141417</v>
       </c>
       <c r="AL75">
-        <v>0.01718089276</v>
+        <v>0.017180893</v>
       </c>
       <c r="AM75">
         <v>14.23603373</v>
@@ -10549,7 +10549,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO75">
-        <v>0.2709966809</v>
+        <v>0.270996681</v>
       </c>
     </row>
     <row r="76">
@@ -10588,7 +10588,7 @@
         <v>495.215823</v>
       </c>
       <c r="I76">
-        <v>-0.1250654557</v>
+        <v>-0.125065456</v>
       </c>
       <c r="J76">
         <v>3.446563715</v>
@@ -10618,37 +10618,37 @@
         <v>5.465301403</v>
       </c>
       <c r="S76">
-        <v>0.7768470487</v>
+        <v>0.776847049</v>
       </c>
       <c r="T76">
         <v>73.00691854</v>
       </c>
       <c r="U76">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V76">
-        <v>0.3379985136</v>
+        <v>0.337998514</v>
       </c>
       <c r="W76">
         <v>5.292972978</v>
       </c>
       <c r="X76">
-        <v>0.02691093869</v>
+        <v>0.026910939</v>
       </c>
       <c r="Y76">
-        <v>0.6255423218</v>
+        <v>0.625542322</v>
       </c>
       <c r="Z76">
-        <v>0.02691093869</v>
+        <v>0.026910939</v>
       </c>
       <c r="AA76">
-        <v>0.4171693077</v>
+        <v>0.417169308</v>
       </c>
       <c r="AB76">
-        <v>0.5591663157</v>
+        <v>0.559166316</v>
       </c>
       <c r="AC76">
-        <v>0.06637600616</v>
+        <v>0.066376006</v>
       </c>
       <c r="AD76">
         <v>89.99536625</v>
@@ -10672,10 +10672,10 @@
         <v>7802.403527</v>
       </c>
       <c r="AK76">
-        <v>0.00213458972</v>
+        <v>0.00213459</v>
       </c>
       <c r="AL76">
-        <v>0.01744440717</v>
+        <v>0.017444407</v>
       </c>
       <c r="AM76">
         <v>16.69675827</v>
@@ -10684,7 +10684,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO76">
-        <v>0.2246894092</v>
+        <v>0.224689409</v>
       </c>
     </row>
     <row r="77">
@@ -10723,7 +10723,7 @@
         <v>771.0203054</v>
       </c>
       <c r="I77">
-        <v>0.2629162949</v>
+        <v>0.262916295</v>
       </c>
       <c r="J77">
         <v>3.517253581</v>
@@ -10753,37 +10753,37 @@
         <v>6.40698724</v>
       </c>
       <c r="S77">
-        <v>0.8930060811</v>
+        <v>0.893006081</v>
       </c>
       <c r="T77">
         <v>86.50914155</v>
       </c>
       <c r="U77">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V77">
-        <v>0.4176709725</v>
+        <v>0.417670973</v>
       </c>
       <c r="W77">
         <v>7.800118118</v>
       </c>
       <c r="X77">
-        <v>0.04772895647</v>
+        <v>0.047728956</v>
       </c>
       <c r="Y77">
         <v>1.029015667</v>
       </c>
       <c r="Z77">
-        <v>0.04772895647</v>
+        <v>0.047728956</v>
       </c>
       <c r="AA77">
-        <v>0.6464923409</v>
+        <v>0.646492341</v>
       </c>
       <c r="AB77">
-        <v>0.9447193093</v>
+        <v>0.944719309</v>
       </c>
       <c r="AC77">
-        <v>0.08429635794</v>
+        <v>0.084296358</v>
       </c>
       <c r="AD77">
         <v>90.00024593000001</v>
@@ -10807,10 +10807,10 @@
         <v>8428.743055000001</v>
       </c>
       <c r="AK77">
-        <v>0.001084291108</v>
+        <v>0.001084291</v>
       </c>
       <c r="AL77">
-        <v>0.01747267567</v>
+        <v>0.017472676</v>
       </c>
       <c r="AM77">
         <v>26.09698216</v>
@@ -10819,7 +10819,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO77">
-        <v>0.2260062908</v>
+        <v>0.226006291</v>
       </c>
     </row>
     <row r="78">
@@ -10858,7 +10858,7 @@
         <v>619.3667868</v>
       </c>
       <c r="I78">
-        <v>0.3021215012</v>
+        <v>0.302121501</v>
       </c>
       <c r="J78">
         <v>4.080106348</v>
@@ -10876,7 +10876,7 @@
         <v>480.7359926</v>
       </c>
       <c r="O78">
-        <v>0.5707127377</v>
+        <v>0.570712738</v>
       </c>
       <c r="P78">
         <v>761.333232</v>
@@ -10894,31 +10894,31 @@
         <v>129.2481255</v>
       </c>
       <c r="U78">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V78">
-        <v>0.3847369749</v>
+        <v>0.384736975</v>
       </c>
       <c r="W78">
         <v>6.734194237</v>
       </c>
       <c r="X78">
-        <v>0.03849544224</v>
+        <v>0.038495442</v>
       </c>
       <c r="Y78">
-        <v>0.7998141976000001</v>
+        <v>0.799814198</v>
       </c>
       <c r="Z78">
-        <v>0.03849544224</v>
+        <v>0.038495442</v>
       </c>
       <c r="AA78">
-        <v>0.5239712927</v>
+        <v>0.523971293</v>
       </c>
       <c r="AB78">
         <v>0.734223306</v>
       </c>
       <c r="AC78">
-        <v>0.06559089160000001</v>
+        <v>0.065590892</v>
       </c>
       <c r="AD78">
         <v>90.00738932</v>
@@ -10942,10 +10942,10 @@
         <v>10221.01263</v>
       </c>
       <c r="AK78">
-        <v>0.001441395285</v>
+        <v>0.001441395</v>
       </c>
       <c r="AL78">
-        <v>0.01754790649</v>
+        <v>0.017547906</v>
       </c>
       <c r="AM78">
         <v>20.73199912</v>
@@ -10954,7 +10954,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO78">
-        <v>0.1861565462</v>
+        <v>0.186156546</v>
       </c>
     </row>
     <row r="79">
@@ -10993,7 +10993,7 @@
         <v>472.3638793</v>
       </c>
       <c r="I79">
-        <v>-0.1205882446</v>
+        <v>-0.120588245</v>
       </c>
       <c r="J79">
         <v>4.583780577</v>
@@ -11023,37 +11023,37 @@
         <v>6.503240196</v>
       </c>
       <c r="S79">
-        <v>0.8357341506</v>
+        <v>0.835734151</v>
       </c>
       <c r="T79">
         <v>42.25072015</v>
       </c>
       <c r="U79">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V79">
-        <v>0.3411316718</v>
+        <v>0.341131672</v>
       </c>
       <c r="W79">
         <v>5.393869981</v>
       </c>
       <c r="X79">
-        <v>0.0294909753</v>
+        <v>0.029490975</v>
       </c>
       <c r="Y79">
         <v>0.576405273</v>
       </c>
       <c r="Z79">
-        <v>0.0294909753</v>
+        <v>0.029490975</v>
       </c>
       <c r="AA79">
-        <v>0.3730716417</v>
+        <v>0.373071642</v>
       </c>
       <c r="AB79">
-        <v>0.5143517056</v>
+        <v>0.514351706</v>
       </c>
       <c r="AC79">
-        <v>0.06205356737</v>
+        <v>0.062053567</v>
       </c>
       <c r="AD79">
         <v>45.00835308</v>
@@ -11077,10 +11077,10 @@
         <v>7290.088536</v>
       </c>
       <c r="AK79">
-        <v>0.001475806546</v>
+        <v>0.001475807</v>
       </c>
       <c r="AL79">
-        <v>0.01728380301</v>
+        <v>0.017283803</v>
       </c>
       <c r="AM79">
         <v>16.35104849</v>
@@ -11089,7 +11089,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO79">
-        <v>0.2853338032</v>
+        <v>0.285333803</v>
       </c>
     </row>
     <row r="80">
@@ -11128,7 +11128,7 @@
         <v>474.1011126</v>
       </c>
       <c r="I80">
-        <v>0.1486890258</v>
+        <v>0.148689026</v>
       </c>
       <c r="J80">
         <v>3.146783397</v>
@@ -11158,13 +11158,13 @@
         <v>5.635656304</v>
       </c>
       <c r="S80">
-        <v>0.7907107861</v>
+        <v>0.790710786</v>
       </c>
       <c r="T80">
         <v>87.25229462</v>
       </c>
       <c r="U80">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V80">
         <v>0.358440387</v>
@@ -11173,22 +11173,22 @@
         <v>5.933325445</v>
       </c>
       <c r="X80">
-        <v>0.02636397301</v>
+        <v>0.026363973</v>
       </c>
       <c r="Y80">
-        <v>0.6248015643</v>
+        <v>0.624801564</v>
       </c>
       <c r="Z80">
-        <v>0.02636397301</v>
+        <v>0.026363973</v>
       </c>
       <c r="AA80">
-        <v>0.4190132173</v>
+        <v>0.419013217</v>
       </c>
       <c r="AB80">
-        <v>0.5722800868</v>
+        <v>0.572280087</v>
       </c>
       <c r="AC80">
-        <v>0.05252147749</v>
+        <v>0.052521477</v>
       </c>
       <c r="AD80">
         <v>89.9904839</v>
@@ -11212,10 +11212,10 @@
         <v>8397.109836</v>
       </c>
       <c r="AK80">
-        <v>0.001582366014</v>
+        <v>0.001582366</v>
       </c>
       <c r="AL80">
-        <v>0.01708732729</v>
+        <v>0.017087327</v>
       </c>
       <c r="AM80">
         <v>19.22119314</v>
@@ -11224,7 +11224,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO80">
-        <v>0.1015906642</v>
+        <v>0.101590664</v>
       </c>
     </row>
     <row r="81">
@@ -11263,7 +11263,7 @@
         <v>729.4114863999999</v>
       </c>
       <c r="I81">
-        <v>0.4778796195</v>
+        <v>0.47787962</v>
       </c>
       <c r="J81">
         <v>3.847813073</v>
@@ -11293,37 +11293,37 @@
         <v>6.34596851</v>
       </c>
       <c r="S81">
-        <v>0.8439213432</v>
+        <v>0.843921343</v>
       </c>
       <c r="T81">
         <v>53.75174034</v>
       </c>
       <c r="U81">
-        <v>0.4249085041</v>
+        <v>0.424908504</v>
       </c>
       <c r="V81">
-        <v>0.4061718738</v>
+        <v>0.406171874</v>
       </c>
       <c r="W81">
         <v>7.290662817</v>
       </c>
       <c r="X81">
-        <v>0.05188771977</v>
+        <v>0.05188772</v>
       </c>
       <c r="Y81">
-        <v>0.9700963829</v>
+        <v>0.970096383</v>
       </c>
       <c r="Z81">
-        <v>0.05188771977</v>
+        <v>0.05188772</v>
       </c>
       <c r="AA81">
-        <v>0.5942811864</v>
+        <v>0.594281186</v>
       </c>
       <c r="AB81">
-        <v>0.8932986067000001</v>
+        <v>0.893298607</v>
       </c>
       <c r="AC81">
-        <v>0.07679777619</v>
+        <v>0.076797776</v>
       </c>
       <c r="AD81">
         <v>45.01644532</v>
@@ -11347,10 +11347,10 @@
         <v>7603.362548</v>
       </c>
       <c r="AK81">
-        <v>0.00084417328</v>
+        <v>0.000844173</v>
       </c>
       <c r="AL81">
-        <v>0.01731638102</v>
+        <v>0.017316381</v>
       </c>
       <c r="AM81">
         <v>24.58992298</v>
@@ -11359,7 +11359,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO81">
-        <v>0.5597120549</v>
+        <v>0.559712055</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/derived_data/FT_STA_formatted-data.xlsx
+++ b/analysis/derived_data/FT_STA_formatted-data.xlsx
@@ -598,7 +598,7 @@
         <v>510.3146761</v>
       </c>
       <c r="I2">
-        <v>0.208299526</v>
+        <v>0.2082995257</v>
       </c>
       <c r="J2">
         <v>3.611167169</v>
@@ -628,13 +628,13 @@
         <v>5.535717812</v>
       </c>
       <c r="S2">
-        <v>0.757126494</v>
+        <v>0.7571264937</v>
       </c>
       <c r="T2">
         <v>54.74853125</v>
       </c>
       <c r="U2">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V2">
         <v>0.59373265</v>
@@ -643,28 +643,28 @@
         <v>14.10821254</v>
       </c>
       <c r="X2">
-        <v>0.032207122</v>
+        <v>0.03220712242</v>
       </c>
       <c r="Y2">
-        <v>0.663238285</v>
+        <v>0.6632382845</v>
       </c>
       <c r="Z2">
-        <v>0.032207122</v>
+        <v>0.03220712242</v>
       </c>
       <c r="AA2">
-        <v>0.429877005</v>
+        <v>0.4298770045</v>
       </c>
       <c r="AB2">
-        <v>0.605845551</v>
+        <v>0.6058455505</v>
       </c>
       <c r="AC2">
-        <v>0.057392734</v>
+        <v>0.05739273397</v>
       </c>
       <c r="AD2">
         <v>44.99066565</v>
       </c>
       <c r="AE2">
-        <v>0.01081937</v>
+        <v>0.01081937014</v>
       </c>
       <c r="AF2">
         <v>90.00509230999999</v>
@@ -682,10 +682,10 @@
         <v>6492.158778</v>
       </c>
       <c r="AK2">
-        <v>0.00058558</v>
+        <v>0.0005855797274</v>
       </c>
       <c r="AL2">
-        <v>0.017484349</v>
+        <v>0.01748434864</v>
       </c>
       <c r="AM2">
         <v>49.92665862</v>
@@ -694,7 +694,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO2">
-        <v>0.133322846</v>
+        <v>0.1333228463</v>
       </c>
     </row>
     <row r="3">
@@ -763,37 +763,37 @@
         <v>6.570978128</v>
       </c>
       <c r="S3">
-        <v>0.69733778</v>
+        <v>0.6973377801</v>
       </c>
       <c r="T3">
         <v>74.74840725</v>
       </c>
       <c r="U3">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V3">
-        <v>0.318690804</v>
+        <v>0.3186908037</v>
       </c>
       <c r="W3">
         <v>4.665524789</v>
       </c>
       <c r="X3">
-        <v>0.041818774</v>
+        <v>0.04181877389</v>
       </c>
       <c r="Y3">
-        <v>0.746869303</v>
+        <v>0.7468693034</v>
       </c>
       <c r="Z3">
-        <v>0.041818774</v>
+        <v>0.04181877389</v>
       </c>
       <c r="AA3">
-        <v>0.451837662</v>
+        <v>0.4518376615</v>
       </c>
       <c r="AB3">
-        <v>0.666519418</v>
+        <v>0.6665194179</v>
       </c>
       <c r="AC3">
-        <v>0.080349885</v>
+        <v>0.08034988547999999</v>
       </c>
       <c r="AD3">
         <v>89.99558777999999</v>
@@ -817,10 +817,10 @@
         <v>6945.496465</v>
       </c>
       <c r="AK3">
-        <v>0.002807361</v>
+        <v>0.002807360738</v>
       </c>
       <c r="AL3">
-        <v>0.016818941</v>
+        <v>0.01681894117</v>
       </c>
       <c r="AM3">
         <v>13.83171789</v>
@@ -829,7 +829,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO3">
-        <v>0.443702823</v>
+        <v>0.4437028233</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
         <v>399.6521136</v>
       </c>
       <c r="O4">
-        <v>0.138457662</v>
+        <v>0.1384576616</v>
       </c>
       <c r="P4">
         <v>594.0356977</v>
@@ -898,13 +898,13 @@
         <v>5.662374686</v>
       </c>
       <c r="S4">
-        <v>0.61124376</v>
+        <v>0.6112437598</v>
       </c>
       <c r="T4">
         <v>85.50156405</v>
       </c>
       <c r="U4">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V4">
         <v>0.372205708</v>
@@ -913,22 +913,22 @@
         <v>5.960471374</v>
       </c>
       <c r="X4">
-        <v>0.041059843</v>
+        <v>0.04105984277</v>
       </c>
       <c r="Y4">
-        <v>0.635072564</v>
+        <v>0.6350725639</v>
       </c>
       <c r="Z4">
-        <v>0.041059843</v>
+        <v>0.04105984277</v>
       </c>
       <c r="AA4">
-        <v>0.380612255</v>
+        <v>0.3806122545</v>
       </c>
       <c r="AB4">
-        <v>0.546598671</v>
+        <v>0.5465986711</v>
       </c>
       <c r="AC4">
-        <v>0.088473893</v>
+        <v>0.08847389275</v>
       </c>
       <c r="AD4">
         <v>90.00049955</v>
@@ -952,10 +952,10 @@
         <v>7121.220991</v>
       </c>
       <c r="AK4">
-        <v>0.001736147</v>
+        <v>0.0017361474</v>
       </c>
       <c r="AL4">
-        <v>0.017873197</v>
+        <v>0.01787319695</v>
       </c>
       <c r="AM4">
         <v>19.82068691</v>
@@ -964,7 +964,7 @@
         <v>1.49503139</v>
       </c>
       <c r="AO4">
-        <v>0.949429685</v>
+        <v>0.9494296848</v>
       </c>
     </row>
     <row r="5">
@@ -1003,7 +1003,7 @@
         <v>535.8292596</v>
       </c>
       <c r="I5">
-        <v>0.30662948</v>
+        <v>0.3066294796</v>
       </c>
       <c r="J5">
         <v>3.504881576</v>
@@ -1033,13 +1033,13 @@
         <v>5.69363755</v>
       </c>
       <c r="S5">
-        <v>0.648431761</v>
+        <v>0.6484317613</v>
       </c>
       <c r="T5">
         <v>57.75130496</v>
       </c>
       <c r="U5">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V5">
         <v>0.324198925</v>
@@ -1048,22 +1048,22 @@
         <v>4.854969956</v>
       </c>
       <c r="X5">
-        <v>0.033058494</v>
+        <v>0.03305849431</v>
       </c>
       <c r="Y5">
-        <v>0.7030889259999999</v>
+        <v>0.7030889261</v>
       </c>
       <c r="Z5">
-        <v>0.033058494</v>
+        <v>0.03305849431</v>
       </c>
       <c r="AA5">
-        <v>0.467087613</v>
+        <v>0.4670876133</v>
       </c>
       <c r="AB5">
-        <v>0.649042586</v>
+        <v>0.6490425864</v>
       </c>
       <c r="AC5">
-        <v>0.05404634</v>
+        <v>0.05404633971</v>
       </c>
       <c r="AD5">
         <v>44.98490159</v>
@@ -1087,10 +1087,10 @@
         <v>6632.411999</v>
       </c>
       <c r="AK5">
-        <v>0.002383401</v>
+        <v>0.00238340124</v>
       </c>
       <c r="AL5">
-        <v>0.016669345</v>
+        <v>0.01666934487</v>
       </c>
       <c r="AM5">
         <v>13.0605013</v>
@@ -1099,7 +1099,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO5">
-        <v>0.313567187</v>
+        <v>0.3135671868</v>
       </c>
     </row>
     <row r="6">
@@ -1138,7 +1138,7 @@
         <v>461.3624847</v>
       </c>
       <c r="I6">
-        <v>0.364424196</v>
+        <v>0.3644241958</v>
       </c>
       <c r="J6">
         <v>3.438281754</v>
@@ -1168,37 +1168,37 @@
         <v>6.10753735</v>
       </c>
       <c r="S6">
-        <v>0.681078536</v>
+        <v>0.6810785363</v>
       </c>
       <c r="T6">
         <v>86.25057710999999</v>
       </c>
       <c r="U6">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V6">
-        <v>0.317969462</v>
+        <v>0.3179694623</v>
       </c>
       <c r="W6">
         <v>4.701684148</v>
       </c>
       <c r="X6">
-        <v>0.030148621</v>
+        <v>0.03014862059</v>
       </c>
       <c r="Y6">
-        <v>0.598367477</v>
+        <v>0.5983674765</v>
       </c>
       <c r="Z6">
-        <v>0.030148621</v>
+        <v>0.03014862059</v>
       </c>
       <c r="AA6">
-        <v>0.400553848</v>
+        <v>0.4005538481</v>
       </c>
       <c r="AB6">
-        <v>0.551419814</v>
+        <v>0.5514198143</v>
       </c>
       <c r="AC6">
-        <v>0.046947662</v>
+        <v>0.04694766218</v>
       </c>
       <c r="AD6">
         <v>89.99058392000001</v>
@@ -1222,19 +1222,19 @@
         <v>6748.033798</v>
       </c>
       <c r="AK6">
-        <v>0.002473629</v>
+        <v>0.002473628671</v>
       </c>
       <c r="AL6">
-        <v>0.016869024</v>
+        <v>0.01686902362</v>
       </c>
       <c r="AM6">
         <v>13.10260134</v>
       </c>
       <c r="AN6">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO6">
-        <v>0.177368041</v>
+        <v>0.1773680407</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
         <v>537.4528483</v>
       </c>
       <c r="I7">
-        <v>-0.333985725</v>
+        <v>-0.3339857246</v>
       </c>
       <c r="J7">
         <v>4.060290192</v>
@@ -1303,37 +1303,37 @@
         <v>5.961985451</v>
       </c>
       <c r="S7">
-        <v>0.674363193</v>
+        <v>0.6743631927</v>
       </c>
       <c r="T7">
         <v>86.99719416000001</v>
       </c>
       <c r="U7">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V7">
-        <v>0.406017052</v>
+        <v>0.4060170515</v>
       </c>
       <c r="W7">
         <v>7.404031275</v>
       </c>
       <c r="X7">
-        <v>0.024039964</v>
+        <v>0.02403996445</v>
       </c>
       <c r="Y7">
-        <v>0.698275483</v>
+        <v>0.6982754828</v>
       </c>
       <c r="Z7">
-        <v>0.024039964</v>
+        <v>0.02403996445</v>
       </c>
       <c r="AA7">
-        <v>0.456522293</v>
+        <v>0.4565222931</v>
       </c>
       <c r="AB7">
-        <v>0.627742532</v>
+        <v>0.6277425315</v>
       </c>
       <c r="AC7">
-        <v>0.070532951</v>
+        <v>0.07053295125</v>
       </c>
       <c r="AD7">
         <v>45.01407039</v>
@@ -1357,19 +1357,19 @@
         <v>7054.717255</v>
       </c>
       <c r="AK7">
-        <v>0.001293233</v>
+        <v>0.001293232514</v>
       </c>
       <c r="AL7">
-        <v>0.017108488</v>
+        <v>0.01710848802</v>
       </c>
       <c r="AM7">
         <v>26.90326537</v>
       </c>
       <c r="AN7">
-        <v>0.889334407</v>
+        <v>0.8893344066</v>
       </c>
       <c r="AO7">
-        <v>0.290853147</v>
+        <v>0.2908531468</v>
       </c>
     </row>
     <row r="8">
@@ -1408,7 +1408,7 @@
         <v>539.9840836</v>
       </c>
       <c r="I8">
-        <v>-0.304824558</v>
+        <v>-0.3048245575</v>
       </c>
       <c r="J8">
         <v>8.520845771999999</v>
@@ -1426,7 +1426,7 @@
         <v>372.9492162</v>
       </c>
       <c r="O8">
-        <v>0.120573974</v>
+        <v>0.1205739737</v>
       </c>
       <c r="P8">
         <v>572.0733026</v>
@@ -1438,43 +1438,43 @@
         <v>6.019787637</v>
       </c>
       <c r="S8">
-        <v>0.727769559</v>
+        <v>0.7277695592</v>
       </c>
       <c r="T8">
         <v>3.737033889</v>
       </c>
       <c r="U8">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V8">
-        <v>0.326253647</v>
+        <v>0.3262536467</v>
       </c>
       <c r="W8">
         <v>4.692863466</v>
       </c>
       <c r="X8">
-        <v>0.035175898</v>
+        <v>0.03517589837</v>
       </c>
       <c r="Y8">
-        <v>0.607252923</v>
+        <v>0.6072529225</v>
       </c>
       <c r="Z8">
-        <v>0.035175898</v>
+        <v>0.03517589837</v>
       </c>
       <c r="AA8">
-        <v>0.369590638</v>
+        <v>0.3695906382</v>
       </c>
       <c r="AB8">
-        <v>0.532056133</v>
+        <v>0.5320561324999999</v>
       </c>
       <c r="AC8">
-        <v>0.07519679</v>
+        <v>0.07519678993999999</v>
       </c>
       <c r="AD8">
         <v>89.99521581</v>
       </c>
       <c r="AE8">
-        <v>0.016554384</v>
+        <v>0.01655438439</v>
       </c>
       <c r="AF8">
         <v>45.0192746</v>
@@ -1492,10 +1492,10 @@
         <v>6799.609241</v>
       </c>
       <c r="AK8">
-        <v>0.002106224</v>
+        <v>0.00210622374</v>
       </c>
       <c r="AL8">
-        <v>0.017560547</v>
+        <v>0.01756054661</v>
       </c>
       <c r="AM8">
         <v>15.39682273</v>
@@ -1543,7 +1543,7 @@
         <v>588.5908686</v>
       </c>
       <c r="I9">
-        <v>0.307244133</v>
+        <v>0.3072441328</v>
       </c>
       <c r="J9">
         <v>3.674228689</v>
@@ -1573,37 +1573,37 @@
         <v>5.260780714</v>
       </c>
       <c r="S9">
-        <v>0.651505986</v>
+        <v>0.6515059861</v>
       </c>
       <c r="T9">
         <v>154.9948161</v>
       </c>
       <c r="U9">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V9">
-        <v>0.675609583</v>
+        <v>0.6756095828000001</v>
       </c>
       <c r="W9">
         <v>17.56141901</v>
       </c>
       <c r="X9">
-        <v>0.037076995</v>
+        <v>0.03707699527</v>
       </c>
       <c r="Y9">
-        <v>0.771394562</v>
+        <v>0.7713945615</v>
       </c>
       <c r="Z9">
-        <v>0.037076995</v>
+        <v>0.03707699527</v>
       </c>
       <c r="AA9">
-        <v>0.504434007</v>
+        <v>0.5044340074</v>
       </c>
       <c r="AB9">
-        <v>0.710492406</v>
+        <v>0.7104924061</v>
       </c>
       <c r="AC9">
-        <v>0.060902155</v>
+        <v>0.0609021554</v>
       </c>
       <c r="AD9">
         <v>44.96265715</v>
@@ -1627,10 +1627,10 @@
         <v>6332.729893</v>
       </c>
       <c r="AK9">
-        <v>0.001431175</v>
+        <v>0.001431175296</v>
       </c>
       <c r="AL9">
-        <v>0.017630593</v>
+        <v>0.01763059265</v>
       </c>
       <c r="AM9">
         <v>60.36009183</v>
@@ -1639,7 +1639,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO9">
-        <v>0.317567892</v>
+        <v>0.3175678915</v>
       </c>
     </row>
     <row r="10">
@@ -1678,7 +1678,7 @@
         <v>418.1911344</v>
       </c>
       <c r="I10">
-        <v>-0.274824572</v>
+        <v>-0.2748245721</v>
       </c>
       <c r="J10">
         <v>3.861412347</v>
@@ -1708,37 +1708,37 @@
         <v>5.350888373</v>
       </c>
       <c r="S10">
-        <v>0.720703658</v>
+        <v>0.7207036583999999</v>
       </c>
       <c r="T10">
         <v>73.24679519999999</v>
       </c>
       <c r="U10">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V10">
-        <v>0.312574246</v>
+        <v>0.3125742457</v>
       </c>
       <c r="W10">
         <v>4.595304171</v>
       </c>
       <c r="X10">
-        <v>0.019791675</v>
+        <v>0.01979167513</v>
       </c>
       <c r="Y10">
-        <v>0.530865831</v>
+        <v>0.5308658305</v>
       </c>
       <c r="Z10">
-        <v>0.019791675</v>
+        <v>0.01979167513</v>
       </c>
       <c r="AA10">
-        <v>0.360408029</v>
+        <v>0.3604080293</v>
       </c>
       <c r="AB10">
-        <v>0.476946261</v>
+        <v>0.4769462606</v>
       </c>
       <c r="AC10">
-        <v>0.05391957</v>
+        <v>0.05391956989</v>
       </c>
       <c r="AD10">
         <v>90.00599378</v>
@@ -1762,10 +1762,10 @@
         <v>7388.894195</v>
       </c>
       <c r="AK10">
-        <v>0.001747257</v>
+        <v>0.001747257457</v>
       </c>
       <c r="AL10">
-        <v>0.016985223</v>
+        <v>0.0169852232</v>
       </c>
       <c r="AM10">
         <v>13.21267267</v>
@@ -1813,7 +1813,7 @@
         <v>503.4285743</v>
       </c>
       <c r="I11">
-        <v>0.323561465</v>
+        <v>0.3235614654</v>
       </c>
       <c r="J11">
         <v>5.524179616</v>
@@ -1831,7 +1831,7 @@
         <v>368.7360754</v>
       </c>
       <c r="O11">
-        <v>0.455756306</v>
+        <v>0.4557563058</v>
       </c>
       <c r="P11">
         <v>572.6412771</v>
@@ -1843,37 +1843,37 @@
         <v>5.655654493</v>
       </c>
       <c r="S11">
-        <v>0.827604139</v>
+        <v>0.8276041391</v>
       </c>
       <c r="T11">
         <v>65.50174826999999</v>
       </c>
       <c r="U11">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V11">
-        <v>0.370337532</v>
+        <v>0.3703375321</v>
       </c>
       <c r="W11">
         <v>6.251337261</v>
       </c>
       <c r="X11">
-        <v>0.035547006</v>
+        <v>0.03554700628</v>
       </c>
       <c r="Y11">
         <v>0.6082180700000001</v>
       </c>
       <c r="Z11">
-        <v>0.035547006</v>
+        <v>0.03554700628</v>
       </c>
       <c r="AA11">
-        <v>0.38038697</v>
+        <v>0.3803869698</v>
       </c>
       <c r="AB11">
-        <v>0.542831917</v>
+        <v>0.5428319169</v>
       </c>
       <c r="AC11">
-        <v>0.065386153</v>
+        <v>0.0653861531</v>
       </c>
       <c r="AD11">
         <v>89.9983581</v>
@@ -1897,10 +1897,10 @@
         <v>8312.423063</v>
       </c>
       <c r="AK11">
-        <v>0.002688262</v>
+        <v>0.002688262227</v>
       </c>
       <c r="AL11">
-        <v>0.017217686</v>
+        <v>0.01721768627</v>
       </c>
       <c r="AM11">
         <v>20.59179929</v>
@@ -1909,7 +1909,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO11">
-        <v>0.464404327</v>
+        <v>0.4644043272</v>
       </c>
     </row>
     <row r="12">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="F12">
-        <v>10.08109182</v>
+        <v>10.08824448</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1945,106 +1945,106 @@
         </is>
       </c>
       <c r="H12">
-        <v>510.7015034</v>
+        <v>512.2201753000001</v>
       </c>
       <c r="I12">
-        <v>-0.101717998</v>
+        <v>-0.09966996307000001</v>
       </c>
       <c r="J12">
-        <v>4.289308911</v>
+        <v>4.304960793</v>
       </c>
       <c r="K12">
-        <v>2246.323916</v>
+        <v>2253.609291</v>
       </c>
       <c r="L12">
-        <v>2239.281387</v>
+        <v>2230.862732</v>
       </c>
       <c r="M12">
-        <v>4485.605303</v>
+        <v>4484.472023</v>
       </c>
       <c r="N12">
-        <v>383.5872565</v>
+        <v>384.4984961</v>
       </c>
       <c r="O12">
-        <v>1.047148059</v>
+        <v>1.037037881</v>
       </c>
       <c r="P12">
-        <v>601.0761277</v>
+        <v>601.9498655</v>
       </c>
       <c r="Q12">
-        <v>1134.637968</v>
+        <v>1139.146897</v>
       </c>
       <c r="R12">
-        <v>5.036067516</v>
+        <v>5.046714171</v>
       </c>
       <c r="S12">
-        <v>0.596400251</v>
+        <v>0.5970352916</v>
       </c>
       <c r="T12">
-        <v>67.24925881</v>
+        <v>67.24245621999999</v>
       </c>
       <c r="U12">
-        <v>0.424637257</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V12">
-        <v>0.324830529</v>
+        <v>0.3248099599</v>
       </c>
       <c r="W12">
-        <v>4.878476929</v>
+        <v>4.878310548</v>
       </c>
       <c r="X12">
-        <v>0.030656931</v>
+        <v>0.03088021978</v>
       </c>
       <c r="Y12">
-        <v>0.631713655</v>
+        <v>0.6328454941</v>
       </c>
       <c r="Z12">
-        <v>0.030656931</v>
+        <v>0.03088021978</v>
       </c>
       <c r="AA12">
-        <v>0.405932218</v>
+        <v>0.406589222</v>
       </c>
       <c r="AB12">
-        <v>0.5619703069999999</v>
+        <v>0.5628513265</v>
       </c>
       <c r="AC12">
-        <v>0.069743348</v>
+        <v>0.06999416761</v>
       </c>
       <c r="AD12">
-        <v>90.00229208</v>
+        <v>90.00271576</v>
       </c>
       <c r="AE12">
-        <v>0.001037538</v>
+        <v>45.01005606</v>
       </c>
       <c r="AF12">
-        <v>44.99882789</v>
+        <v>0.001469183534</v>
       </c>
       <c r="AG12">
-        <v>58.09335391</v>
+        <v>58.22129712</v>
       </c>
       <c r="AH12">
-        <v>5079.120509</v>
+        <v>5093.61031</v>
       </c>
       <c r="AI12">
-        <v>2015.012995</v>
+        <v>2021.241445</v>
       </c>
       <c r="AJ12">
-        <v>7508.532352</v>
+        <v>7510.252923</v>
       </c>
       <c r="AK12">
-        <v>0.000678735</v>
+        <v>0.0006646227288999999</v>
       </c>
       <c r="AL12">
-        <v>0.017501358</v>
+        <v>0.01749656662</v>
       </c>
       <c r="AM12">
-        <v>14.13784574</v>
+        <v>14.28453706</v>
       </c>
       <c r="AN12">
-        <v>1.07962932</v>
+        <v>1.15307539</v>
       </c>
       <c r="AO12">
-        <v>0.330980324</v>
+        <v>0.3378935383</v>
       </c>
     </row>
     <row r="13">
@@ -2083,7 +2083,7 @@
         <v>484.9841795</v>
       </c>
       <c r="I13">
-        <v>0.017359287</v>
+        <v>0.01735928726</v>
       </c>
       <c r="J13">
         <v>3.09126278</v>
@@ -2119,31 +2119,31 @@
         <v>69.25657594</v>
       </c>
       <c r="U13">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V13">
-        <v>0.309376363</v>
+        <v>0.3093763631</v>
       </c>
       <c r="W13">
         <v>4.488861045</v>
       </c>
       <c r="X13">
-        <v>0.023435281</v>
+        <v>0.02343528147</v>
       </c>
       <c r="Y13">
-        <v>0.64233216</v>
+        <v>0.6423321598</v>
       </c>
       <c r="Z13">
-        <v>0.023435281</v>
+        <v>0.02343528147</v>
       </c>
       <c r="AA13">
-        <v>0.425276767</v>
+        <v>0.4252767668</v>
       </c>
       <c r="AB13">
-        <v>0.586744753</v>
+        <v>0.5867447531</v>
       </c>
       <c r="AC13">
-        <v>0.055587407</v>
+        <v>0.05558740676</v>
       </c>
       <c r="AD13">
         <v>90.00294669</v>
@@ -2167,10 +2167,10 @@
         <v>7731.862037</v>
       </c>
       <c r="AK13">
-        <v>0.002130977</v>
+        <v>0.00213097714</v>
       </c>
       <c r="AL13">
-        <v>0.017176761</v>
+        <v>0.01717676117</v>
       </c>
       <c r="AM13">
         <v>11.53373567</v>
@@ -2179,7 +2179,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO13">
-        <v>0.200440044</v>
+        <v>0.2004400441</v>
       </c>
     </row>
     <row r="14">
@@ -2218,7 +2218,7 @@
         <v>387.299794</v>
       </c>
       <c r="I14">
-        <v>0.079794769</v>
+        <v>0.07979476923000001</v>
       </c>
       <c r="J14">
         <v>3.500776241</v>
@@ -2254,31 +2254,31 @@
         <v>87.74501932</v>
       </c>
       <c r="U14">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V14">
-        <v>0.318727306</v>
+        <v>0.3187273061</v>
       </c>
       <c r="W14">
         <v>4.777423368</v>
       </c>
       <c r="X14">
-        <v>0.022182279</v>
+        <v>0.02218227862</v>
       </c>
       <c r="Y14">
-        <v>0.50416376</v>
+        <v>0.5041637596</v>
       </c>
       <c r="Z14">
-        <v>0.022182279</v>
+        <v>0.02218227862</v>
       </c>
       <c r="AA14">
-        <v>0.32821547</v>
+        <v>0.3282154699</v>
       </c>
       <c r="AB14">
-        <v>0.459492481</v>
+        <v>0.4594924808</v>
       </c>
       <c r="AC14">
-        <v>0.044671279</v>
+        <v>0.04467127885</v>
       </c>
       <c r="AD14">
         <v>89.98919463999999</v>
@@ -2302,19 +2302,19 @@
         <v>6638.707642</v>
       </c>
       <c r="AK14">
-        <v>0.002563995</v>
+        <v>0.002563995152</v>
       </c>
       <c r="AL14">
-        <v>0.016810413</v>
+        <v>0.01681041264</v>
       </c>
       <c r="AM14">
         <v>13.38708385</v>
       </c>
       <c r="AN14">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO14">
-        <v>0.13596104</v>
+        <v>0.1359610398</v>
       </c>
     </row>
     <row r="15">
@@ -2353,7 +2353,7 @@
         <v>521.4110425</v>
       </c>
       <c r="I15">
-        <v>0.378419677</v>
+        <v>0.3784196771</v>
       </c>
       <c r="J15">
         <v>5.334335944</v>
@@ -2371,7 +2371,7 @@
         <v>382.9884276</v>
       </c>
       <c r="O15">
-        <v>0.559228817</v>
+        <v>0.5592288168</v>
       </c>
       <c r="P15">
         <v>596.4435599</v>
@@ -2383,37 +2383,37 @@
         <v>5.804250165</v>
       </c>
       <c r="S15">
-        <v>0.826010962</v>
+        <v>0.8260109616</v>
       </c>
       <c r="T15">
         <v>64.99888462</v>
       </c>
       <c r="U15">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V15">
-        <v>0.364012803</v>
+        <v>0.3640128028</v>
       </c>
       <c r="W15">
         <v>6.023867001</v>
       </c>
       <c r="X15">
-        <v>0.037262762</v>
+        <v>0.03726276208</v>
       </c>
       <c r="Y15">
-        <v>0.63370518</v>
+        <v>0.6337051803</v>
       </c>
       <c r="Z15">
-        <v>0.037262762</v>
+        <v>0.03726276208</v>
       </c>
       <c r="AA15">
-        <v>0.396924961</v>
+        <v>0.3969249607</v>
       </c>
       <c r="AB15">
-        <v>0.566593414</v>
+        <v>0.5665934141</v>
       </c>
       <c r="AC15">
-        <v>0.067111766</v>
+        <v>0.06711176620000001</v>
       </c>
       <c r="AD15">
         <v>90.01348286</v>
@@ -2422,7 +2422,7 @@
         <v>63.5669445</v>
       </c>
       <c r="AF15">
-        <v>0.014833567</v>
+        <v>0.0148335673</v>
       </c>
       <c r="AG15">
         <v>84.32437627</v>
@@ -2437,10 +2437,10 @@
         <v>7635.045151</v>
       </c>
       <c r="AK15">
-        <v>0.002549388</v>
+        <v>0.002549388052</v>
       </c>
       <c r="AL15">
-        <v>0.017162539</v>
+        <v>0.01716253874</v>
       </c>
       <c r="AM15">
         <v>17.57738677</v>
@@ -2449,7 +2449,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO15">
-        <v>0.376689081</v>
+        <v>0.3766890808</v>
       </c>
     </row>
     <row r="16">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="F16">
-        <v>11.1454831</v>
+        <v>11.14298079</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2485,106 +2485,106 @@
         </is>
       </c>
       <c r="H16">
-        <v>471.8760562</v>
+        <v>472.0478012</v>
       </c>
       <c r="I16">
-        <v>0.23638473</v>
+        <v>0.2362752215</v>
       </c>
       <c r="J16">
-        <v>3.542046096</v>
+        <v>3.540442234</v>
       </c>
       <c r="K16">
-        <v>2052.532945</v>
+        <v>2051.318716</v>
       </c>
       <c r="L16">
-        <v>1662.684441</v>
+        <v>1665.112899</v>
       </c>
       <c r="M16">
-        <v>3715.217386</v>
+        <v>3716.431615</v>
       </c>
       <c r="N16">
-        <v>367.4514431</v>
+        <v>367.611456</v>
       </c>
       <c r="O16">
-        <v>2.126713574</v>
+        <v>2.140659196</v>
       </c>
       <c r="P16">
-        <v>587.2732321</v>
+        <v>587.6218768</v>
       </c>
       <c r="Q16">
-        <v>887.4721883</v>
+        <v>887.5684413</v>
       </c>
       <c r="R16">
-        <v>5.552590159</v>
+        <v>5.552753927</v>
       </c>
       <c r="S16">
-        <v>0.880205832</v>
+        <v>0.8801928845</v>
       </c>
       <c r="T16">
-        <v>42.24951719</v>
+        <v>103.2417575</v>
       </c>
       <c r="U16">
-        <v>0.424637257</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V16">
-        <v>0.386158832</v>
+        <v>0.3862276892</v>
       </c>
       <c r="W16">
-        <v>6.784148269</v>
+        <v>6.786169011</v>
       </c>
       <c r="X16">
-        <v>0.029085805</v>
+        <v>0.02909452861</v>
       </c>
       <c r="Y16">
-        <v>0.616378911</v>
+        <v>0.6167100563</v>
       </c>
       <c r="Z16">
-        <v>0.029085805</v>
+        <v>0.02909452861</v>
       </c>
       <c r="AA16">
-        <v>0.410529343</v>
+        <v>0.4105539773</v>
       </c>
       <c r="AB16">
-        <v>0.565710888</v>
+        <v>0.5660100488000001</v>
       </c>
       <c r="AC16">
-        <v>0.050668023</v>
+        <v>0.05070000753</v>
       </c>
       <c r="AD16">
-        <v>0.020452672</v>
+        <v>0.02097411398</v>
       </c>
       <c r="AE16">
-        <v>89.99623647</v>
+        <v>89.99718401</v>
       </c>
       <c r="AF16">
-        <v>44.9851579</v>
+        <v>45.01171114</v>
       </c>
       <c r="AG16">
-        <v>92.02933692000001</v>
+        <v>91.96019491</v>
       </c>
       <c r="AH16">
-        <v>3540.044595</v>
+        <v>3539.397006</v>
       </c>
       <c r="AI16">
-        <v>1786.952629</v>
+        <v>1784.881746</v>
       </c>
       <c r="AJ16">
-        <v>7704.171062</v>
+        <v>7706.044736</v>
       </c>
       <c r="AK16">
-        <v>0.001504958</v>
+        <v>0.001536963676</v>
       </c>
       <c r="AL16">
-        <v>0.017026516</v>
+        <v>0.01701609431</v>
       </c>
       <c r="AM16">
-        <v>20.52295659</v>
+        <v>20.4957211</v>
       </c>
       <c r="AN16">
-        <v>0.948177231</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO16">
-        <v>0.169493358</v>
+        <v>0.1659137112</v>
       </c>
     </row>
     <row r="17">
@@ -2623,7 +2623,7 @@
         <v>471.8481138</v>
       </c>
       <c r="I17">
-        <v>-0.03028752</v>
+        <v>-0.03028751984</v>
       </c>
       <c r="J17">
         <v>3.110815759</v>
@@ -2653,37 +2653,37 @@
         <v>5.336796261</v>
       </c>
       <c r="S17">
-        <v>0.667728633</v>
+        <v>0.6677286332</v>
       </c>
       <c r="T17">
         <v>50.99396777</v>
       </c>
       <c r="U17">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V17">
-        <v>0.325576428</v>
+        <v>0.3255764283</v>
       </c>
       <c r="W17">
         <v>4.955007873</v>
       </c>
       <c r="X17">
-        <v>0.022410515</v>
+        <v>0.02241051508</v>
       </c>
       <c r="Y17">
-        <v>0.627681811</v>
+        <v>0.6276818111</v>
       </c>
       <c r="Z17">
-        <v>0.022410515</v>
+        <v>0.02241051508</v>
       </c>
       <c r="AA17">
-        <v>0.410265226</v>
+        <v>0.4102652263</v>
       </c>
       <c r="AB17">
-        <v>0.5715046580000001</v>
+        <v>0.5715046582</v>
       </c>
       <c r="AC17">
-        <v>0.056177153</v>
+        <v>0.05617715287</v>
       </c>
       <c r="AD17">
         <v>63.53787504</v>
@@ -2707,10 +2707,10 @@
         <v>7696.915631</v>
       </c>
       <c r="AK17">
-        <v>0.002408372</v>
+        <v>0.002408372343</v>
       </c>
       <c r="AL17">
-        <v>0.017208084</v>
+        <v>0.01720808354</v>
       </c>
       <c r="AM17">
         <v>13.65012657</v>
@@ -2719,7 +2719,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO17">
-        <v>0.147885845</v>
+        <v>0.1478858446</v>
       </c>
     </row>
     <row r="18">
@@ -2758,7 +2758,7 @@
         <v>548.0495092</v>
       </c>
       <c r="I18">
-        <v>-0.18746267</v>
+        <v>-0.1874626698</v>
       </c>
       <c r="J18">
         <v>3.186759226</v>
@@ -2788,13 +2788,13 @@
         <v>6.49623193</v>
       </c>
       <c r="S18">
-        <v>0.860070329</v>
+        <v>0.8600703289</v>
       </c>
       <c r="T18">
         <v>132.2503093</v>
       </c>
       <c r="U18">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V18">
         <v>0.333193916</v>
@@ -2803,22 +2803,22 @@
         <v>5.162452275</v>
       </c>
       <c r="X18">
-        <v>0.025620585</v>
+        <v>0.02562058476</v>
       </c>
       <c r="Y18">
-        <v>0.687049935</v>
+        <v>0.6870499348</v>
       </c>
       <c r="Z18">
-        <v>0.025620585</v>
+        <v>0.02562058476</v>
       </c>
       <c r="AA18">
-        <v>0.490863166</v>
+        <v>0.4908631662</v>
       </c>
       <c r="AB18">
-        <v>0.619655207</v>
+        <v>0.6196552071</v>
       </c>
       <c r="AC18">
-        <v>0.067394728</v>
+        <v>0.06739472769</v>
       </c>
       <c r="AD18">
         <v>90.00216137</v>
@@ -2842,10 +2842,10 @@
         <v>7668.045181</v>
       </c>
       <c r="AK18">
-        <v>0.001883012</v>
+        <v>0.001883012182</v>
       </c>
       <c r="AL18">
-        <v>0.016961578</v>
+        <v>0.01696157831</v>
       </c>
       <c r="AM18">
         <v>15.23046992</v>
@@ -2893,7 +2893,7 @@
         <v>661.5677942</v>
       </c>
       <c r="I19">
-        <v>0.238365114</v>
+        <v>0.2383651136</v>
       </c>
       <c r="J19">
         <v>3.493185053</v>
@@ -2929,31 +2929,31 @@
         <v>71.25125500999999</v>
       </c>
       <c r="U19">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V19">
-        <v>0.33885533</v>
+        <v>0.3388553304</v>
       </c>
       <c r="W19">
         <v>5.244692208</v>
       </c>
       <c r="X19">
-        <v>0.041058775</v>
+        <v>0.04105877466</v>
       </c>
       <c r="Y19">
-        <v>0.888162657</v>
+        <v>0.8881626566</v>
       </c>
       <c r="Z19">
-        <v>0.041058775</v>
+        <v>0.04105877466</v>
       </c>
       <c r="AA19">
-        <v>0.548900733</v>
+        <v>0.5489007326999999</v>
       </c>
       <c r="AB19">
-        <v>0.81521851</v>
+        <v>0.8152185101</v>
       </c>
       <c r="AC19">
-        <v>0.072944146</v>
+        <v>0.07294414649</v>
       </c>
       <c r="AD19">
         <v>44.98925474</v>
@@ -2977,10 +2977,10 @@
         <v>8068.601261</v>
       </c>
       <c r="AK19">
-        <v>0.000741676</v>
+        <v>0.0007416757947000001</v>
       </c>
       <c r="AL19">
-        <v>0.017756059</v>
+        <v>0.01775605854</v>
       </c>
       <c r="AM19">
         <v>15.74455287</v>
@@ -2989,7 +2989,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO19">
-        <v>0.567420752</v>
+        <v>0.5674207524</v>
       </c>
     </row>
     <row r="20">
@@ -3028,7 +3028,7 @@
         <v>519.2917982</v>
       </c>
       <c r="I20">
-        <v>0.008388549</v>
+        <v>0.008388549015</v>
       </c>
       <c r="J20">
         <v>3.362976194</v>
@@ -3058,13 +3058,13 @@
         <v>5.47080351</v>
       </c>
       <c r="S20">
-        <v>0.630659757</v>
+        <v>0.6306597567</v>
       </c>
       <c r="T20">
         <v>92.51457499</v>
       </c>
       <c r="U20">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V20">
         <v>0.301225401</v>
@@ -3073,22 +3073,22 @@
         <v>4.262667829</v>
       </c>
       <c r="X20">
-        <v>0.028399687</v>
+        <v>0.02839968715</v>
       </c>
       <c r="Y20">
-        <v>0.668256652</v>
+        <v>0.6682566522</v>
       </c>
       <c r="Z20">
-        <v>0.028399687</v>
+        <v>0.02839968715</v>
       </c>
       <c r="AA20">
-        <v>0.449801068</v>
+        <v>0.4498010684</v>
       </c>
       <c r="AB20">
-        <v>0.605295621</v>
+        <v>0.6052956213</v>
       </c>
       <c r="AC20">
-        <v>0.062961031</v>
+        <v>0.06296103097</v>
       </c>
       <c r="AD20">
         <v>90.00556184</v>
@@ -3112,10 +3112,10 @@
         <v>8249.824144</v>
       </c>
       <c r="AK20">
-        <v>0.002493304</v>
+        <v>0.002493304332</v>
       </c>
       <c r="AL20">
-        <v>0.016622752</v>
+        <v>0.01662275187</v>
       </c>
       <c r="AM20">
         <v>11.39144626</v>
@@ -3124,7 +3124,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO20">
-        <v>0.265965647</v>
+        <v>0.2659656469</v>
       </c>
     </row>
     <row r="21">
@@ -3163,7 +3163,7 @@
         <v>564.0463701</v>
       </c>
       <c r="I21">
-        <v>-0.067873302</v>
+        <v>-0.06787330208</v>
       </c>
       <c r="J21">
         <v>3.301562239</v>
@@ -3193,43 +3193,43 @@
         <v>4.859419226</v>
       </c>
       <c r="S21">
-        <v>0.791181599</v>
+        <v>0.7911815992</v>
       </c>
       <c r="T21">
         <v>51.24495329</v>
       </c>
       <c r="U21">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V21">
-        <v>0.37378526</v>
+        <v>0.3737852595</v>
       </c>
       <c r="W21">
         <v>6.256990387</v>
       </c>
       <c r="X21">
-        <v>0.027903157</v>
+        <v>0.02790315737</v>
       </c>
       <c r="Y21">
-        <v>0.710162187</v>
+        <v>0.7101621866</v>
       </c>
       <c r="Z21">
-        <v>0.027903157</v>
+        <v>0.02790315737</v>
       </c>
       <c r="AA21">
-        <v>0.500811715</v>
+        <v>0.5008117147</v>
       </c>
       <c r="AB21">
-        <v>0.641092507</v>
+        <v>0.6410925072</v>
       </c>
       <c r="AC21">
-        <v>0.06906967899999999</v>
+        <v>0.06906967941</v>
       </c>
       <c r="AD21">
         <v>44.97297542</v>
       </c>
       <c r="AE21">
-        <v>0.007793994</v>
+        <v>0.007793994133</v>
       </c>
       <c r="AF21">
         <v>90.00897873</v>
@@ -3247,10 +3247,10 @@
         <v>7039.042073</v>
       </c>
       <c r="AK21">
-        <v>0.000573225</v>
+        <v>0.0005732247993</v>
       </c>
       <c r="AL21">
-        <v>0.01743382</v>
+        <v>0.01743382023</v>
       </c>
       <c r="AM21">
         <v>19.6791778</v>
@@ -3259,7 +3259,7 @@
         <v>1.49503139</v>
       </c>
       <c r="AO21">
-        <v>0.447417379</v>
+        <v>0.4474173785</v>
       </c>
     </row>
     <row r="22">
@@ -3298,7 +3298,7 @@
         <v>620.4114056</v>
       </c>
       <c r="I22">
-        <v>-0.159452565</v>
+        <v>-0.1594525648</v>
       </c>
       <c r="J22">
         <v>3.102289955</v>
@@ -3328,13 +3328,13 @@
         <v>5.935100543</v>
       </c>
       <c r="S22">
-        <v>0.812082788</v>
+        <v>0.8120827881</v>
       </c>
       <c r="T22">
         <v>50.74145054</v>
       </c>
       <c r="U22">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V22">
         <v>0.714250804</v>
@@ -3343,28 +3343,28 @@
         <v>19.96640139</v>
       </c>
       <c r="X22">
-        <v>0.029057544</v>
+        <v>0.02905754353</v>
       </c>
       <c r="Y22">
-        <v>0.789625263</v>
+        <v>0.7896252634000001</v>
       </c>
       <c r="Z22">
-        <v>0.029057544</v>
+        <v>0.02905754353</v>
       </c>
       <c r="AA22">
-        <v>0.558417006</v>
+        <v>0.5584170063</v>
       </c>
       <c r="AB22">
         <v>0.715195777</v>
       </c>
       <c r="AC22">
-        <v>0.074429486</v>
+        <v>0.07442948639999999</v>
       </c>
       <c r="AD22">
         <v>89.97403188</v>
       </c>
       <c r="AE22">
-        <v>0.001899651</v>
+        <v>0.001899650606</v>
       </c>
       <c r="AF22">
         <v>26.46854869</v>
@@ -3382,19 +3382,19 @@
         <v>6659.713418</v>
       </c>
       <c r="AK22">
-        <v>0.00152118</v>
+        <v>0.00152117973</v>
       </c>
       <c r="AL22">
-        <v>0.017437696</v>
+        <v>0.01743769648</v>
       </c>
       <c r="AM22">
         <v>64.81045314000001</v>
       </c>
       <c r="AN22">
-        <v>0.889334407</v>
+        <v>0.8893344066</v>
       </c>
       <c r="AO22">
-        <v>0.243645142</v>
+        <v>0.2436451422</v>
       </c>
     </row>
     <row r="23">
@@ -3433,7 +3433,7 @@
         <v>694.0895814</v>
       </c>
       <c r="I23">
-        <v>0.303932189</v>
+        <v>0.3039321889</v>
       </c>
       <c r="J23">
         <v>3.609368521</v>
@@ -3463,37 +3463,37 @@
         <v>6.040427342</v>
       </c>
       <c r="S23">
-        <v>0.727976379</v>
+        <v>0.7279763794</v>
       </c>
       <c r="T23">
         <v>148.7538807</v>
       </c>
       <c r="U23">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V23">
-        <v>0.536307381</v>
+        <v>0.5363073806999999</v>
       </c>
       <c r="W23">
         <v>11.78032782</v>
       </c>
       <c r="X23">
-        <v>0.043204735</v>
+        <v>0.04320473483</v>
       </c>
       <c r="Y23">
-        <v>0.938366059</v>
+        <v>0.9383660592</v>
       </c>
       <c r="Z23">
-        <v>0.043204735</v>
+        <v>0.04320473483</v>
       </c>
       <c r="AA23">
-        <v>0.572213267</v>
+        <v>0.5722132674</v>
       </c>
       <c r="AB23">
-        <v>0.862711286</v>
+        <v>0.8627112862</v>
       </c>
       <c r="AC23">
-        <v>0.07565477299999999</v>
+        <v>0.07565477298000001</v>
       </c>
       <c r="AD23">
         <v>135.017562</v>
@@ -3502,7 +3502,7 @@
         <v>90.01076676</v>
       </c>
       <c r="AF23">
-        <v>0.030672247</v>
+        <v>0.03067224704</v>
       </c>
       <c r="AG23">
         <v>75.06602556999999</v>
@@ -3517,16 +3517,16 @@
         <v>6694.243065</v>
       </c>
       <c r="AK23">
-        <v>0.000755128</v>
+        <v>0.0007551278542</v>
       </c>
       <c r="AL23">
-        <v>0.017923896</v>
+        <v>0.01792389637</v>
       </c>
       <c r="AM23">
         <v>41.61284652</v>
       </c>
       <c r="AN23">
-        <v>0.889334407</v>
+        <v>0.8893344066</v>
       </c>
       <c r="AO23">
         <v>0.5149618</v>
@@ -3568,7 +3568,7 @@
         <v>501.9184038</v>
       </c>
       <c r="I24">
-        <v>0.011626073</v>
+        <v>0.01162607298</v>
       </c>
       <c r="J24">
         <v>3.25887195</v>
@@ -3598,37 +3598,37 @@
         <v>5.405077641</v>
       </c>
       <c r="S24">
-        <v>0.638797037</v>
+        <v>0.6387970371</v>
       </c>
       <c r="T24">
         <v>93.24863053999999</v>
       </c>
       <c r="U24">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V24">
-        <v>0.314951437</v>
+        <v>0.3149514373</v>
       </c>
       <c r="W24">
         <v>4.635522315</v>
       </c>
       <c r="X24">
-        <v>0.026504308</v>
+        <v>0.02650430829</v>
       </c>
       <c r="Y24">
         <v>0.655713474</v>
       </c>
       <c r="Z24">
-        <v>0.026504308</v>
+        <v>0.02650430829</v>
       </c>
       <c r="AA24">
-        <v>0.437198186</v>
+        <v>0.4371981864</v>
       </c>
       <c r="AB24">
-        <v>0.596004117</v>
+        <v>0.5960041167</v>
       </c>
       <c r="AC24">
-        <v>0.059709357</v>
+        <v>0.05970935723</v>
       </c>
       <c r="AD24">
         <v>90.00597908</v>
@@ -3652,10 +3652,10 @@
         <v>6897.993574</v>
       </c>
       <c r="AK24">
-        <v>0.002630952</v>
+        <v>0.002630952126</v>
       </c>
       <c r="AL24">
-        <v>0.016636116</v>
+        <v>0.01663611613</v>
       </c>
       <c r="AM24">
         <v>12.71700486</v>
@@ -3664,7 +3664,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO24">
-        <v>0.213235069</v>
+        <v>0.2132350694</v>
       </c>
     </row>
     <row r="25">
@@ -3703,7 +3703,7 @@
         <v>509.961186</v>
       </c>
       <c r="I25">
-        <v>-0.141831394</v>
+        <v>-0.1418313935</v>
       </c>
       <c r="J25">
         <v>3.522457213</v>
@@ -3733,37 +3733,37 @@
         <v>4.716368922</v>
       </c>
       <c r="S25">
-        <v>0.782398767</v>
+        <v>0.7823987672</v>
       </c>
       <c r="T25">
         <v>86.50627641</v>
       </c>
       <c r="U25">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V25">
-        <v>0.363628593</v>
+        <v>0.3636285932</v>
       </c>
       <c r="W25">
         <v>6.083900295</v>
       </c>
       <c r="X25">
-        <v>0.024557624</v>
+        <v>0.02455762446</v>
       </c>
       <c r="Y25">
-        <v>0.651595931</v>
+        <v>0.6515959314000001</v>
       </c>
       <c r="Z25">
-        <v>0.024557624</v>
+        <v>0.02455762446</v>
       </c>
       <c r="AA25">
-        <v>0.445640994</v>
+        <v>0.4456409942</v>
       </c>
       <c r="AB25">
-        <v>0.587338504</v>
+        <v>0.5873385035000001</v>
       </c>
       <c r="AC25">
-        <v>0.06425742800000001</v>
+        <v>0.06425742792</v>
       </c>
       <c r="AD25">
         <v>44.99817506</v>
@@ -3772,7 +3772,7 @@
         <v>26.48703346</v>
       </c>
       <c r="AF25">
-        <v>0.007795418</v>
+        <v>0.007795418284</v>
       </c>
       <c r="AG25">
         <v>83.65164932</v>
@@ -3787,10 +3787,10 @@
         <v>7943.285787</v>
       </c>
       <c r="AK25">
-        <v>0.001574084</v>
+        <v>0.001574084128</v>
       </c>
       <c r="AL25">
-        <v>0.017034848</v>
+        <v>0.01703484812</v>
       </c>
       <c r="AM25">
         <v>17.7961098</v>
@@ -3838,7 +3838,7 @@
         <v>440.8546733</v>
       </c>
       <c r="I26">
-        <v>0.315587086</v>
+        <v>0.3155870863</v>
       </c>
       <c r="J26">
         <v>4.64621104</v>
@@ -3856,7 +3856,7 @@
         <v>337.3759436</v>
       </c>
       <c r="O26">
-        <v>0.482810924</v>
+        <v>0.4828109236</v>
       </c>
       <c r="P26">
         <v>515.5724259</v>
@@ -3868,37 +3868,37 @@
         <v>5.23457575</v>
       </c>
       <c r="S26">
-        <v>0.817836683</v>
+        <v>0.8178366825</v>
       </c>
       <c r="T26">
         <v>93.74015838</v>
       </c>
       <c r="U26">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V26">
-        <v>0.342700778</v>
+        <v>0.3427007782</v>
       </c>
       <c r="W26">
         <v>5.447045667</v>
       </c>
       <c r="X26">
-        <v>0.028140718</v>
+        <v>0.0281407183</v>
       </c>
       <c r="Y26">
-        <v>0.543702682</v>
+        <v>0.5437026824</v>
       </c>
       <c r="Z26">
-        <v>0.028140718</v>
+        <v>0.0281407183</v>
       </c>
       <c r="AA26">
-        <v>0.371417339</v>
+        <v>0.3714173394</v>
       </c>
       <c r="AB26">
-        <v>0.492652081</v>
+        <v>0.4926520807</v>
       </c>
       <c r="AC26">
-        <v>0.051050602</v>
+        <v>0.05105060176</v>
       </c>
       <c r="AD26">
         <v>90.00585438</v>
@@ -3922,10 +3922,10 @@
         <v>7483.865782</v>
       </c>
       <c r="AK26">
-        <v>0.001852017</v>
+        <v>0.001852017408</v>
       </c>
       <c r="AL26">
-        <v>0.01688551</v>
+        <v>0.0168855103</v>
       </c>
       <c r="AM26">
         <v>16.78921936</v>
@@ -3934,7 +3934,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO26">
-        <v>0.227733672</v>
+        <v>0.2277336719</v>
       </c>
     </row>
     <row r="27">
@@ -3973,7 +3973,7 @@
         <v>700.4567584</v>
       </c>
       <c r="I27">
-        <v>0.149737739</v>
+        <v>0.1497377386</v>
       </c>
       <c r="J27">
         <v>3.988445829</v>
@@ -3991,7 +3991,7 @@
         <v>532.7177045</v>
       </c>
       <c r="O27">
-        <v>0.535278969</v>
+        <v>0.5352789687</v>
       </c>
       <c r="P27">
         <v>844.8970715</v>
@@ -4003,37 +4003,37 @@
         <v>5.373104493</v>
       </c>
       <c r="S27">
-        <v>0.598109624</v>
+        <v>0.5981096239</v>
       </c>
       <c r="T27">
         <v>73.49694091000001</v>
       </c>
       <c r="U27">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V27">
-        <v>0.399267931</v>
+        <v>0.3992679307</v>
       </c>
       <c r="W27">
         <v>7.075261445</v>
       </c>
       <c r="X27">
-        <v>0.043992451</v>
+        <v>0.04399245058</v>
       </c>
       <c r="Y27">
-        <v>0.888941951</v>
+        <v>0.8889419513</v>
       </c>
       <c r="Z27">
-        <v>0.043992451</v>
+        <v>0.04399245058</v>
       </c>
       <c r="AA27">
-        <v>0.581684775</v>
+        <v>0.5816847745</v>
       </c>
       <c r="AB27">
-        <v>0.803406799</v>
+        <v>0.8034067993</v>
       </c>
       <c r="AC27">
-        <v>0.085535152</v>
+        <v>0.08553515199</v>
       </c>
       <c r="AD27">
         <v>90.00765536</v>
@@ -4042,7 +4042,7 @@
         <v>116.4418765</v>
       </c>
       <c r="AF27">
-        <v>0.00283802</v>
+        <v>0.002838020157</v>
       </c>
       <c r="AG27">
         <v>70.34549975</v>
@@ -4057,10 +4057,10 @@
         <v>8735.340389000001</v>
       </c>
       <c r="AK27">
-        <v>0.003375705</v>
+        <v>0.003375705353</v>
       </c>
       <c r="AL27">
-        <v>0.01697802</v>
+        <v>0.01697801963</v>
       </c>
       <c r="AM27">
         <v>24.52109864</v>
@@ -4069,7 +4069,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO27">
-        <v>0.310494979</v>
+        <v>0.3104949791</v>
       </c>
     </row>
     <row r="28">
@@ -4108,7 +4108,7 @@
         <v>742.1566598000001</v>
       </c>
       <c r="I28">
-        <v>-0.023536991</v>
+        <v>-0.02353699093</v>
       </c>
       <c r="J28">
         <v>4.573964834</v>
@@ -4138,37 +4138,37 @@
         <v>5.828312604</v>
       </c>
       <c r="S28">
-        <v>0.931773633</v>
+        <v>0.9317736326</v>
       </c>
       <c r="T28">
         <v>86.7459691</v>
       </c>
       <c r="U28">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V28">
-        <v>0.594493488</v>
+        <v>0.5944934879</v>
       </c>
       <c r="W28">
         <v>14.64351978</v>
       </c>
       <c r="X28">
-        <v>0.048978173</v>
+        <v>0.04897817346</v>
       </c>
       <c r="Y28">
-        <v>0.918461529</v>
+        <v>0.9184615287</v>
       </c>
       <c r="Z28">
-        <v>0.048978173</v>
+        <v>0.04897817346</v>
       </c>
       <c r="AA28">
-        <v>0.580037381</v>
+        <v>0.5800373808</v>
       </c>
       <c r="AB28">
-        <v>0.8218457139999999</v>
+        <v>0.8218457139000001</v>
       </c>
       <c r="AC28">
-        <v>0.09661581499999999</v>
+        <v>0.09661581482000001</v>
       </c>
       <c r="AD28">
         <v>90.00639803999999</v>
@@ -4192,10 +4192,10 @@
         <v>8428.875056999999</v>
       </c>
       <c r="AK28">
-        <v>0.000724779</v>
+        <v>0.0007247786166</v>
       </c>
       <c r="AL28">
-        <v>0.017406842</v>
+        <v>0.0174068415</v>
       </c>
       <c r="AM28">
         <v>48.38877145</v>
@@ -4204,7 +4204,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO28">
-        <v>0.362977815</v>
+        <v>0.3629778147</v>
       </c>
     </row>
     <row r="29">
@@ -4243,7 +4243,7 @@
         <v>515.6712267</v>
       </c>
       <c r="I29">
-        <v>-0.344869132</v>
+        <v>-0.3448691316</v>
       </c>
       <c r="J29">
         <v>5.153260937</v>
@@ -4273,37 +4273,37 @@
         <v>5.140027519</v>
       </c>
       <c r="S29">
-        <v>0.704933623</v>
+        <v>0.7049336234</v>
       </c>
       <c r="T29">
         <v>129.003893</v>
       </c>
       <c r="U29">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V29">
-        <v>0.345509774</v>
+        <v>0.3455097737</v>
       </c>
       <c r="W29">
         <v>5.469556126</v>
       </c>
       <c r="X29">
-        <v>0.031430921</v>
+        <v>0.03143092061</v>
       </c>
       <c r="Y29">
-        <v>0.6310421939999999</v>
+        <v>0.6310421943</v>
       </c>
       <c r="Z29">
-        <v>0.031430921</v>
+        <v>0.03143092061</v>
       </c>
       <c r="AA29">
-        <v>0.399721656</v>
+        <v>0.3997216557</v>
       </c>
       <c r="AB29">
-        <v>0.561909529</v>
+        <v>0.5619095286</v>
       </c>
       <c r="AC29">
-        <v>0.069132666</v>
+        <v>0.06913266563000001</v>
       </c>
       <c r="AD29">
         <v>90.03107985</v>
@@ -4327,10 +4327,10 @@
         <v>8313.804614999999</v>
       </c>
       <c r="AK29">
-        <v>0.001176662</v>
+        <v>0.001176662404</v>
       </c>
       <c r="AL29">
-        <v>0.017523657</v>
+        <v>0.01752365669</v>
       </c>
       <c r="AM29">
         <v>16.91495435</v>
@@ -4339,7 +4339,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO29">
-        <v>0.351269156</v>
+        <v>0.3512691556</v>
       </c>
     </row>
     <row r="30">
@@ -4396,7 +4396,7 @@
         <v>329.3369465</v>
       </c>
       <c r="O30">
-        <v>0.06969595100000001</v>
+        <v>0.06969595141</v>
       </c>
       <c r="P30">
         <v>503.5606015</v>
@@ -4408,37 +4408,37 @@
         <v>4.971890066</v>
       </c>
       <c r="S30">
-        <v>0.7720100090000001</v>
+        <v>0.7720100087</v>
       </c>
       <c r="T30">
         <v>93.75175869</v>
       </c>
       <c r="U30">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V30">
-        <v>0.351231002</v>
+        <v>0.3512310021</v>
       </c>
       <c r="W30">
         <v>5.674495731</v>
       </c>
       <c r="X30">
-        <v>0.028970274</v>
+        <v>0.02897027389</v>
       </c>
       <c r="Y30">
-        <v>0.532561673</v>
+        <v>0.5325616726</v>
       </c>
       <c r="Z30">
-        <v>0.028970274</v>
+        <v>0.02897027389</v>
       </c>
       <c r="AA30">
-        <v>0.357951491</v>
+        <v>0.3579514914</v>
       </c>
       <c r="AB30">
-        <v>0.481534289</v>
+        <v>0.4815342887</v>
       </c>
       <c r="AC30">
-        <v>0.051027384</v>
+        <v>0.05102738393</v>
       </c>
       <c r="AD30">
         <v>89.99550463</v>
@@ -4462,10 +4462,10 @@
         <v>7270.008905</v>
       </c>
       <c r="AK30">
-        <v>0.001619892</v>
+        <v>0.001619891832</v>
       </c>
       <c r="AL30">
-        <v>0.017007213</v>
+        <v>0.01700721273</v>
       </c>
       <c r="AM30">
         <v>17.75026635</v>
@@ -4474,7 +4474,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO30">
-        <v>0.22926427</v>
+        <v>0.2292642696</v>
       </c>
     </row>
     <row r="31">
@@ -4513,7 +4513,7 @@
         <v>615.7832499</v>
       </c>
       <c r="I31">
-        <v>0.143374075</v>
+        <v>0.1433740748</v>
       </c>
       <c r="J31">
         <v>3.698901556</v>
@@ -4549,31 +4549,31 @@
         <v>119.7517713</v>
       </c>
       <c r="U31">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V31">
-        <v>0.374334278</v>
+        <v>0.3743342781</v>
       </c>
       <c r="W31">
         <v>6.288912683</v>
       </c>
       <c r="X31">
-        <v>0.034931601</v>
+        <v>0.03493160126</v>
       </c>
       <c r="Y31">
-        <v>0.810749246</v>
+        <v>0.8107492462</v>
       </c>
       <c r="Z31">
-        <v>0.034931601</v>
+        <v>0.03493160126</v>
       </c>
       <c r="AA31">
-        <v>0.516194262</v>
+        <v>0.5161942621</v>
       </c>
       <c r="AB31">
-        <v>0.73929071</v>
+        <v>0.7392907096</v>
       </c>
       <c r="AC31">
-        <v>0.071458537</v>
+        <v>0.07145853659</v>
       </c>
       <c r="AD31">
         <v>134.9816176</v>
@@ -4597,10 +4597,10 @@
         <v>8260.064982</v>
       </c>
       <c r="AK31">
-        <v>0.002286015</v>
+        <v>0.002286015131</v>
       </c>
       <c r="AL31">
-        <v>0.016799457</v>
+        <v>0.01679945722</v>
       </c>
       <c r="AM31">
         <v>20.96166202</v>
@@ -4609,7 +4609,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO31">
-        <v>0.279354634</v>
+        <v>0.2793546341</v>
       </c>
     </row>
     <row r="32">
@@ -4648,7 +4648,7 @@
         <v>728.8004426</v>
       </c>
       <c r="I32">
-        <v>-0.177988556</v>
+        <v>-0.1779885563</v>
       </c>
       <c r="J32">
         <v>4.866987085</v>
@@ -4678,43 +4678,43 @@
         <v>5.81351224</v>
       </c>
       <c r="S32">
-        <v>0.841080004</v>
+        <v>0.8410800042</v>
       </c>
       <c r="T32">
         <v>86.49498733</v>
       </c>
       <c r="U32">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V32">
-        <v>0.416859735</v>
+        <v>0.4168597353</v>
       </c>
       <c r="W32">
         <v>7.594139273</v>
       </c>
       <c r="X32">
-        <v>0.051168274</v>
+        <v>0.05116827374</v>
       </c>
       <c r="Y32">
-        <v>0.865150848</v>
+        <v>0.8651508479</v>
       </c>
       <c r="Z32">
-        <v>0.051168274</v>
+        <v>0.05116827374</v>
       </c>
       <c r="AA32">
-        <v>0.536060209</v>
+        <v>0.5360602087</v>
       </c>
       <c r="AB32">
-        <v>0.7600813749999999</v>
+        <v>0.7600813745</v>
       </c>
       <c r="AC32">
-        <v>0.105069473</v>
+        <v>0.1050694733</v>
       </c>
       <c r="AD32">
         <v>89.99984895999999</v>
       </c>
       <c r="AE32">
-        <v>0.008306654</v>
+        <v>0.008306653793</v>
       </c>
       <c r="AF32">
         <v>134.9948709</v>
@@ -4732,10 +4732,10 @@
         <v>8104.97664</v>
       </c>
       <c r="AK32">
-        <v>0.001028467</v>
+        <v>0.001028466988</v>
       </c>
       <c r="AL32">
-        <v>0.017247453</v>
+        <v>0.01724745342</v>
       </c>
       <c r="AM32">
         <v>26.55289353</v>
@@ -4744,7 +4744,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO32">
-        <v>0.397124662</v>
+        <v>0.3971246619</v>
       </c>
     </row>
     <row r="33">
@@ -4783,7 +4783,7 @@
         <v>523.2467327000001</v>
       </c>
       <c r="I33">
-        <v>-0.249376857</v>
+        <v>-0.2493768572</v>
       </c>
       <c r="J33">
         <v>4.434631953</v>
@@ -4813,37 +4813,37 @@
         <v>5.374707515</v>
       </c>
       <c r="S33">
-        <v>0.593151165</v>
+        <v>0.5931511648</v>
       </c>
       <c r="T33">
         <v>86.74687109</v>
       </c>
       <c r="U33">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V33">
-        <v>0.372854314</v>
+        <v>0.3728543142</v>
       </c>
       <c r="W33">
         <v>6.323570483</v>
       </c>
       <c r="X33">
-        <v>0.03091269</v>
+        <v>0.0309126899</v>
       </c>
       <c r="Y33">
-        <v>0.6469359220000001</v>
+        <v>0.6469359223</v>
       </c>
       <c r="Z33">
-        <v>0.03091269</v>
+        <v>0.0309126899</v>
       </c>
       <c r="AA33">
-        <v>0.413711751</v>
+        <v>0.4137117508</v>
       </c>
       <c r="AB33">
-        <v>0.575955884</v>
+        <v>0.5759558842</v>
       </c>
       <c r="AC33">
-        <v>0.070980038</v>
+        <v>0.07098003808</v>
       </c>
       <c r="AD33">
         <v>89.99320978999999</v>
@@ -4867,10 +4867,10 @@
         <v>7121.622208</v>
       </c>
       <c r="AK33">
-        <v>0.00221672</v>
+        <v>0.002216719769</v>
       </c>
       <c r="AL33">
-        <v>0.017237683</v>
+        <v>0.01723768321</v>
       </c>
       <c r="AM33">
         <v>19.87722505</v>
@@ -4879,7 +4879,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO33">
-        <v>0.319828372</v>
+        <v>0.3198283716</v>
       </c>
     </row>
     <row r="34">
@@ -4918,7 +4918,7 @@
         <v>473.7795641</v>
       </c>
       <c r="I34">
-        <v>-0.297985956</v>
+        <v>-0.2979859558</v>
       </c>
       <c r="J34">
         <v>4.282493802</v>
@@ -4948,37 +4948,37 @@
         <v>4.868315564</v>
       </c>
       <c r="S34">
-        <v>0.651592317</v>
+        <v>0.6515923173</v>
       </c>
       <c r="T34">
         <v>86.74915917</v>
       </c>
       <c r="U34">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V34">
-        <v>0.340907911</v>
+        <v>0.3409079106</v>
       </c>
       <c r="W34">
         <v>5.366702015</v>
       </c>
       <c r="X34">
-        <v>0.024946003</v>
+        <v>0.02494600301</v>
       </c>
       <c r="Y34">
-        <v>0.589764782</v>
+        <v>0.5897647824</v>
       </c>
       <c r="Z34">
-        <v>0.024946003</v>
+        <v>0.02494600301</v>
       </c>
       <c r="AA34">
-        <v>0.391922723</v>
+        <v>0.3919227229</v>
       </c>
       <c r="AB34">
-        <v>0.525711758</v>
+        <v>0.5257117575</v>
       </c>
       <c r="AC34">
-        <v>0.064053025</v>
+        <v>0.06405302488</v>
       </c>
       <c r="AD34">
         <v>89.99149339</v>
@@ -5002,10 +5002,10 @@
         <v>8292.710837000001</v>
       </c>
       <c r="AK34">
-        <v>0.002227322</v>
+        <v>0.002227322249</v>
       </c>
       <c r="AL34">
-        <v>0.016906851</v>
+        <v>0.0169068511</v>
       </c>
       <c r="AM34">
         <v>16.90755897</v>
@@ -5053,7 +5053,7 @@
         <v>488.9681076</v>
       </c>
       <c r="I35">
-        <v>-0.085352574</v>
+        <v>-0.08535257407999999</v>
       </c>
       <c r="J35">
         <v>3.360738022</v>
@@ -5083,37 +5083,37 @@
         <v>4.824586328</v>
       </c>
       <c r="S35">
-        <v>0.659537094</v>
+        <v>0.6595370939</v>
       </c>
       <c r="T35">
         <v>93.74600368</v>
       </c>
       <c r="U35">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V35">
-        <v>0.366832888</v>
+        <v>0.3668328875</v>
       </c>
       <c r="W35">
         <v>6.169645666</v>
       </c>
       <c r="X35">
-        <v>0.023742317</v>
+        <v>0.02374231703</v>
       </c>
       <c r="Y35">
-        <v>0.6401023850000001</v>
+        <v>0.6401023852</v>
       </c>
       <c r="Z35">
-        <v>0.023742317</v>
+        <v>0.02374231703</v>
       </c>
       <c r="AA35">
-        <v>0.420707303</v>
+        <v>0.4207073027</v>
       </c>
       <c r="AB35">
-        <v>0.5781193140000001</v>
+        <v>0.5781193135</v>
       </c>
       <c r="AC35">
-        <v>0.061983072</v>
+        <v>0.06198307171</v>
       </c>
       <c r="AD35">
         <v>134.9997648</v>
@@ -5137,10 +5137,10 @@
         <v>8549.450559000001</v>
       </c>
       <c r="AK35">
-        <v>0.0026555</v>
+        <v>0.002655500418</v>
       </c>
       <c r="AL35">
-        <v>0.016881138</v>
+        <v>0.0168811383</v>
       </c>
       <c r="AM35">
         <v>19.96053253</v>
@@ -5149,7 +5149,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO35">
-        <v>0.190392483</v>
+        <v>0.1903924826</v>
       </c>
     </row>
     <row r="36">
@@ -5188,7 +5188,7 @@
         <v>532.9491592000001</v>
       </c>
       <c r="I36">
-        <v>0.08322342100000001</v>
+        <v>0.08322342079</v>
       </c>
       <c r="J36">
         <v>3.399470241</v>
@@ -5224,31 +5224,31 @@
         <v>81.75323211</v>
       </c>
       <c r="U36">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V36">
-        <v>0.357516248</v>
+        <v>0.3575162477</v>
       </c>
       <c r="W36">
         <v>5.82554151</v>
       </c>
       <c r="X36">
-        <v>0.029760944</v>
+        <v>0.02976094447</v>
       </c>
       <c r="Y36">
-        <v>0.694824738</v>
+        <v>0.6948247384</v>
       </c>
       <c r="Z36">
-        <v>0.029760944</v>
+        <v>0.02976094447</v>
       </c>
       <c r="AA36">
-        <v>0.472463967</v>
+        <v>0.4724639668</v>
       </c>
       <c r="AB36">
-        <v>0.635491821</v>
+        <v>0.6354918211</v>
       </c>
       <c r="AC36">
-        <v>0.059332917</v>
+        <v>0.05933291729</v>
       </c>
       <c r="AD36">
         <v>89.99727976</v>
@@ -5272,10 +5272,10 @@
         <v>7880.072409</v>
       </c>
       <c r="AK36">
-        <v>0.001567657</v>
+        <v>0.001567656591</v>
       </c>
       <c r="AL36">
-        <v>0.017035274</v>
+        <v>0.0170352735</v>
       </c>
       <c r="AM36">
         <v>19.4607995</v>
@@ -5284,7 +5284,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO36">
-        <v>0.305600089</v>
+        <v>0.3056000886</v>
       </c>
     </row>
     <row r="37">
@@ -5323,7 +5323,7 @@
         <v>638.3373587</v>
       </c>
       <c r="I37">
-        <v>0.218825721</v>
+        <v>0.2188257208</v>
       </c>
       <c r="J37">
         <v>3.067112333</v>
@@ -5353,37 +5353,37 @@
         <v>5.69470673</v>
       </c>
       <c r="S37">
-        <v>0.802248758</v>
+        <v>0.8022487577</v>
       </c>
       <c r="T37">
         <v>98.26071595000001</v>
       </c>
       <c r="U37">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V37">
-        <v>0.388818496</v>
+        <v>0.3888184957</v>
       </c>
       <c r="W37">
         <v>6.879844179</v>
       </c>
       <c r="X37">
-        <v>0.035812271</v>
+        <v>0.03581227078</v>
       </c>
       <c r="Y37">
-        <v>0.867301134</v>
+        <v>0.8673011336000001</v>
       </c>
       <c r="Z37">
-        <v>0.035812271</v>
+        <v>0.03581227078</v>
       </c>
       <c r="AA37">
-        <v>0.566796162</v>
+        <v>0.5667961619</v>
       </c>
       <c r="AB37">
-        <v>0.801113896</v>
+        <v>0.8011138964</v>
       </c>
       <c r="AC37">
-        <v>0.066187237</v>
+        <v>0.06618723723</v>
       </c>
       <c r="AD37">
         <v>89.99985174</v>
@@ -5407,10 +5407,10 @@
         <v>7741.515482</v>
       </c>
       <c r="AK37">
-        <v>0.001640228</v>
+        <v>0.001640228437</v>
       </c>
       <c r="AL37">
-        <v>0.017103872</v>
+        <v>0.01710387232</v>
       </c>
       <c r="AM37">
         <v>20.83204398</v>
@@ -5419,7 +5419,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO37">
-        <v>0.191616684</v>
+        <v>0.1916166835</v>
       </c>
     </row>
     <row r="38">
@@ -5458,7 +5458,7 @@
         <v>524.1161681</v>
       </c>
       <c r="I38">
-        <v>0.153791559</v>
+        <v>0.1537915592</v>
       </c>
       <c r="J38">
         <v>3.384159379</v>
@@ -5488,37 +5488,37 @@
         <v>5.15389965</v>
       </c>
       <c r="S38">
-        <v>0.777916739</v>
+        <v>0.7779167388</v>
       </c>
       <c r="T38">
         <v>35.99358031</v>
       </c>
       <c r="U38">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V38">
-        <v>0.404311609</v>
+        <v>0.4043116086</v>
       </c>
       <c r="W38">
         <v>7.394706621</v>
       </c>
       <c r="X38">
-        <v>0.029380389</v>
+        <v>0.02938038872</v>
       </c>
       <c r="Y38">
-        <v>0.6844853279999999</v>
+        <v>0.6844853279000001</v>
       </c>
       <c r="Z38">
-        <v>0.029380389</v>
+        <v>0.02938038872</v>
       </c>
       <c r="AA38">
-        <v>0.463456932</v>
+        <v>0.4634569317</v>
       </c>
       <c r="AB38">
-        <v>0.627426939</v>
+        <v>0.6274269386</v>
       </c>
       <c r="AC38">
-        <v>0.057058389</v>
+        <v>0.05705838924</v>
       </c>
       <c r="AD38">
         <v>179.9882456</v>
@@ -5542,10 +5542,10 @@
         <v>8580.190863</v>
       </c>
       <c r="AK38">
-        <v>0.001057781</v>
+        <v>0.001057781381</v>
       </c>
       <c r="AL38">
-        <v>0.017651578</v>
+        <v>0.01765157793</v>
       </c>
       <c r="AM38">
         <v>25.95923489</v>
@@ -5554,7 +5554,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO38">
-        <v>0.246911704</v>
+        <v>0.2469117038</v>
       </c>
     </row>
     <row r="39">
@@ -5593,7 +5593,7 @@
         <v>524.5376113</v>
       </c>
       <c r="I39">
-        <v>0.569677196</v>
+        <v>0.5696771959</v>
       </c>
       <c r="J39">
         <v>4.807428613</v>
@@ -5623,37 +5623,37 @@
         <v>5.75673384</v>
       </c>
       <c r="S39">
-        <v>0.912965291</v>
+        <v>0.9129652908</v>
       </c>
       <c r="T39">
         <v>28.50829381</v>
       </c>
       <c r="U39">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V39">
-        <v>0.350513796</v>
+        <v>0.3505137962</v>
       </c>
       <c r="W39">
         <v>5.601959522</v>
       </c>
       <c r="X39">
-        <v>0.039609065</v>
+        <v>0.03960906451</v>
       </c>
       <c r="Y39">
-        <v>0.63727082</v>
+        <v>0.6372708199</v>
       </c>
       <c r="Z39">
-        <v>0.039609065</v>
+        <v>0.03960906451</v>
       </c>
       <c r="AA39">
-        <v>0.426383495</v>
+        <v>0.4263834951</v>
       </c>
       <c r="AB39">
-        <v>0.581259219</v>
+        <v>0.5812592188</v>
       </c>
       <c r="AC39">
-        <v>0.056011601</v>
+        <v>0.0560116011</v>
       </c>
       <c r="AD39">
         <v>44.99537972</v>
@@ -5662,7 +5662,7 @@
         <v>89.99052301</v>
       </c>
       <c r="AF39">
-        <v>0.005992968</v>
+        <v>0.005992967951</v>
       </c>
       <c r="AG39">
         <v>88.48560938</v>
@@ -5677,10 +5677,10 @@
         <v>8142.471146</v>
       </c>
       <c r="AK39">
-        <v>0.001375051</v>
+        <v>0.001375051449</v>
       </c>
       <c r="AL39">
-        <v>0.017841047</v>
+        <v>0.0178410465</v>
       </c>
       <c r="AM39">
         <v>18.47639836</v>
@@ -5689,7 +5689,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO39">
-        <v>0.515994106</v>
+        <v>0.5159941061</v>
       </c>
     </row>
     <row r="40">
@@ -5758,37 +5758,37 @@
         <v>5.553216105</v>
       </c>
       <c r="S40">
-        <v>0.828189843</v>
+        <v>0.8281898434</v>
       </c>
       <c r="T40">
         <v>151.7487401</v>
       </c>
       <c r="U40">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V40">
-        <v>0.367134464</v>
+        <v>0.3671344635</v>
       </c>
       <c r="W40">
         <v>6.145770503</v>
       </c>
       <c r="X40">
-        <v>0.03052808</v>
+        <v>0.03052807986</v>
       </c>
       <c r="Y40">
-        <v>0.71358226</v>
+        <v>0.7135822596</v>
       </c>
       <c r="Z40">
-        <v>0.03052808</v>
+        <v>0.03052807986</v>
       </c>
       <c r="AA40">
-        <v>0.465731933</v>
+        <v>0.4657319329</v>
       </c>
       <c r="AB40">
-        <v>0.653758507</v>
+        <v>0.6537585074</v>
       </c>
       <c r="AC40">
-        <v>0.059823752</v>
+        <v>0.05982375224</v>
       </c>
       <c r="AD40">
         <v>44.9843084</v>
@@ -5812,10 +5812,10 @@
         <v>8211.845914</v>
       </c>
       <c r="AK40">
-        <v>0.0001784</v>
+        <v>0.0001784002546</v>
       </c>
       <c r="AL40">
-        <v>0.017712011</v>
+        <v>0.01771201069</v>
       </c>
       <c r="AM40">
         <v>19.43860115</v>
@@ -5824,7 +5824,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO40">
-        <v>0.236968309</v>
+        <v>0.2369683093</v>
       </c>
     </row>
     <row r="41">
@@ -5863,7 +5863,7 @@
         <v>684.2428391</v>
       </c>
       <c r="I41">
-        <v>0.150698207</v>
+        <v>0.1506982072</v>
       </c>
       <c r="J41">
         <v>2.990583612</v>
@@ -5893,37 +5893,37 @@
         <v>5.829542482</v>
       </c>
       <c r="S41">
-        <v>0.843173039</v>
+        <v>0.8431730388000001</v>
       </c>
       <c r="T41">
         <v>93.26049132999999</v>
       </c>
       <c r="U41">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V41">
-        <v>0.419723354</v>
+        <v>0.4197233536</v>
       </c>
       <c r="W41">
         <v>7.924443727</v>
       </c>
       <c r="X41">
-        <v>0.036586215</v>
+        <v>0.03658621536</v>
       </c>
       <c r="Y41">
-        <v>0.9209007890000001</v>
+        <v>0.9209007885</v>
       </c>
       <c r="Z41">
-        <v>0.036586215</v>
+        <v>0.03658621536</v>
       </c>
       <c r="AA41">
-        <v>0.609689084</v>
+        <v>0.6096890835</v>
       </c>
       <c r="AB41">
-        <v>0.846860023</v>
+        <v>0.8468600226</v>
       </c>
       <c r="AC41">
-        <v>0.07404076599999999</v>
+        <v>0.07404076582000001</v>
       </c>
       <c r="AD41">
         <v>135.0113827</v>
@@ -5947,10 +5947,10 @@
         <v>9044.194199</v>
       </c>
       <c r="AK41">
-        <v>0.001318356</v>
+        <v>0.00131835554</v>
       </c>
       <c r="AL41">
-        <v>0.017232148</v>
+        <v>0.01723214849</v>
       </c>
       <c r="AM41">
         <v>22.63907348</v>
@@ -5959,7 +5959,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO41">
-        <v>0.125731114</v>
+        <v>0.1257311141</v>
       </c>
     </row>
     <row r="42">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>22.62848964</v>
+        <v>22.4797285</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5995,106 +5995,106 @@
         </is>
       </c>
       <c r="H42">
-        <v>588.4516861</v>
+        <v>594.5537134</v>
       </c>
       <c r="I42">
-        <v>0.31210305</v>
+        <v>0.3311372634</v>
       </c>
       <c r="J42">
-        <v>3.30542193</v>
+        <v>3.258587591</v>
       </c>
       <c r="K42">
-        <v>2203.135301</v>
+        <v>2231.113754</v>
       </c>
       <c r="L42">
-        <v>1601.150907</v>
+        <v>1574.627334</v>
       </c>
       <c r="M42">
-        <v>3804.286208</v>
+        <v>3805.741088</v>
       </c>
       <c r="N42">
-        <v>460.3987307</v>
+        <v>466.6687539</v>
       </c>
       <c r="O42">
-        <v>3.008718058</v>
+        <v>2.932383626</v>
       </c>
       <c r="P42">
-        <v>755.2411669000001</v>
+        <v>761.4805104</v>
       </c>
       <c r="Q42">
-        <v>1090.086378</v>
+        <v>1081.278994</v>
       </c>
       <c r="R42">
-        <v>5.46888513</v>
+        <v>5.558164279</v>
       </c>
       <c r="S42">
-        <v>0.811454621</v>
+        <v>0.7907273728000001</v>
       </c>
       <c r="T42">
-        <v>12.75117744</v>
+        <v>12.74905765</v>
       </c>
       <c r="U42">
-        <v>0.418714339</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V42">
-        <v>0.358152045</v>
+        <v>0.3592947607</v>
       </c>
       <c r="W42">
-        <v>5.845710443</v>
+        <v>5.884639456</v>
       </c>
       <c r="X42">
-        <v>0.035419376</v>
+        <v>0.03589654959</v>
       </c>
       <c r="Y42">
-        <v>0.790644735</v>
+        <v>0.7974013965</v>
       </c>
       <c r="Z42">
-        <v>0.035419376</v>
+        <v>0.03589654959</v>
       </c>
       <c r="AA42">
-        <v>0.50457176</v>
+        <v>0.5165110244</v>
       </c>
       <c r="AB42">
-        <v>0.727711223</v>
+        <v>0.735692617</v>
       </c>
       <c r="AC42">
-        <v>0.062933512</v>
+        <v>0.06170877955</v>
       </c>
       <c r="AD42">
-        <v>27.25845449</v>
+        <v>44.97790246</v>
       </c>
       <c r="AE42">
-        <v>45.69686284</v>
+        <v>90.00320175</v>
       </c>
       <c r="AF42">
-        <v>0.005312769</v>
+        <v>0.007602101299</v>
       </c>
       <c r="AG42">
-        <v>81.39797646</v>
+        <v>81.08128685</v>
       </c>
       <c r="AH42">
-        <v>4186.58379</v>
+        <v>4089.778342</v>
       </c>
       <c r="AI42">
-        <v>1794.281559</v>
+        <v>1826.483008</v>
       </c>
       <c r="AJ42">
-        <v>9711.901282999999</v>
+        <v>9707.761671</v>
       </c>
       <c r="AK42">
-        <v>0.000299001</v>
+        <v>0.0002073480819</v>
       </c>
       <c r="AL42">
-        <v>0.017524254</v>
+        <v>0.01756954961</v>
       </c>
       <c r="AM42">
-        <v>18.74536075</v>
+        <v>18.90034876</v>
       </c>
       <c r="AN42">
-        <v>1.129141677</v>
+        <v>1.230427007</v>
       </c>
       <c r="AO42">
-        <v>0.214639773</v>
+        <v>0.1808738908</v>
       </c>
     </row>
     <row r="43">
@@ -6133,7 +6133,7 @@
         <v>551.3157571</v>
       </c>
       <c r="I43">
-        <v>-0.115753717</v>
+        <v>-0.1157537166</v>
       </c>
       <c r="J43">
         <v>3.130713154</v>
@@ -6163,37 +6163,37 @@
         <v>5.308047039</v>
       </c>
       <c r="S43">
-        <v>0.555804622</v>
+        <v>0.5558046223000001</v>
       </c>
       <c r="T43">
         <v>50.98882622</v>
       </c>
       <c r="U43">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V43">
-        <v>0.356275633</v>
+        <v>0.3562756325</v>
       </c>
       <c r="W43">
         <v>5.889797839</v>
       </c>
       <c r="X43">
-        <v>0.026257244</v>
+        <v>0.02625724378</v>
       </c>
       <c r="Y43">
-        <v>0.725093389</v>
+        <v>0.7250933888</v>
       </c>
       <c r="Z43">
-        <v>0.026257244</v>
+        <v>0.02625724378</v>
       </c>
       <c r="AA43">
-        <v>0.48356531</v>
+        <v>0.4835653102</v>
       </c>
       <c r="AB43">
         <v>0.655066844</v>
       </c>
       <c r="AC43">
-        <v>0.070026545</v>
+        <v>0.07002654474</v>
       </c>
       <c r="AD43">
         <v>45.00965739</v>
@@ -6202,7 +6202,7 @@
         <v>89.99979691999999</v>
       </c>
       <c r="AF43">
-        <v>0.008841781</v>
+        <v>0.00884178111</v>
       </c>
       <c r="AG43">
         <v>64.09347944</v>
@@ -6217,10 +6217,10 @@
         <v>8139.808622</v>
       </c>
       <c r="AK43">
-        <v>0.002404657</v>
+        <v>0.002404656823</v>
       </c>
       <c r="AL43">
-        <v>0.017322095</v>
+        <v>0.01732209526</v>
       </c>
       <c r="AM43">
         <v>16.72983538</v>
@@ -6229,7 +6229,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO43">
-        <v>0.182623565</v>
+        <v>0.1826235645</v>
       </c>
     </row>
     <row r="44">
@@ -6268,7 +6268,7 @@
         <v>585.5325658</v>
       </c>
       <c r="I44">
-        <v>0.348070324</v>
+        <v>0.3480703235</v>
       </c>
       <c r="J44">
         <v>3.802934238</v>
@@ -6298,43 +6298,43 @@
         <v>5.095130561</v>
       </c>
       <c r="S44">
-        <v>0.544797648</v>
+        <v>0.5447976481</v>
       </c>
       <c r="T44">
         <v>36.2486234</v>
       </c>
       <c r="U44">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V44">
-        <v>0.368508548</v>
+        <v>0.3685085482</v>
       </c>
       <c r="W44">
         <v>6.158966556</v>
       </c>
       <c r="X44">
-        <v>0.040096281</v>
+        <v>0.04009628135</v>
       </c>
       <c r="Y44">
-        <v>0.781876291</v>
+        <v>0.7818762913</v>
       </c>
       <c r="Z44">
-        <v>0.040096281</v>
+        <v>0.04009628135</v>
       </c>
       <c r="AA44">
-        <v>0.48394015</v>
+        <v>0.4839401497</v>
       </c>
       <c r="AB44">
-        <v>0.719193764</v>
+        <v>0.7191937639</v>
       </c>
       <c r="AC44">
-        <v>0.062682527</v>
+        <v>0.06268252735</v>
       </c>
       <c r="AD44">
         <v>134.9898477</v>
       </c>
       <c r="AE44">
-        <v>0.009506208</v>
+        <v>0.009506207628</v>
       </c>
       <c r="AF44">
         <v>26.47225109</v>
@@ -6352,10 +6352,10 @@
         <v>8319.43773</v>
       </c>
       <c r="AK44">
-        <v>0.003144669</v>
+        <v>0.003144669483</v>
       </c>
       <c r="AL44">
-        <v>0.018348503</v>
+        <v>0.01834850337</v>
       </c>
       <c r="AM44">
         <v>20.25456374</v>
@@ -6403,7 +6403,7 @@
         <v>462.9315333</v>
       </c>
       <c r="I45">
-        <v>0.037481293</v>
+        <v>0.03748129312</v>
       </c>
       <c r="J45">
         <v>3.350299542</v>
@@ -6439,37 +6439,37 @@
         <v>8.512598153000001</v>
       </c>
       <c r="U45">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V45">
-        <v>0.332230488</v>
+        <v>0.3322304884</v>
       </c>
       <c r="W45">
         <v>5.163046513</v>
       </c>
       <c r="X45">
-        <v>0.024789399</v>
+        <v>0.02478939859</v>
       </c>
       <c r="Y45">
-        <v>0.617255208</v>
+        <v>0.6172552079</v>
       </c>
       <c r="Z45">
-        <v>0.024789399</v>
+        <v>0.02478939859</v>
       </c>
       <c r="AA45">
-        <v>0.396020803</v>
+        <v>0.3960208026</v>
       </c>
       <c r="AB45">
-        <v>0.564405055</v>
+        <v>0.5644050551999999</v>
       </c>
       <c r="AC45">
-        <v>0.052850153</v>
+        <v>0.05285015266</v>
       </c>
       <c r="AD45">
         <v>135.0475337</v>
       </c>
       <c r="AE45">
-        <v>0.008561733</v>
+        <v>0.008561733261</v>
       </c>
       <c r="AF45">
         <v>56.22895163</v>
@@ -6487,10 +6487,10 @@
         <v>6827.805954</v>
       </c>
       <c r="AK45">
-        <v>0.000962659</v>
+        <v>0.0009626586932</v>
       </c>
       <c r="AL45">
-        <v>0.017803715</v>
+        <v>0.01780371462</v>
       </c>
       <c r="AM45">
         <v>14.63001114</v>
@@ -6499,7 +6499,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO45">
-        <v>0.1489784</v>
+        <v>0.1489784002</v>
       </c>
     </row>
     <row r="46">
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>17.41381507</v>
+        <v>17.35377187</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6535,106 +6535,106 @@
         </is>
       </c>
       <c r="H46">
-        <v>591.962143</v>
+        <v>594.9891004999999</v>
       </c>
       <c r="I46">
-        <v>0.191190583</v>
+        <v>0.1961328276</v>
       </c>
       <c r="J46">
-        <v>3.958394892</v>
+        <v>3.963100667</v>
       </c>
       <c r="K46">
-        <v>2572.562794</v>
+        <v>2569.20538</v>
       </c>
       <c r="L46">
-        <v>2093.459766</v>
+        <v>2100.622249</v>
       </c>
       <c r="M46">
-        <v>4666.02256</v>
+        <v>4669.827629</v>
       </c>
       <c r="N46">
-        <v>450.8699735</v>
+        <v>452.339319</v>
       </c>
       <c r="O46">
-        <v>1.029428795</v>
+        <v>1.101689658</v>
       </c>
       <c r="P46">
-        <v>730.1634064</v>
+        <v>729.2996189</v>
       </c>
       <c r="Q46">
-        <v>1158.527012</v>
+        <v>1166.787901</v>
       </c>
       <c r="R46">
-        <v>6.203936107</v>
+        <v>6.297725092</v>
       </c>
       <c r="S46">
-        <v>0.874524796</v>
+        <v>0.8864867898</v>
       </c>
       <c r="T46">
-        <v>148.7513097</v>
+        <v>147.7559223</v>
       </c>
       <c r="U46">
-        <v>0.418714339</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V46">
-        <v>0.354684348</v>
+        <v>0.3553718464</v>
       </c>
       <c r="W46">
-        <v>5.741260877</v>
+        <v>5.765628563</v>
       </c>
       <c r="X46">
-        <v>0.038052804</v>
+        <v>0.03895738166</v>
       </c>
       <c r="Y46">
-        <v>0.768253152</v>
+        <v>0.7682657617</v>
       </c>
       <c r="Z46">
-        <v>0.038052804</v>
+        <v>0.03895738166</v>
       </c>
       <c r="AA46">
-        <v>0.48150353</v>
+        <v>0.4836695873</v>
       </c>
       <c r="AB46">
-        <v>0.699411013</v>
+        <v>0.6984760079</v>
       </c>
       <c r="AC46">
-        <v>0.068842139</v>
+        <v>0.06978975381999999</v>
       </c>
       <c r="AD46">
-        <v>152.7190893</v>
+        <v>89.99564822000001</v>
       </c>
       <c r="AE46">
-        <v>89.99627588</v>
+        <v>153.5201898</v>
       </c>
       <c r="AF46">
-        <v>27.27950196</v>
+        <v>146.2700251</v>
       </c>
       <c r="AG46">
-        <v>87.37275412</v>
+        <v>88.17329368999999</v>
       </c>
       <c r="AH46">
-        <v>4749.482285</v>
+        <v>4731.296291</v>
       </c>
       <c r="AI46">
-        <v>2166.593263</v>
+        <v>2171.858024</v>
       </c>
       <c r="AJ46">
-        <v>8809.064363</v>
+        <v>8827.827855</v>
       </c>
       <c r="AK46">
-        <v>0.001225667</v>
+        <v>0.001222403642</v>
       </c>
       <c r="AL46">
-        <v>0.017300033</v>
+        <v>0.0172682636</v>
       </c>
       <c r="AM46">
-        <v>18.51823915</v>
+        <v>18.93564205</v>
       </c>
       <c r="AN46">
-        <v>1.204526773</v>
+        <v>1.230427007</v>
       </c>
       <c r="AO46">
-        <v>0.243901054</v>
+        <v>0.267798393</v>
       </c>
     </row>
     <row r="47">
@@ -6691,7 +6691,7 @@
         <v>502.2451101</v>
       </c>
       <c r="O47">
-        <v>0.632898736</v>
+        <v>0.6328987361</v>
       </c>
       <c r="P47">
         <v>771.7290972</v>
@@ -6703,37 +6703,37 @@
         <v>6.401168813</v>
       </c>
       <c r="S47">
-        <v>0.774281318</v>
+        <v>0.7742813181</v>
       </c>
       <c r="T47">
         <v>50.75030135</v>
       </c>
       <c r="U47">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V47">
-        <v>0.416300453</v>
+        <v>0.4163004534</v>
       </c>
       <c r="W47">
         <v>7.68186065</v>
       </c>
       <c r="X47">
-        <v>0.04148572</v>
+        <v>0.04148572031</v>
       </c>
       <c r="Y47">
-        <v>0.813174291</v>
+        <v>0.8131742913</v>
       </c>
       <c r="Z47">
-        <v>0.04148572</v>
+        <v>0.04148572031</v>
       </c>
       <c r="AA47">
-        <v>0.549045055</v>
+        <v>0.5490450554</v>
       </c>
       <c r="AB47">
-        <v>0.738736024</v>
+        <v>0.7387360238</v>
       </c>
       <c r="AC47">
-        <v>0.074438267</v>
+        <v>0.07443826745</v>
       </c>
       <c r="AD47">
         <v>44.96467987</v>
@@ -6757,10 +6757,10 @@
         <v>8391.570460000001</v>
       </c>
       <c r="AK47">
-        <v>0.000774373</v>
+        <v>0.000774373068</v>
       </c>
       <c r="AL47">
-        <v>0.017426237</v>
+        <v>0.01742623706</v>
       </c>
       <c r="AM47">
         <v>25.45691301</v>
@@ -6769,7 +6769,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO47">
-        <v>0.263905136</v>
+        <v>0.2639051363</v>
       </c>
     </row>
     <row r="48">
@@ -6808,7 +6808,7 @@
         <v>525.4680747</v>
       </c>
       <c r="I48">
-        <v>0.392823551</v>
+        <v>0.3928235512</v>
       </c>
       <c r="J48">
         <v>3.524110682</v>
@@ -6838,37 +6838,37 @@
         <v>5.525380873</v>
       </c>
       <c r="S48">
-        <v>0.774444406</v>
+        <v>0.7744444056000001</v>
       </c>
       <c r="T48">
         <v>114.7474355</v>
       </c>
       <c r="U48">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V48">
-        <v>0.373498176</v>
+        <v>0.3734981758</v>
       </c>
       <c r="W48">
         <v>6.34685705</v>
       </c>
       <c r="X48">
-        <v>0.034483076</v>
+        <v>0.03448307574</v>
       </c>
       <c r="Y48">
-        <v>0.679896225</v>
+        <v>0.6798962254000001</v>
       </c>
       <c r="Z48">
-        <v>0.034483076</v>
+        <v>0.03448307574</v>
       </c>
       <c r="AA48">
-        <v>0.464347339</v>
+        <v>0.4643473387</v>
       </c>
       <c r="AB48">
-        <v>0.630136493</v>
+        <v>0.6301364926</v>
       </c>
       <c r="AC48">
-        <v>0.049759733</v>
+        <v>0.04975973284</v>
       </c>
       <c r="AD48">
         <v>89.99617205</v>
@@ -6892,10 +6892,10 @@
         <v>8732.169253</v>
       </c>
       <c r="AK48">
-        <v>0.000925825</v>
+        <v>0.0009258252545</v>
       </c>
       <c r="AL48">
-        <v>0.01794171</v>
+        <v>0.01794171014</v>
       </c>
       <c r="AM48">
         <v>21.26196646</v>
@@ -6904,7 +6904,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO48">
-        <v>0.181074561</v>
+        <v>0.1810745606</v>
       </c>
     </row>
     <row r="49">
@@ -6973,37 +6973,37 @@
         <v>5.13705294</v>
       </c>
       <c r="S49">
-        <v>0.724808539</v>
+        <v>0.7248085389</v>
       </c>
       <c r="T49">
         <v>73.00049077</v>
       </c>
       <c r="U49">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V49">
-        <v>0.341407353</v>
+        <v>0.3414073529</v>
       </c>
       <c r="W49">
         <v>5.423704219</v>
       </c>
       <c r="X49">
-        <v>0.026095907</v>
+        <v>0.02609590705</v>
       </c>
       <c r="Y49">
-        <v>0.637420461</v>
+        <v>0.6374204609</v>
       </c>
       <c r="Z49">
-        <v>0.026095907</v>
+        <v>0.02609590705</v>
       </c>
       <c r="AA49">
-        <v>0.396561541</v>
+        <v>0.3965615409</v>
       </c>
       <c r="AB49">
         <v>0.586618177</v>
       </c>
       <c r="AC49">
-        <v>0.050802284</v>
+        <v>0.05080228392</v>
       </c>
       <c r="AD49">
         <v>135.0414044</v>
@@ -7027,10 +7027,10 @@
         <v>6952.37334</v>
       </c>
       <c r="AK49">
-        <v>0.000907266</v>
+        <v>0.0009072663414</v>
       </c>
       <c r="AL49">
-        <v>0.017561434</v>
+        <v>0.01756143425</v>
       </c>
       <c r="AM49">
         <v>15.41287664</v>
@@ -7039,7 +7039,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO49">
-        <v>0.100058149</v>
+        <v>0.1000581488</v>
       </c>
     </row>
     <row r="50">
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>5.858375959</v>
+        <v>5.851077676</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7075,106 +7075,106 @@
         </is>
       </c>
       <c r="H50">
-        <v>373.4984129</v>
+        <v>374.0779612</v>
       </c>
       <c r="I50">
-        <v>0.196457561</v>
+        <v>0.2006211906</v>
       </c>
       <c r="J50">
-        <v>3.563664101</v>
+        <v>3.562910433</v>
       </c>
       <c r="K50">
-        <v>1582.344068</v>
+        <v>1589.88588</v>
       </c>
       <c r="L50">
-        <v>1225.993432</v>
+        <v>1222.940794</v>
       </c>
       <c r="M50">
-        <v>2808.3375</v>
+        <v>2812.826674</v>
       </c>
       <c r="N50">
-        <v>290.8399351</v>
+        <v>291.385591</v>
       </c>
       <c r="O50">
-        <v>5.852974989</v>
+        <v>5.697230661</v>
       </c>
       <c r="P50">
-        <v>465.6977973</v>
+        <v>466.8909422</v>
       </c>
       <c r="Q50">
-        <v>715.3569871</v>
+        <v>715.7173438</v>
       </c>
       <c r="R50">
-        <v>5.420697749</v>
+        <v>5.432875939</v>
       </c>
       <c r="S50">
-        <v>0.580397447</v>
+        <v>0.579324854</v>
       </c>
       <c r="T50">
-        <v>64.9942559</v>
+        <v>50.74966544</v>
       </c>
       <c r="U50">
-        <v>0.424366184</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V50">
-        <v>0.276151014</v>
+        <v>0.2762126807</v>
       </c>
       <c r="W50">
-        <v>3.606743844</v>
+        <v>3.607793209</v>
       </c>
       <c r="X50">
-        <v>0.021915353</v>
+        <v>0.02193467245</v>
       </c>
       <c r="Y50">
-        <v>0.487610305</v>
+        <v>0.4887990502</v>
       </c>
       <c r="Z50">
-        <v>0.021915353</v>
+        <v>0.02193467245</v>
       </c>
       <c r="AA50">
-        <v>0.317560317</v>
+        <v>0.3184152331</v>
       </c>
       <c r="AB50">
-        <v>0.445419704</v>
+        <v>0.4467195913</v>
       </c>
       <c r="AC50">
-        <v>0.042190601</v>
+        <v>0.04207945893</v>
       </c>
       <c r="AD50">
-        <v>90.01550007</v>
+        <v>90.01768896999999</v>
       </c>
       <c r="AE50">
-        <v>63.5248077</v>
+        <v>45.00600106</v>
       </c>
       <c r="AF50">
-        <v>116.5138824</v>
+        <v>63.56632893</v>
       </c>
       <c r="AG50">
-        <v>62.57252901</v>
+        <v>62.87942571</v>
       </c>
       <c r="AH50">
-        <v>2776.037892</v>
+        <v>2759.383057</v>
       </c>
       <c r="AI50">
-        <v>1160.384687</v>
+        <v>1163.69109</v>
       </c>
       <c r="AJ50">
-        <v>6342.800022</v>
+        <v>6329.190248</v>
       </c>
       <c r="AK50">
-        <v>0.002656972</v>
+        <v>0.002569794201</v>
       </c>
       <c r="AL50">
-        <v>0.017513522</v>
+        <v>0.0175023954</v>
       </c>
       <c r="AM50">
-        <v>10.19115438</v>
+        <v>10.14782668</v>
       </c>
       <c r="AN50">
-        <v>1.078671731</v>
+        <v>1.080586533</v>
       </c>
       <c r="AO50">
-        <v>0.18716492</v>
+        <v>0.1956359968</v>
       </c>
     </row>
     <row r="51">
@@ -7243,37 +7243,37 @@
         <v>5.589738786</v>
       </c>
       <c r="S51">
-        <v>0.676836598</v>
+        <v>0.6768365983</v>
       </c>
       <c r="T51">
         <v>93.00196585</v>
       </c>
       <c r="U51">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V51">
-        <v>0.344714569</v>
+        <v>0.3447145688</v>
       </c>
       <c r="W51">
         <v>5.094008493</v>
       </c>
       <c r="X51">
-        <v>0.03084663</v>
+        <v>0.03084662972</v>
       </c>
       <c r="Y51">
-        <v>0.664007606</v>
+        <v>0.6640076059</v>
       </c>
       <c r="Z51">
-        <v>0.03084663</v>
+        <v>0.03084662972</v>
       </c>
       <c r="AA51">
-        <v>0.403423849</v>
+        <v>0.4034238486</v>
       </c>
       <c r="AB51">
-        <v>0.597591739</v>
+        <v>0.5975917393</v>
       </c>
       <c r="AC51">
-        <v>0.066415867</v>
+        <v>0.06641586662</v>
       </c>
       <c r="AD51">
         <v>90.00745773</v>
@@ -7297,7 +7297,7 @@
         <v>8646.19326</v>
       </c>
       <c r="AK51">
-        <v>0.002230367</v>
+        <v>0.002230366568</v>
       </c>
       <c r="AL51">
         <v>0.016631524</v>
@@ -7309,7 +7309,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO51">
-        <v>0.503033635</v>
+        <v>0.5030336354</v>
       </c>
     </row>
     <row r="52">
@@ -7348,7 +7348,7 @@
         <v>480.2972762</v>
       </c>
       <c r="I52">
-        <v>-0.101960898</v>
+        <v>-0.1019608982</v>
       </c>
       <c r="J52">
         <v>4.566993706</v>
@@ -7378,40 +7378,40 @@
         <v>5.832833733</v>
       </c>
       <c r="S52">
-        <v>0.910429844</v>
+        <v>0.9104298436</v>
       </c>
       <c r="T52">
         <v>175.7451914</v>
       </c>
       <c r="U52">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V52">
-        <v>0.305756617</v>
+        <v>0.3057566165</v>
       </c>
       <c r="W52">
         <v>4.348405432</v>
       </c>
       <c r="X52">
-        <v>0.029200862</v>
+        <v>0.02920086239</v>
       </c>
       <c r="Y52">
-        <v>0.610444075</v>
+        <v>0.6104440747</v>
       </c>
       <c r="Z52">
-        <v>0.029200862</v>
+        <v>0.02920086239</v>
       </c>
       <c r="AA52">
-        <v>0.383386836</v>
+        <v>0.3833868363</v>
       </c>
       <c r="AB52">
-        <v>0.5499182500000001</v>
+        <v>0.5499182497</v>
       </c>
       <c r="AC52">
-        <v>0.060525825</v>
+        <v>0.06052582496</v>
       </c>
       <c r="AD52">
-        <v>0.006755462</v>
+        <v>0.006755462179</v>
       </c>
       <c r="AE52">
         <v>90.00600211</v>
@@ -7432,10 +7432,10 @@
         <v>6876.646911</v>
       </c>
       <c r="AK52">
-        <v>0.002075246</v>
+        <v>0.002075245871</v>
       </c>
       <c r="AL52">
-        <v>0.016879236</v>
+        <v>0.01687923584</v>
       </c>
       <c r="AM52">
         <v>13.25188741</v>
@@ -7444,7 +7444,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO52">
-        <v>0.286034827</v>
+        <v>0.2860348266</v>
       </c>
     </row>
     <row r="53">
@@ -7483,7 +7483,7 @@
         <v>442.7706082</v>
       </c>
       <c r="I53">
-        <v>-0.06232074</v>
+        <v>-0.06232073995</v>
       </c>
       <c r="J53">
         <v>3.005025126</v>
@@ -7513,37 +7513,37 @@
         <v>5.453197929</v>
       </c>
       <c r="S53">
-        <v>0.859113529</v>
+        <v>0.8591135294</v>
       </c>
       <c r="T53">
         <v>33.74369209</v>
       </c>
       <c r="U53">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V53">
-        <v>0.324684318</v>
+        <v>0.3246843175</v>
       </c>
       <c r="W53">
         <v>4.923591601</v>
       </c>
       <c r="X53">
-        <v>0.020802655</v>
+        <v>0.02080265478</v>
       </c>
       <c r="Y53">
-        <v>0.5822905900000001</v>
+        <v>0.5822905904</v>
       </c>
       <c r="Z53">
-        <v>0.020802655</v>
+        <v>0.02080265478</v>
       </c>
       <c r="AA53">
-        <v>0.39955994</v>
+        <v>0.3995599396</v>
       </c>
       <c r="AB53">
-        <v>0.530455884</v>
+        <v>0.5304558834999999</v>
       </c>
       <c r="AC53">
-        <v>0.051834707</v>
+        <v>0.05183470689</v>
       </c>
       <c r="AD53">
         <v>45.0062722</v>
@@ -7567,10 +7567,10 @@
         <v>7310.472342</v>
       </c>
       <c r="AK53">
-        <v>0.0007337240000000001</v>
+        <v>0.0007337238601</v>
       </c>
       <c r="AL53">
-        <v>0.01780436</v>
+        <v>0.01780436042</v>
       </c>
       <c r="AM53">
         <v>14.18348266</v>
@@ -7579,7 +7579,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO53">
-        <v>0.169567151</v>
+        <v>0.1695671514</v>
       </c>
     </row>
     <row r="54">
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="F54">
-        <v>9.210586407999999</v>
+        <v>9.197502343</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -7615,106 +7615,106 @@
         </is>
       </c>
       <c r="H54">
-        <v>400.4771777</v>
+        <v>400.4143132</v>
       </c>
       <c r="I54">
-        <v>0.170122068</v>
+        <v>0.1706755294</v>
       </c>
       <c r="J54">
-        <v>3.494574401</v>
+        <v>3.490502471</v>
       </c>
       <c r="K54">
-        <v>1623.644469</v>
+        <v>1631.814766</v>
       </c>
       <c r="L54">
-        <v>1409.510867</v>
+        <v>1409.151733</v>
       </c>
       <c r="M54">
-        <v>3033.155336</v>
+        <v>3040.966499</v>
       </c>
       <c r="N54">
-        <v>312.1182561</v>
+        <v>312.1569523</v>
       </c>
       <c r="O54">
-        <v>5.590924444</v>
+        <v>5.413422551</v>
       </c>
       <c r="P54">
-        <v>497.1974278</v>
+        <v>497.6149681</v>
       </c>
       <c r="Q54">
-        <v>771.5132079</v>
+        <v>771.403127</v>
       </c>
       <c r="R54">
-        <v>5.490501519</v>
+        <v>5.495459343</v>
       </c>
       <c r="S54">
-        <v>0.658268906</v>
+        <v>0.6572540238</v>
       </c>
       <c r="T54">
-        <v>54.00076207</v>
+        <v>54.01038459</v>
       </c>
       <c r="U54">
-        <v>0.424366184</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V54">
-        <v>0.310850129</v>
+        <v>0.310745778</v>
       </c>
       <c r="W54">
-        <v>4.50705213</v>
+        <v>4.503957143</v>
       </c>
       <c r="X54">
-        <v>0.02301079</v>
+        <v>0.02296718543</v>
       </c>
       <c r="Y54">
-        <v>0.52023229</v>
+        <v>0.5205648201</v>
       </c>
       <c r="Z54">
-        <v>0.02301079</v>
+        <v>0.02296718543</v>
       </c>
       <c r="AA54">
-        <v>0.347921722</v>
+        <v>0.3479076253</v>
       </c>
       <c r="AB54">
-        <v>0.474943881</v>
+        <v>0.4753171112</v>
       </c>
       <c r="AC54">
-        <v>0.045288409</v>
+        <v>0.04524770884</v>
       </c>
       <c r="AD54">
-        <v>63.47766885</v>
+        <v>44.98739017</v>
       </c>
       <c r="AE54">
-        <v>44.94073482</v>
+        <v>0.0116694584</v>
       </c>
       <c r="AF54">
-        <v>0.011893616</v>
+        <v>89.99649939</v>
       </c>
       <c r="AG54">
-        <v>67.10080227</v>
+        <v>67.07337584</v>
       </c>
       <c r="AH54">
-        <v>3253.424142</v>
+        <v>3229.661448</v>
       </c>
       <c r="AI54">
-        <v>1407.152311</v>
+        <v>1412.494406</v>
       </c>
       <c r="AJ54">
-        <v>7251.998623</v>
+        <v>7255.245479</v>
       </c>
       <c r="AK54">
-        <v>0.00254496</v>
+        <v>0.002604071305</v>
       </c>
       <c r="AL54">
-        <v>0.017844637</v>
+        <v>0.01784804752</v>
       </c>
       <c r="AM54">
-        <v>13.87228779</v>
+        <v>13.93506311</v>
       </c>
       <c r="AN54">
-        <v>1.078671731</v>
+        <v>1.080586533</v>
       </c>
       <c r="AO54">
-        <v>0.15316904</v>
+        <v>0.159483322</v>
       </c>
     </row>
     <row r="55">
@@ -7753,7 +7753,7 @@
         <v>413.3544307</v>
       </c>
       <c r="I55">
-        <v>-0.131522222</v>
+        <v>-0.1315222219</v>
       </c>
       <c r="J55">
         <v>3.792988664</v>
@@ -7783,43 +7783,43 @@
         <v>5.378359602</v>
       </c>
       <c r="S55">
-        <v>0.620743381</v>
+        <v>0.6207433812000001</v>
       </c>
       <c r="T55">
         <v>68.99938056000001</v>
       </c>
       <c r="U55">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V55">
-        <v>0.312538354</v>
+        <v>0.3125383543</v>
       </c>
       <c r="W55">
         <v>4.555356693</v>
       </c>
       <c r="X55">
-        <v>0.021779029</v>
+        <v>0.0217790291</v>
       </c>
       <c r="Y55">
         <v>0.533039154</v>
       </c>
       <c r="Z55">
-        <v>0.021779029</v>
+        <v>0.0217790291</v>
       </c>
       <c r="AA55">
-        <v>0.346887827</v>
+        <v>0.3468878271</v>
       </c>
       <c r="AB55">
-        <v>0.481455004</v>
+        <v>0.4814550038</v>
       </c>
       <c r="AC55">
-        <v>0.05158415</v>
+        <v>0.05158415023</v>
       </c>
       <c r="AD55">
         <v>90.01015080000001</v>
       </c>
       <c r="AE55">
-        <v>0.012104548</v>
+        <v>0.01210454786</v>
       </c>
       <c r="AF55">
         <v>45.02164771</v>
@@ -7837,7 +7837,7 @@
         <v>8420.657267000001</v>
       </c>
       <c r="AK55">
-        <v>0.00076972</v>
+        <v>0.0007697196835</v>
       </c>
       <c r="AL55">
         <v>0.017348198</v>
@@ -7849,7 +7849,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO55">
-        <v>0.150819439</v>
+        <v>0.1508194389</v>
       </c>
     </row>
     <row r="56">
@@ -7888,7 +7888,7 @@
         <v>498.9645318</v>
       </c>
       <c r="I56">
-        <v>-0.040344169</v>
+        <v>-0.04034416909</v>
       </c>
       <c r="J56">
         <v>4.066183278</v>
@@ -7918,37 +7918,37 @@
         <v>5.815101184</v>
       </c>
       <c r="S56">
-        <v>0.921912211</v>
+        <v>0.9219122105999999</v>
       </c>
       <c r="T56">
         <v>50.99301474</v>
       </c>
       <c r="U56">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V56">
-        <v>0.325089656</v>
+        <v>0.3250896562</v>
       </c>
       <c r="W56">
         <v>4.873550451</v>
       </c>
       <c r="X56">
-        <v>0.030156598</v>
+        <v>0.03015659758</v>
       </c>
       <c r="Y56">
-        <v>0.637700694</v>
+        <v>0.6377006938000001</v>
       </c>
       <c r="Z56">
-        <v>0.030156598</v>
+        <v>0.03015659758</v>
       </c>
       <c r="AA56">
-        <v>0.403849636</v>
+        <v>0.4038496361</v>
       </c>
       <c r="AB56">
-        <v>0.5748487920000001</v>
+        <v>0.5748487918</v>
       </c>
       <c r="AC56">
-        <v>0.062851902</v>
+        <v>0.06285190206000001</v>
       </c>
       <c r="AD56">
         <v>89.99556767999999</v>
@@ -7972,10 +7972,10 @@
         <v>8498.933789999999</v>
       </c>
       <c r="AK56">
-        <v>0.001481267</v>
+        <v>0.001481266991</v>
       </c>
       <c r="AL56">
-        <v>0.017025152</v>
+        <v>0.01702515162</v>
       </c>
       <c r="AM56">
         <v>15.453352</v>
@@ -7984,7 +7984,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO56">
-        <v>0.195937193</v>
+        <v>0.1959371928</v>
       </c>
     </row>
     <row r="57">
@@ -8023,7 +8023,7 @@
         <v>419.9978511</v>
       </c>
       <c r="I57">
-        <v>-0.029714649</v>
+        <v>-0.02971464853</v>
       </c>
       <c r="J57">
         <v>3.366626208</v>
@@ -8053,37 +8053,37 @@
         <v>5.767203536</v>
       </c>
       <c r="S57">
-        <v>0.8846393809999999</v>
+        <v>0.8846393807</v>
       </c>
       <c r="T57">
         <v>3.513223453</v>
       </c>
       <c r="U57">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V57">
-        <v>0.286633201</v>
+        <v>0.2866332013</v>
       </c>
       <c r="W57">
         <v>3.870426511</v>
       </c>
       <c r="X57">
-        <v>0.022662412</v>
+        <v>0.0226624117</v>
       </c>
       <c r="Y57">
-        <v>0.535566715</v>
+        <v>0.5355667149</v>
       </c>
       <c r="Z57">
-        <v>0.022662412</v>
+        <v>0.0226624117</v>
       </c>
       <c r="AA57">
-        <v>0.364165363</v>
+        <v>0.3641653625</v>
       </c>
       <c r="AB57">
-        <v>0.483339665</v>
+        <v>0.4833396646</v>
       </c>
       <c r="AC57">
-        <v>0.05222705</v>
+        <v>0.05222705031</v>
       </c>
       <c r="AD57">
         <v>44.99962733</v>
@@ -8107,19 +8107,19 @@
         <v>7206.022353</v>
       </c>
       <c r="AK57">
-        <v>0.000157607</v>
+        <v>0.0001576070395</v>
       </c>
       <c r="AL57">
-        <v>0.017677516</v>
+        <v>0.01767751563</v>
       </c>
       <c r="AM57">
         <v>11.1871122</v>
       </c>
       <c r="AN57">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO57">
-        <v>0.163700238</v>
+        <v>0.1637002381</v>
       </c>
     </row>
     <row r="58">
@@ -8158,7 +8158,7 @@
         <v>307.2428073</v>
       </c>
       <c r="I58">
-        <v>0.187279061</v>
+        <v>0.1872790611</v>
       </c>
       <c r="J58">
         <v>3.039965615</v>
@@ -8188,37 +8188,37 @@
         <v>5.085529985</v>
       </c>
       <c r="S58">
-        <v>0.806103718</v>
+        <v>0.8061037176</v>
       </c>
       <c r="T58">
         <v>129.2513768</v>
       </c>
       <c r="U58">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V58">
-        <v>0.240163366</v>
+        <v>0.2401633664</v>
       </c>
       <c r="W58">
         <v>2.779315264</v>
       </c>
       <c r="X58">
-        <v>0.01650108</v>
+        <v>0.01650107964</v>
       </c>
       <c r="Y58">
-        <v>0.411977526</v>
+        <v>0.4119775259</v>
       </c>
       <c r="Z58">
-        <v>0.01650108</v>
+        <v>0.01650107964</v>
       </c>
       <c r="AA58">
-        <v>0.271892067</v>
+        <v>0.2718920666</v>
       </c>
       <c r="AB58">
-        <v>0.379820808</v>
+        <v>0.3798208078</v>
       </c>
       <c r="AC58">
-        <v>0.032156718</v>
+        <v>0.03215671815</v>
       </c>
       <c r="AD58">
         <v>90.00202926</v>
@@ -8227,7 +8227,7 @@
         <v>135.0317109</v>
       </c>
       <c r="AF58">
-        <v>0.004792652</v>
+        <v>0.004792651759</v>
       </c>
       <c r="AG58">
         <v>77.12299346</v>
@@ -8242,10 +8242,10 @@
         <v>5523.281326</v>
       </c>
       <c r="AK58">
-        <v>0.001973014</v>
+        <v>0.001973014116</v>
       </c>
       <c r="AL58">
-        <v>0.017149913</v>
+        <v>0.01714991321</v>
       </c>
       <c r="AM58">
         <v>6.676743458</v>
@@ -8254,7 +8254,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO58">
-        <v>0.109212898</v>
+        <v>0.1092128975</v>
       </c>
     </row>
     <row r="59">
@@ -8293,7 +8293,7 @@
         <v>315.0246399</v>
       </c>
       <c r="I59">
-        <v>-0.0336508</v>
+        <v>-0.03365080047</v>
       </c>
       <c r="J59">
         <v>3.738613091</v>
@@ -8323,37 +8323,37 @@
         <v>5.22050176</v>
       </c>
       <c r="S59">
-        <v>0.546921079</v>
+        <v>0.5469210791</v>
       </c>
       <c r="T59">
         <v>39.25185162</v>
       </c>
       <c r="U59">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V59">
-        <v>0.264139481</v>
+        <v>0.2641394813</v>
       </c>
       <c r="W59">
         <v>3.331965924</v>
       </c>
       <c r="X59">
-        <v>0.018719027</v>
+        <v>0.01871902711</v>
       </c>
       <c r="Y59">
-        <v>0.390813932</v>
+        <v>0.3908139322</v>
       </c>
       <c r="Z59">
-        <v>0.018719027</v>
+        <v>0.01871902711</v>
       </c>
       <c r="AA59">
-        <v>0.265503315</v>
+        <v>0.2655033152</v>
       </c>
       <c r="AB59">
-        <v>0.351381019</v>
+        <v>0.3513810189</v>
       </c>
       <c r="AC59">
-        <v>0.039432913</v>
+        <v>0.03943291331</v>
       </c>
       <c r="AD59">
         <v>90.01557022</v>
@@ -8377,16 +8377,16 @@
         <v>6048.524942</v>
       </c>
       <c r="AK59">
-        <v>0.001249513</v>
+        <v>0.001249512889</v>
       </c>
       <c r="AL59">
-        <v>0.017113556</v>
+        <v>0.01711355623</v>
       </c>
       <c r="AM59">
         <v>8.958262952</v>
       </c>
       <c r="AN59">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO59">
         <v>0.13560597</v>
@@ -8428,7 +8428,7 @@
         <v>426.3785753</v>
       </c>
       <c r="I60">
-        <v>0.329483515</v>
+        <v>0.3294835149</v>
       </c>
       <c r="J60">
         <v>4.004909746</v>
@@ -8458,13 +8458,13 @@
         <v>6.113245892</v>
       </c>
       <c r="S60">
-        <v>0.736888825</v>
+        <v>0.7368888252</v>
       </c>
       <c r="T60">
         <v>140.7451735</v>
       </c>
       <c r="U60">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V60">
         <v>0.284717505</v>
@@ -8473,22 +8473,22 @@
         <v>3.801138657</v>
       </c>
       <c r="X60">
-        <v>0.02894864</v>
+        <v>0.02894863998</v>
       </c>
       <c r="Y60">
-        <v>0.55090982</v>
+        <v>0.5509098203</v>
       </c>
       <c r="Z60">
-        <v>0.02894864</v>
+        <v>0.02894863998</v>
       </c>
       <c r="AA60">
-        <v>0.348744205</v>
+        <v>0.3487442045</v>
       </c>
       <c r="AB60">
-        <v>0.504312913</v>
+        <v>0.5043129125</v>
       </c>
       <c r="AC60">
-        <v>0.046596908</v>
+        <v>0.04659690778</v>
       </c>
       <c r="AD60">
         <v>134.9801679</v>
@@ -8512,10 +8512,10 @@
         <v>7208.95622</v>
       </c>
       <c r="AK60">
-        <v>0.002542021</v>
+        <v>0.002542021269</v>
       </c>
       <c r="AL60">
-        <v>0.017568628</v>
+        <v>0.01756862823</v>
       </c>
       <c r="AM60">
         <v>11.37591746</v>
@@ -8524,7 +8524,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO60">
-        <v>0.498675684</v>
+        <v>0.4986756843</v>
       </c>
     </row>
     <row r="61">
@@ -8563,7 +8563,7 @@
         <v>381.3990292</v>
       </c>
       <c r="I61">
-        <v>0.058641734</v>
+        <v>0.05864173432</v>
       </c>
       <c r="J61">
         <v>3.21691317</v>
@@ -8593,43 +8593,43 @@
         <v>5.7438799</v>
       </c>
       <c r="S61">
-        <v>0.839527014</v>
+        <v>0.8395270144</v>
       </c>
       <c r="T61">
         <v>132.2587946</v>
       </c>
       <c r="U61">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V61">
-        <v>0.27535505</v>
+        <v>0.2753550496</v>
       </c>
       <c r="W61">
         <v>3.606230651</v>
       </c>
       <c r="X61">
-        <v>0.021023223</v>
+        <v>0.02102322261</v>
       </c>
       <c r="Y61">
-        <v>0.498354287</v>
+        <v>0.4983542869</v>
       </c>
       <c r="Z61">
-        <v>0.021023223</v>
+        <v>0.02102322261</v>
       </c>
       <c r="AA61">
-        <v>0.331887978</v>
+        <v>0.3318879779</v>
       </c>
       <c r="AB61">
-        <v>0.453825401</v>
+        <v>0.4538254009</v>
       </c>
       <c r="AC61">
-        <v>0.044528886</v>
+        <v>0.04452888602</v>
       </c>
       <c r="AD61">
         <v>134.9978621</v>
       </c>
       <c r="AE61">
-        <v>0.0009779070000000001</v>
+        <v>0.0009779071909000001</v>
       </c>
       <c r="AF61">
         <v>89.98747093999999</v>
@@ -8647,10 +8647,10 @@
         <v>6734.339328</v>
       </c>
       <c r="AK61">
-        <v>0.00229221</v>
+        <v>0.002292210192</v>
       </c>
       <c r="AL61">
-        <v>0.016845103</v>
+        <v>0.01684510327</v>
       </c>
       <c r="AM61">
         <v>9.479947277999999</v>
@@ -8659,7 +8659,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO61">
-        <v>0.151898478</v>
+        <v>0.1518984782</v>
       </c>
     </row>
     <row r="62">
@@ -8728,37 +8728,37 @@
         <v>4.987168241</v>
       </c>
       <c r="S62">
-        <v>0.8361955</v>
+        <v>0.8361955003</v>
       </c>
       <c r="T62">
         <v>93.75100836999999</v>
       </c>
       <c r="U62">
-        <v>0.566544672</v>
+        <v>0.5665446722</v>
       </c>
       <c r="V62">
-        <v>0.292208462</v>
+        <v>0.2922084617</v>
       </c>
       <c r="W62">
         <v>4.05195178</v>
       </c>
       <c r="X62">
-        <v>0.017442673</v>
+        <v>0.01744267275</v>
       </c>
       <c r="Y62">
-        <v>0.439989398</v>
+        <v>0.4399893978</v>
       </c>
       <c r="Z62">
-        <v>0.017442673</v>
+        <v>0.01744267275</v>
       </c>
       <c r="AA62">
-        <v>0.28781088</v>
+        <v>0.2878108799</v>
       </c>
       <c r="AB62">
-        <v>0.406383791</v>
+        <v>0.4063837905</v>
       </c>
       <c r="AC62">
-        <v>0.033605607</v>
+        <v>0.03360560735</v>
       </c>
       <c r="AD62">
         <v>90.00602234999999</v>
@@ -8782,19 +8782,19 @@
         <v>6059.662655</v>
       </c>
       <c r="AK62">
-        <v>0.001330908</v>
+        <v>0.001330907819</v>
       </c>
       <c r="AL62">
-        <v>0.017167457</v>
+        <v>0.01716745663</v>
       </c>
       <c r="AM62">
         <v>11.47167012</v>
       </c>
       <c r="AN62">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO62">
-        <v>0.155549797</v>
+        <v>0.1555497971</v>
       </c>
     </row>
     <row r="63">
@@ -8833,7 +8833,7 @@
         <v>304.5316773</v>
       </c>
       <c r="I63">
-        <v>-0.098308695</v>
+        <v>-0.0983086953</v>
       </c>
       <c r="J63">
         <v>3.747891506</v>
@@ -8863,37 +8863,37 @@
         <v>5.027709405</v>
       </c>
       <c r="S63">
-        <v>0.536306523</v>
+        <v>0.5363065228</v>
       </c>
       <c r="T63">
         <v>111.0058114</v>
       </c>
       <c r="U63">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V63">
-        <v>0.276654423</v>
+        <v>0.2766544226</v>
       </c>
       <c r="W63">
         <v>3.649494698</v>
       </c>
       <c r="X63">
-        <v>0.017134696</v>
+        <v>0.01713469591</v>
       </c>
       <c r="Y63">
-        <v>0.381783609</v>
+        <v>0.3817836094</v>
       </c>
       <c r="Z63">
-        <v>0.017134696</v>
+        <v>0.01713469591</v>
       </c>
       <c r="AA63">
         <v>0.25828685</v>
       </c>
       <c r="AB63">
-        <v>0.343957634</v>
+        <v>0.3439576338</v>
       </c>
       <c r="AC63">
-        <v>0.037825976</v>
+        <v>0.03782597558</v>
       </c>
       <c r="AD63">
         <v>89.99824252000001</v>
@@ -8917,19 +8917,19 @@
         <v>6714.935503</v>
       </c>
       <c r="AK63">
-        <v>0.001397248</v>
+        <v>0.001397247844</v>
       </c>
       <c r="AL63">
-        <v>0.017062418</v>
+        <v>0.01706241779</v>
       </c>
       <c r="AM63">
         <v>10.4519849</v>
       </c>
       <c r="AN63">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO63">
-        <v>0.130128442</v>
+        <v>0.1301284424</v>
       </c>
     </row>
     <row r="64">
@@ -8968,7 +8968,7 @@
         <v>417.8681758</v>
       </c>
       <c r="I64">
-        <v>0.263738455</v>
+        <v>0.2637384546</v>
       </c>
       <c r="J64">
         <v>3.778695783</v>
@@ -8998,37 +8998,37 @@
         <v>5.844354549</v>
       </c>
       <c r="S64">
-        <v>0.288748373</v>
+        <v>0.2887483731</v>
       </c>
       <c r="T64">
         <v>107.0041413</v>
       </c>
       <c r="U64">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V64">
-        <v>0.301061747</v>
+        <v>0.3010617469</v>
       </c>
       <c r="W64">
         <v>4.219203725</v>
       </c>
       <c r="X64">
-        <v>0.027507058</v>
+        <v>0.02750705781</v>
       </c>
       <c r="Y64">
-        <v>0.543731088</v>
+        <v>0.5437310883000001</v>
       </c>
       <c r="Z64">
-        <v>0.027507058</v>
+        <v>0.02750705781</v>
       </c>
       <c r="AA64">
         <v>0.347352828</v>
       </c>
       <c r="AB64">
-        <v>0.498556735</v>
+        <v>0.4985567348</v>
       </c>
       <c r="AC64">
-        <v>0.045174353</v>
+        <v>0.04517435347</v>
       </c>
       <c r="AD64">
         <v>44.97238686</v>
@@ -9052,10 +9052,10 @@
         <v>7949.457502</v>
       </c>
       <c r="AK64">
-        <v>0.001464636</v>
+        <v>0.001464636231</v>
       </c>
       <c r="AL64">
-        <v>0.017338578</v>
+        <v>0.0173385776</v>
       </c>
       <c r="AM64">
         <v>13.0066057</v>
@@ -9103,7 +9103,7 @@
         <v>386.9930395</v>
       </c>
       <c r="I65">
-        <v>0.047951333</v>
+        <v>0.04795133276</v>
       </c>
       <c r="J65">
         <v>3.317682391</v>
@@ -9133,37 +9133,37 @@
         <v>5.736736394</v>
       </c>
       <c r="S65">
-        <v>0.7984314769999999</v>
+        <v>0.7984314766</v>
       </c>
       <c r="T65">
         <v>137.7437965</v>
       </c>
       <c r="U65">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V65">
-        <v>0.28669343</v>
+        <v>0.2866934299</v>
       </c>
       <c r="W65">
         <v>3.890825893</v>
       </c>
       <c r="X65">
-        <v>0.021715088</v>
+        <v>0.0217150876</v>
       </c>
       <c r="Y65">
-        <v>0.503221297</v>
+        <v>0.5032212966</v>
       </c>
       <c r="Z65">
-        <v>0.021715088</v>
+        <v>0.0217150876</v>
       </c>
       <c r="AA65">
-        <v>0.335711502</v>
+        <v>0.3357115017</v>
       </c>
       <c r="AB65">
-        <v>0.458325268</v>
+        <v>0.4583252681</v>
       </c>
       <c r="AC65">
-        <v>0.044896029</v>
+        <v>0.04489602851</v>
       </c>
       <c r="AD65">
         <v>135.0084059</v>
@@ -9187,19 +9187,19 @@
         <v>6952.282145</v>
       </c>
       <c r="AK65">
-        <v>0.002419675</v>
+        <v>0.002419675128</v>
       </c>
       <c r="AL65">
-        <v>0.016871423</v>
+        <v>0.01687142286</v>
       </c>
       <c r="AM65">
         <v>10.35075437</v>
       </c>
       <c r="AN65">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO65">
-        <v>0.181662475</v>
+        <v>0.1816624751</v>
       </c>
     </row>
     <row r="66">
@@ -9238,7 +9238,7 @@
         <v>517.7693349</v>
       </c>
       <c r="I66">
-        <v>-0.320521595</v>
+        <v>-0.3205215945</v>
       </c>
       <c r="J66">
         <v>3.720009261</v>
@@ -9268,37 +9268,37 @@
         <v>6.400142744</v>
       </c>
       <c r="S66">
-        <v>0.753431169</v>
+        <v>0.7534311691</v>
       </c>
       <c r="T66">
         <v>47.75212056</v>
       </c>
       <c r="U66">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V66">
-        <v>0.322956188</v>
+        <v>0.3229561879</v>
       </c>
       <c r="W66">
         <v>4.834977551</v>
       </c>
       <c r="X66">
-        <v>0.024482252</v>
+        <v>0.02448225177</v>
       </c>
       <c r="Y66">
-        <v>0.6595049039999999</v>
+        <v>0.6595049041</v>
       </c>
       <c r="Z66">
-        <v>0.024482252</v>
+        <v>0.02448225177</v>
       </c>
       <c r="AA66">
-        <v>0.426191614</v>
+        <v>0.4261916144</v>
       </c>
       <c r="AB66">
-        <v>0.588549571</v>
+        <v>0.5885495707</v>
       </c>
       <c r="AC66">
-        <v>0.070955333</v>
+        <v>0.07095533337</v>
       </c>
       <c r="AD66">
         <v>44.98191128</v>
@@ -9307,7 +9307,7 @@
         <v>90.01480506999999</v>
       </c>
       <c r="AF66">
-        <v>0.005046929</v>
+        <v>0.005046928729</v>
       </c>
       <c r="AG66">
         <v>81.51971949</v>
@@ -9322,10 +9322,10 @@
         <v>8313.740258</v>
       </c>
       <c r="AK66">
-        <v>0.000487668</v>
+        <v>0.0004876679945</v>
       </c>
       <c r="AL66">
-        <v>0.017501216</v>
+        <v>0.01750121606</v>
       </c>
       <c r="AM66">
         <v>14.46620128</v>
@@ -9334,7 +9334,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO66">
-        <v>0.391952667</v>
+        <v>0.3919526666</v>
       </c>
     </row>
     <row r="67">
@@ -9373,7 +9373,7 @@
         <v>563.9910596</v>
       </c>
       <c r="I67">
-        <v>0.004988792</v>
+        <v>0.004988791514</v>
       </c>
       <c r="J67">
         <v>2.75808754</v>
@@ -9403,37 +9403,37 @@
         <v>6.014871235</v>
       </c>
       <c r="S67">
-        <v>0.708892242</v>
+        <v>0.7088922416</v>
       </c>
       <c r="T67">
         <v>93.25517787</v>
       </c>
       <c r="U67">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V67">
-        <v>0.344098862</v>
+        <v>0.3440988616</v>
       </c>
       <c r="W67">
         <v>5.519905521</v>
       </c>
       <c r="X67">
-        <v>0.026560607</v>
+        <v>0.02656060679</v>
       </c>
       <c r="Y67">
-        <v>0.743524072</v>
+        <v>0.7435240722999999</v>
       </c>
       <c r="Z67">
-        <v>0.026560607</v>
+        <v>0.02656060679</v>
       </c>
       <c r="AA67">
-        <v>0.52578815</v>
+        <v>0.5257881499</v>
       </c>
       <c r="AB67">
-        <v>0.681164278</v>
+        <v>0.6811642778</v>
       </c>
       <c r="AC67">
-        <v>0.062359794</v>
+        <v>0.06235979441</v>
       </c>
       <c r="AD67">
         <v>90.00133503000001</v>
@@ -9457,10 +9457,10 @@
         <v>8683.278</v>
       </c>
       <c r="AK67">
-        <v>0.001903948</v>
+        <v>0.001903947719</v>
       </c>
       <c r="AL67">
-        <v>0.017161876</v>
+        <v>0.01716187567</v>
       </c>
       <c r="AM67">
         <v>16.33687704</v>
@@ -9469,7 +9469,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO67">
-        <v>0.172895875</v>
+        <v>0.1728958752</v>
       </c>
     </row>
     <row r="68">
@@ -9508,7 +9508,7 @@
         <v>401.0010849</v>
       </c>
       <c r="I68">
-        <v>-0.241632578</v>
+        <v>-0.2416325778</v>
       </c>
       <c r="J68">
         <v>3.459914961</v>
@@ -9538,37 +9538,37 @@
         <v>5.435497932</v>
       </c>
       <c r="S68">
-        <v>0.7941327929999999</v>
+        <v>0.7941327928</v>
       </c>
       <c r="T68">
         <v>132.9842939</v>
       </c>
       <c r="U68">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V68">
-        <v>0.324012356</v>
+        <v>0.3240123559</v>
       </c>
       <c r="W68">
         <v>4.930065365</v>
       </c>
       <c r="X68">
-        <v>0.0181632</v>
+        <v>0.01816319969</v>
       </c>
       <c r="Y68">
-        <v>0.514959397</v>
+        <v>0.5149593973</v>
       </c>
       <c r="Z68">
-        <v>0.0181632</v>
+        <v>0.01816319969</v>
       </c>
       <c r="AA68">
-        <v>0.359120053</v>
+        <v>0.3591200533</v>
       </c>
       <c r="AB68">
-        <v>0.464862711</v>
+        <v>0.4648627109</v>
       </c>
       <c r="AC68">
-        <v>0.050096686</v>
+        <v>0.05009668632</v>
       </c>
       <c r="AD68">
         <v>134.989853</v>
@@ -9592,10 +9592,10 @@
         <v>6732.352212</v>
       </c>
       <c r="AK68">
-        <v>0.001445821</v>
+        <v>0.001445821406</v>
       </c>
       <c r="AL68">
-        <v>0.017198261</v>
+        <v>0.01719826133</v>
       </c>
       <c r="AM68">
         <v>14.6815462</v>
@@ -9604,7 +9604,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO68">
-        <v>0.139730955</v>
+        <v>0.1397309554</v>
       </c>
     </row>
     <row r="69">
@@ -9643,7 +9643,7 @@
         <v>535.8477432</v>
       </c>
       <c r="I69">
-        <v>0.372738428</v>
+        <v>0.3727384278</v>
       </c>
       <c r="J69">
         <v>3.505507152</v>
@@ -9673,37 +9673,37 @@
         <v>5.150563723</v>
       </c>
       <c r="S69">
-        <v>0.824482928</v>
+        <v>0.8244829275</v>
       </c>
       <c r="T69">
         <v>64.99647315999999</v>
       </c>
       <c r="U69">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V69">
-        <v>0.36919749</v>
+        <v>0.3691974903</v>
       </c>
       <c r="W69">
         <v>6.264271959</v>
       </c>
       <c r="X69">
-        <v>0.033848767</v>
+        <v>0.03384876706</v>
       </c>
       <c r="Y69">
-        <v>0.711058879</v>
+        <v>0.7110588792</v>
       </c>
       <c r="Z69">
-        <v>0.033848767</v>
+        <v>0.03384876706</v>
       </c>
       <c r="AA69">
-        <v>0.46214039</v>
+        <v>0.4621403896</v>
       </c>
       <c r="AB69">
-        <v>0.656490851</v>
+        <v>0.6564908508</v>
       </c>
       <c r="AC69">
-        <v>0.054568028</v>
+        <v>0.05456802843</v>
       </c>
       <c r="AD69">
         <v>179.9843774</v>
@@ -9727,10 +9727,10 @@
         <v>7775.392235</v>
       </c>
       <c r="AK69">
-        <v>0.002053967</v>
+        <v>0.002053967474</v>
       </c>
       <c r="AL69">
-        <v>0.017701573</v>
+        <v>0.01770157273</v>
       </c>
       <c r="AM69">
         <v>19.05408826</v>
@@ -9739,7 +9739,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO69">
-        <v>0.101174645</v>
+        <v>0.1011746451</v>
       </c>
     </row>
     <row r="70">
@@ -9808,37 +9808,37 @@
         <v>6.501686547</v>
       </c>
       <c r="S70">
-        <v>0.782194482</v>
+        <v>0.7821944823</v>
       </c>
       <c r="T70">
         <v>47.75220638</v>
       </c>
       <c r="U70">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V70">
-        <v>0.372351393</v>
+        <v>0.3723513932</v>
       </c>
       <c r="W70">
         <v>6.287440268</v>
       </c>
       <c r="X70">
-        <v>0.027673403</v>
+        <v>0.02767340313</v>
       </c>
       <c r="Y70">
-        <v>0.666908638</v>
+        <v>0.6669086383</v>
       </c>
       <c r="Z70">
-        <v>0.027673403</v>
+        <v>0.02767340313</v>
       </c>
       <c r="AA70">
         <v>0.437863012</v>
       </c>
       <c r="AB70">
-        <v>0.592606712</v>
+        <v>0.5926067116</v>
       </c>
       <c r="AC70">
-        <v>0.074301927</v>
+        <v>0.07430192665</v>
       </c>
       <c r="AD70">
         <v>44.97328878</v>
@@ -9862,10 +9862,10 @@
         <v>7932.573905</v>
       </c>
       <c r="AK70">
-        <v>0.001145965</v>
+        <v>0.001145964589</v>
       </c>
       <c r="AL70">
-        <v>0.017503451</v>
+        <v>0.01750345133</v>
       </c>
       <c r="AM70">
         <v>21.04311967</v>
@@ -9874,7 +9874,7 @@
         <v>1.230427007</v>
       </c>
       <c r="AO70">
-        <v>0.308022728</v>
+        <v>0.3080227281</v>
       </c>
     </row>
     <row r="71">
@@ -9913,7 +9913,7 @@
         <v>544.0909351</v>
       </c>
       <c r="I71">
-        <v>0.048618862</v>
+        <v>0.04861886228</v>
       </c>
       <c r="J71">
         <v>2.775194011</v>
@@ -9943,37 +9943,37 @@
         <v>6.049986434</v>
       </c>
       <c r="S71">
-        <v>0.707663213</v>
+        <v>0.7076632128</v>
       </c>
       <c r="T71">
         <v>93.25609701</v>
       </c>
       <c r="U71">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V71">
-        <v>0.359533198</v>
+        <v>0.3595331978</v>
       </c>
       <c r="W71">
         <v>5.974886589</v>
       </c>
       <c r="X71">
-        <v>0.025289721</v>
+        <v>0.02528972088</v>
       </c>
       <c r="Y71">
-        <v>0.730964995</v>
+        <v>0.7309649954</v>
       </c>
       <c r="Z71">
-        <v>0.025289721</v>
+        <v>0.02528972088</v>
       </c>
       <c r="AA71">
-        <v>0.504608168</v>
+        <v>0.5046081684</v>
       </c>
       <c r="AB71">
-        <v>0.672249327</v>
+        <v>0.6722493265</v>
       </c>
       <c r="AC71">
-        <v>0.058715669</v>
+        <v>0.05871566896</v>
       </c>
       <c r="AD71">
         <v>90.00874064</v>
@@ -9997,10 +9997,10 @@
         <v>6976.508125</v>
       </c>
       <c r="AK71">
-        <v>0.00205206</v>
+        <v>0.002052059834</v>
       </c>
       <c r="AL71">
-        <v>0.01682299</v>
+        <v>0.01682298951</v>
       </c>
       <c r="AM71">
         <v>17.37933814</v>
@@ -10048,7 +10048,7 @@
         <v>399.3463231</v>
       </c>
       <c r="I72">
-        <v>-0.256150643</v>
+        <v>-0.2561506425</v>
       </c>
       <c r="J72">
         <v>3.389816905</v>
@@ -10078,37 +10078,37 @@
         <v>5.46182266</v>
       </c>
       <c r="S72">
-        <v>0.825903901</v>
+        <v>0.8259039011</v>
       </c>
       <c r="T72">
         <v>137.2590893</v>
       </c>
       <c r="U72">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V72">
-        <v>0.341667638</v>
+        <v>0.3416676377</v>
       </c>
       <c r="W72">
         <v>5.455179044</v>
       </c>
       <c r="X72">
-        <v>0.018039154</v>
+        <v>0.01803915446</v>
       </c>
       <c r="Y72">
-        <v>0.508961849</v>
+        <v>0.5089618486</v>
       </c>
       <c r="Z72">
-        <v>0.018039154</v>
+        <v>0.01803915446</v>
       </c>
       <c r="AA72">
-        <v>0.359779575</v>
+        <v>0.3597795747</v>
       </c>
       <c r="AB72">
-        <v>0.459209886</v>
+        <v>0.4592098855</v>
       </c>
       <c r="AC72">
-        <v>0.049751963</v>
+        <v>0.04975196313</v>
       </c>
       <c r="AD72">
         <v>134.9911242</v>
@@ -10132,19 +10132,19 @@
         <v>6849.59987</v>
       </c>
       <c r="AK72">
-        <v>0.001913704</v>
+        <v>0.001913704039</v>
       </c>
       <c r="AL72">
-        <v>0.017092137</v>
+        <v>0.01709213667</v>
       </c>
       <c r="AM72">
         <v>16.02241157</v>
       </c>
       <c r="AN72">
-        <v>0.94899352</v>
+        <v>0.9489935195</v>
       </c>
       <c r="AO72">
-        <v>0.099442484</v>
+        <v>0.09944248416</v>
       </c>
     </row>
     <row r="73">
@@ -10183,7 +10183,7 @@
         <v>513.9530512</v>
       </c>
       <c r="I73">
-        <v>0.373421457</v>
+        <v>0.3734214574</v>
       </c>
       <c r="J73">
         <v>3.508212674</v>
@@ -10213,40 +10213,40 @@
         <v>5.323396336</v>
       </c>
       <c r="S73">
-        <v>0.839833783</v>
+        <v>0.8398337833</v>
       </c>
       <c r="T73">
         <v>65.01273119</v>
       </c>
       <c r="U73">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V73">
-        <v>0.355528759</v>
+        <v>0.3555287588</v>
       </c>
       <c r="W73">
         <v>5.829993467</v>
       </c>
       <c r="X73">
-        <v>0.031873859</v>
+        <v>0.03187385923</v>
       </c>
       <c r="Y73">
-        <v>0.683750445</v>
+        <v>0.6837504451999999</v>
       </c>
       <c r="Z73">
-        <v>0.031873859</v>
+        <v>0.03187385923</v>
       </c>
       <c r="AA73">
-        <v>0.446803642</v>
+        <v>0.4468036417</v>
       </c>
       <c r="AB73">
         <v>0.632118559</v>
       </c>
       <c r="AC73">
-        <v>0.051631886</v>
+        <v>0.05163188626</v>
       </c>
       <c r="AD73">
-        <v>0.003520189</v>
+        <v>0.003520189146</v>
       </c>
       <c r="AE73">
         <v>26.48705589</v>
@@ -10267,10 +10267,10 @@
         <v>7850.562888</v>
       </c>
       <c r="AK73">
-        <v>0.001656847</v>
+        <v>0.001656846775</v>
       </c>
       <c r="AL73">
-        <v>0.017819979</v>
+        <v>0.01781997912</v>
       </c>
       <c r="AM73">
         <v>17.02024272</v>
@@ -10279,7 +10279,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO73">
-        <v>0.123563413</v>
+        <v>0.1235634134</v>
       </c>
     </row>
     <row r="74">
@@ -10318,7 +10318,7 @@
         <v>634.8586626</v>
       </c>
       <c r="I74">
-        <v>0.185022633</v>
+        <v>0.1850226333</v>
       </c>
       <c r="J74">
         <v>3.488796906</v>
@@ -10348,37 +10348,37 @@
         <v>6.505632121</v>
       </c>
       <c r="S74">
-        <v>0.956344299</v>
+        <v>0.9563442993</v>
       </c>
       <c r="T74">
         <v>140.998305</v>
       </c>
       <c r="U74">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V74">
-        <v>0.380053854</v>
+        <v>0.3800538536</v>
       </c>
       <c r="W74">
         <v>6.612526978</v>
       </c>
       <c r="X74">
-        <v>0.038189676</v>
+        <v>0.03818967575</v>
       </c>
       <c r="Y74">
-        <v>0.833159793</v>
+        <v>0.8331597925000001</v>
       </c>
       <c r="Z74">
-        <v>0.038189676</v>
+        <v>0.03818967575</v>
       </c>
       <c r="AA74">
-        <v>0.549407881</v>
+        <v>0.5494078814</v>
       </c>
       <c r="AB74">
-        <v>0.7661243639999999</v>
+        <v>0.7661243637</v>
       </c>
       <c r="AC74">
-        <v>0.06703542899999999</v>
+        <v>0.0670354288</v>
       </c>
       <c r="AD74">
         <v>135.0010265</v>
@@ -10402,10 +10402,10 @@
         <v>11355.58808</v>
       </c>
       <c r="AK74">
-        <v>0.001054772</v>
+        <v>0.001054771963</v>
       </c>
       <c r="AL74">
-        <v>0.017362848</v>
+        <v>0.01736284784</v>
       </c>
       <c r="AM74">
         <v>18.63439743</v>
@@ -10414,7 +10414,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO74">
-        <v>0.306859884</v>
+        <v>0.3068598835</v>
       </c>
     </row>
     <row r="75">
@@ -10453,7 +10453,7 @@
         <v>461.5079497</v>
       </c>
       <c r="I75">
-        <v>-0.168494069</v>
+        <v>-0.1684940691</v>
       </c>
       <c r="J75">
         <v>4.453926188</v>
@@ -10483,37 +10483,37 @@
         <v>6.448611093</v>
       </c>
       <c r="S75">
-        <v>0.820237223</v>
+        <v>0.8202372233</v>
       </c>
       <c r="T75">
         <v>78.74003784999999</v>
       </c>
       <c r="U75">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V75">
-        <v>0.324044888</v>
+        <v>0.3240448875</v>
       </c>
       <c r="W75">
         <v>4.911084687</v>
       </c>
       <c r="X75">
-        <v>0.027115568</v>
+        <v>0.02711556844</v>
       </c>
       <c r="Y75">
-        <v>0.573505371</v>
+        <v>0.5735053714</v>
       </c>
       <c r="Z75">
-        <v>0.027115568</v>
+        <v>0.02711556844</v>
       </c>
       <c r="AA75">
-        <v>0.365374109</v>
+        <v>0.3653741091</v>
       </c>
       <c r="AB75">
-        <v>0.512557475</v>
+        <v>0.5125574751</v>
       </c>
       <c r="AC75">
-        <v>0.060947896</v>
+        <v>0.0609478963</v>
       </c>
       <c r="AD75">
         <v>90.00384127</v>
@@ -10537,10 +10537,10 @@
         <v>7122.95579</v>
       </c>
       <c r="AK75">
-        <v>0.001141417</v>
+        <v>0.001141416965</v>
       </c>
       <c r="AL75">
-        <v>0.017180893</v>
+        <v>0.01718089276</v>
       </c>
       <c r="AM75">
         <v>14.23603373</v>
@@ -10549,7 +10549,7 @@
         <v>1.080586533</v>
       </c>
       <c r="AO75">
-        <v>0.270996681</v>
+        <v>0.2709966809</v>
       </c>
     </row>
     <row r="76">
@@ -10588,7 +10588,7 @@
         <v>495.215823</v>
       </c>
       <c r="I76">
-        <v>-0.125065456</v>
+        <v>-0.1250654557</v>
       </c>
       <c r="J76">
         <v>3.446563715</v>
@@ -10618,37 +10618,37 @@
         <v>5.465301403</v>
       </c>
       <c r="S76">
-        <v>0.776847049</v>
+        <v>0.7768470487</v>
       </c>
       <c r="T76">
         <v>73.00691854</v>
       </c>
       <c r="U76">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V76">
-        <v>0.337998514</v>
+        <v>0.3379985136</v>
       </c>
       <c r="W76">
         <v>5.292972978</v>
       </c>
       <c r="X76">
-        <v>0.026910939</v>
+        <v>0.02691093869</v>
       </c>
       <c r="Y76">
-        <v>0.625542322</v>
+        <v>0.6255423218</v>
       </c>
       <c r="Z76">
-        <v>0.026910939</v>
+        <v>0.02691093869</v>
       </c>
       <c r="AA76">
-        <v>0.417169308</v>
+        <v>0.4171693077</v>
       </c>
       <c r="AB76">
-        <v>0.559166316</v>
+        <v>0.5591663157</v>
       </c>
       <c r="AC76">
-        <v>0.066376006</v>
+        <v>0.06637600616</v>
       </c>
       <c r="AD76">
         <v>89.99536625</v>
@@ -10672,10 +10672,10 @@
         <v>7802.403527</v>
       </c>
       <c r="AK76">
-        <v>0.00213459</v>
+        <v>0.00213458972</v>
       </c>
       <c r="AL76">
-        <v>0.017444407</v>
+        <v>0.01744440717</v>
       </c>
       <c r="AM76">
         <v>16.69675827</v>
@@ -10684,7 +10684,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO76">
-        <v>0.224689409</v>
+        <v>0.2246894092</v>
       </c>
     </row>
     <row r="77">
@@ -10723,7 +10723,7 @@
         <v>771.0203054</v>
       </c>
       <c r="I77">
-        <v>0.262916295</v>
+        <v>0.2629162949</v>
       </c>
       <c r="J77">
         <v>3.517253581</v>
@@ -10753,37 +10753,37 @@
         <v>6.40698724</v>
       </c>
       <c r="S77">
-        <v>0.893006081</v>
+        <v>0.8930060811</v>
       </c>
       <c r="T77">
         <v>86.50914155</v>
       </c>
       <c r="U77">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V77">
-        <v>0.417670973</v>
+        <v>0.4176709725</v>
       </c>
       <c r="W77">
         <v>7.800118118</v>
       </c>
       <c r="X77">
-        <v>0.047728956</v>
+        <v>0.04772895647</v>
       </c>
       <c r="Y77">
         <v>1.029015667</v>
       </c>
       <c r="Z77">
-        <v>0.047728956</v>
+        <v>0.04772895647</v>
       </c>
       <c r="AA77">
-        <v>0.646492341</v>
+        <v>0.6464923409</v>
       </c>
       <c r="AB77">
-        <v>0.944719309</v>
+        <v>0.9447193093</v>
       </c>
       <c r="AC77">
-        <v>0.084296358</v>
+        <v>0.08429635794</v>
       </c>
       <c r="AD77">
         <v>90.00024593000001</v>
@@ -10807,10 +10807,10 @@
         <v>8428.743055000001</v>
       </c>
       <c r="AK77">
-        <v>0.001084291</v>
+        <v>0.001084291108</v>
       </c>
       <c r="AL77">
-        <v>0.017472676</v>
+        <v>0.01747267567</v>
       </c>
       <c r="AM77">
         <v>26.09698216</v>
@@ -10819,7 +10819,7 @@
         <v>1.401045241</v>
       </c>
       <c r="AO77">
-        <v>0.226006291</v>
+        <v>0.2260062908</v>
       </c>
     </row>
     <row r="78">
@@ -10858,7 +10858,7 @@
         <v>619.3667868</v>
       </c>
       <c r="I78">
-        <v>0.302121501</v>
+        <v>0.3021215012</v>
       </c>
       <c r="J78">
         <v>4.080106348</v>
@@ -10876,7 +10876,7 @@
         <v>480.7359926</v>
       </c>
       <c r="O78">
-        <v>0.570712738</v>
+        <v>0.5707127377</v>
       </c>
       <c r="P78">
         <v>761.333232</v>
@@ -10894,31 +10894,31 @@
         <v>129.2481255</v>
       </c>
       <c r="U78">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V78">
-        <v>0.384736975</v>
+        <v>0.3847369749</v>
       </c>
       <c r="W78">
         <v>6.734194237</v>
       </c>
       <c r="X78">
-        <v>0.038495442</v>
+        <v>0.03849544224</v>
       </c>
       <c r="Y78">
-        <v>0.799814198</v>
+        <v>0.7998141976000001</v>
       </c>
       <c r="Z78">
-        <v>0.038495442</v>
+        <v>0.03849544224</v>
       </c>
       <c r="AA78">
-        <v>0.523971293</v>
+        <v>0.5239712927</v>
       </c>
       <c r="AB78">
         <v>0.734223306</v>
       </c>
       <c r="AC78">
-        <v>0.065590892</v>
+        <v>0.06559089160000001</v>
       </c>
       <c r="AD78">
         <v>90.00738932</v>
@@ -10942,10 +10942,10 @@
         <v>10221.01263</v>
       </c>
       <c r="AK78">
-        <v>0.001441395</v>
+        <v>0.001441395285</v>
       </c>
       <c r="AL78">
-        <v>0.017547906</v>
+        <v>0.01754790649</v>
       </c>
       <c r="AM78">
         <v>20.73199912</v>
@@ -10954,7 +10954,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO78">
-        <v>0.186156546</v>
+        <v>0.1861565462</v>
       </c>
     </row>
     <row r="79">
@@ -10993,7 +10993,7 @@
         <v>472.3638793</v>
       </c>
       <c r="I79">
-        <v>-0.120588245</v>
+        <v>-0.1205882446</v>
       </c>
       <c r="J79">
         <v>4.583780577</v>
@@ -11023,37 +11023,37 @@
         <v>6.503240196</v>
       </c>
       <c r="S79">
-        <v>0.835734151</v>
+        <v>0.8357341506</v>
       </c>
       <c r="T79">
         <v>42.25072015</v>
       </c>
       <c r="U79">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V79">
-        <v>0.341131672</v>
+        <v>0.3411316718</v>
       </c>
       <c r="W79">
         <v>5.393869981</v>
       </c>
       <c r="X79">
-        <v>0.029490975</v>
+        <v>0.0294909753</v>
       </c>
       <c r="Y79">
         <v>0.576405273</v>
       </c>
       <c r="Z79">
-        <v>0.029490975</v>
+        <v>0.0294909753</v>
       </c>
       <c r="AA79">
-        <v>0.373071642</v>
+        <v>0.3730716417</v>
       </c>
       <c r="AB79">
-        <v>0.514351706</v>
+        <v>0.5143517056</v>
       </c>
       <c r="AC79">
-        <v>0.062053567</v>
+        <v>0.06205356737</v>
       </c>
       <c r="AD79">
         <v>45.00835308</v>
@@ -11077,10 +11077,10 @@
         <v>7290.088536</v>
       </c>
       <c r="AK79">
-        <v>0.001475807</v>
+        <v>0.001475806546</v>
       </c>
       <c r="AL79">
-        <v>0.017283803</v>
+        <v>0.01728380301</v>
       </c>
       <c r="AM79">
         <v>16.35104849</v>
@@ -11089,7 +11089,7 @@
         <v>1.15307539</v>
       </c>
       <c r="AO79">
-        <v>0.285333803</v>
+        <v>0.2853338032</v>
       </c>
     </row>
     <row r="80">
@@ -11128,7 +11128,7 @@
         <v>474.1011126</v>
       </c>
       <c r="I80">
-        <v>0.148689026</v>
+        <v>0.1486890258</v>
       </c>
       <c r="J80">
         <v>3.146783397</v>
@@ -11158,13 +11158,13 @@
         <v>5.635656304</v>
       </c>
       <c r="S80">
-        <v>0.790710786</v>
+        <v>0.7907107861</v>
       </c>
       <c r="T80">
         <v>87.25229462</v>
       </c>
       <c r="U80">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V80">
         <v>0.358440387</v>
@@ -11173,22 +11173,22 @@
         <v>5.933325445</v>
       </c>
       <c r="X80">
-        <v>0.026363973</v>
+        <v>0.02636397301</v>
       </c>
       <c r="Y80">
-        <v>0.624801564</v>
+        <v>0.6248015643</v>
       </c>
       <c r="Z80">
-        <v>0.026363973</v>
+        <v>0.02636397301</v>
       </c>
       <c r="AA80">
-        <v>0.419013217</v>
+        <v>0.4190132173</v>
       </c>
       <c r="AB80">
-        <v>0.572280087</v>
+        <v>0.5722800868</v>
       </c>
       <c r="AC80">
-        <v>0.052521477</v>
+        <v>0.05252147749</v>
       </c>
       <c r="AD80">
         <v>89.9904839</v>
@@ -11212,10 +11212,10 @@
         <v>8397.109836</v>
       </c>
       <c r="AK80">
-        <v>0.001582366</v>
+        <v>0.001582366014</v>
       </c>
       <c r="AL80">
-        <v>0.017087327</v>
+        <v>0.01708732729</v>
       </c>
       <c r="AM80">
         <v>19.22119314</v>
@@ -11224,7 +11224,7 @@
         <v>1.012654737</v>
       </c>
       <c r="AO80">
-        <v>0.101590664</v>
+        <v>0.1015906642</v>
       </c>
     </row>
     <row r="81">
@@ -11263,7 +11263,7 @@
         <v>729.4114863999999</v>
       </c>
       <c r="I81">
-        <v>0.47787962</v>
+        <v>0.4778796195</v>
       </c>
       <c r="J81">
         <v>3.847813073</v>
@@ -11293,37 +11293,37 @@
         <v>6.34596851</v>
       </c>
       <c r="S81">
-        <v>0.843921343</v>
+        <v>0.8439213432</v>
       </c>
       <c r="T81">
         <v>53.75174034</v>
       </c>
       <c r="U81">
-        <v>0.424908504</v>
+        <v>0.4249085041</v>
       </c>
       <c r="V81">
-        <v>0.406171874</v>
+        <v>0.4061718738</v>
       </c>
       <c r="W81">
         <v>7.290662817</v>
       </c>
       <c r="X81">
-        <v>0.05188772</v>
+        <v>0.05188771977</v>
       </c>
       <c r="Y81">
-        <v>0.970096383</v>
+        <v>0.9700963829</v>
       </c>
       <c r="Z81">
-        <v>0.05188772</v>
+        <v>0.05188771977</v>
       </c>
       <c r="AA81">
-        <v>0.594281186</v>
+        <v>0.5942811864</v>
       </c>
       <c r="AB81">
-        <v>0.893298607</v>
+        <v>0.8932986067000001</v>
       </c>
       <c r="AC81">
-        <v>0.076797776</v>
+        <v>0.07679777619</v>
       </c>
       <c r="AD81">
         <v>45.01644532</v>
@@ -11347,10 +11347,10 @@
         <v>7603.362548</v>
       </c>
       <c r="AK81">
-        <v>0.000844173</v>
+        <v>0.00084417328</v>
       </c>
       <c r="AL81">
-        <v>0.017316381</v>
+        <v>0.01731638102</v>
       </c>
       <c r="AM81">
         <v>24.58992298</v>
@@ -11359,7 +11359,7 @@
         <v>1.312967594</v>
       </c>
       <c r="AO81">
-        <v>0.559712055</v>
+        <v>0.5597120549</v>
       </c>
     </row>
   </sheetData>
